--- a/data/comRead_vs_refCOM-coba.xlsx
+++ b/data/comRead_vs_refCOM-coba.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,28 +483,28 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-8.930999999999999</v>
+        <v>-11.681</v>
       </c>
       <c r="D2" t="n">
-        <v>-35.524</v>
+        <v>-35.597</v>
       </c>
       <c r="E2" t="n">
-        <v>191.103</v>
+        <v>190.981</v>
       </c>
       <c r="F2" t="n">
-        <v>-7</v>
+        <v>-9.757</v>
       </c>
       <c r="G2" t="n">
-        <v>-35.518</v>
+        <v>-35.52</v>
       </c>
       <c r="H2" t="n">
-        <v>191.103</v>
+        <v>190.981</v>
       </c>
       <c r="I2" t="n">
-        <v>5000</v>
+        <v>1100</v>
       </c>
       <c r="J2" t="n">
-        <v>13.72621615175026</v>
+        <v>11.42582165449258</v>
       </c>
     </row>
     <row r="3">
@@ -512,31 +512,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.032</v>
+        <v>0.041</v>
       </c>
       <c r="C3" t="n">
-        <v>-8.930999999999999</v>
+        <v>-8.680999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-35.521</v>
+        <v>-35.595</v>
       </c>
       <c r="E3" t="n">
-        <v>191.103</v>
+        <v>190.981</v>
       </c>
       <c r="F3" t="n">
-        <v>-7</v>
+        <v>-9.757</v>
       </c>
       <c r="G3" t="n">
-        <v>-35.518</v>
+        <v>-35.52</v>
       </c>
       <c r="H3" t="n">
-        <v>191.103</v>
+        <v>190.981</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.439269630818298</v>
+        <v>1.296482696848138</v>
       </c>
     </row>
     <row r="4">
@@ -544,31 +544,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.803</v>
+        <v>86.771</v>
       </c>
       <c r="C4" t="n">
-        <v>-8.930999999999999</v>
+        <v>-8.680999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>-26.218</v>
+        <v>-30.449</v>
       </c>
       <c r="E4" t="n">
-        <v>191.112</v>
+        <v>190.981</v>
       </c>
       <c r="F4" t="n">
-        <v>-7</v>
+        <v>-9.757</v>
       </c>
       <c r="G4" t="n">
-        <v>-35.871</v>
+        <v>-35.52</v>
       </c>
       <c r="H4" t="n">
-        <v>191.112</v>
+        <v>190.981</v>
       </c>
       <c r="I4" t="n">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="J4" t="n">
-        <v>12.00302594367595</v>
+        <v>9.931672610749228</v>
       </c>
     </row>
     <row r="5">
@@ -576,31 +576,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>165.331</v>
+        <v>166.65</v>
       </c>
       <c r="C5" t="n">
-        <v>-8.930999999999999</v>
+        <v>-8.680999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-17.799</v>
+        <v>-25.71</v>
       </c>
       <c r="E5" t="n">
-        <v>191.077</v>
+        <v>191.005</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.404</v>
+        <v>-9.757</v>
       </c>
       <c r="G5" t="n">
-        <v>-36.931</v>
+        <v>-36.227</v>
       </c>
       <c r="H5" t="n">
-        <v>191.077</v>
+        <v>191.005</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.293702436461849</v>
+        <v>1.183338454250571</v>
       </c>
     </row>
     <row r="6">
@@ -608,25 +608,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245.133</v>
+        <v>244.304</v>
       </c>
       <c r="C6" t="n">
-        <v>-8.930999999999999</v>
+        <v>-8.680999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>-9.243</v>
+        <v>-21.103</v>
       </c>
       <c r="E6" t="n">
-        <v>193.614</v>
+        <v>191.62</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.407</v>
+        <v>-9.73</v>
       </c>
       <c r="G6" t="n">
-        <v>-27.437</v>
+        <v>-34.147</v>
       </c>
       <c r="H6" t="n">
-        <v>193.614</v>
+        <v>191.62</v>
       </c>
     </row>
     <row r="7">
@@ -634,25 +634,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325.628</v>
+        <v>324.859</v>
       </c>
       <c r="C7" t="n">
-        <v>-8.930999999999999</v>
+        <v>-8.680999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.613</v>
+        <v>-16.324</v>
       </c>
       <c r="E7" t="n">
-        <v>195.742</v>
+        <v>192.189</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.266</v>
+        <v>-10.101</v>
       </c>
       <c r="G7" t="n">
-        <v>-18.529</v>
+        <v>-29.805</v>
       </c>
       <c r="H7" t="n">
-        <v>195.742</v>
+        <v>192.189</v>
       </c>
     </row>
     <row r="8">
@@ -660,25 +660,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>405.123</v>
+        <v>404.748</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.829</v>
+        <v>-8.680999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.037</v>
+        <v>-11.584</v>
       </c>
       <c r="E8" t="n">
-        <v>197.736</v>
+        <v>193.903</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.802</v>
+        <v>-7.355</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.592</v>
+        <v>-22.368</v>
       </c>
       <c r="H8" t="n">
-        <v>197.736</v>
+        <v>193.903</v>
       </c>
     </row>
     <row r="9">
@@ -686,25 +686,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>486.152</v>
+        <v>485.075</v>
       </c>
       <c r="C9" t="n">
-        <v>-6.208</v>
+        <v>-8.680999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8100000000000001</v>
+        <v>-6.818</v>
       </c>
       <c r="E9" t="n">
-        <v>198.186</v>
+        <v>195.205</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.045</v>
+        <v>-7.354</v>
       </c>
       <c r="G9" t="n">
-        <v>3.098</v>
+        <v>-14.836</v>
       </c>
       <c r="H9" t="n">
-        <v>198.186</v>
+        <v>195.205</v>
       </c>
     </row>
     <row r="10">
@@ -712,25 +712,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>567.663</v>
+        <v>564.7380000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.578</v>
+        <v>-8.680999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.662</v>
+        <v>-2.092</v>
       </c>
       <c r="E10" t="n">
-        <v>198.605</v>
+        <v>195.006</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.632</v>
+        <v>-4.836</v>
       </c>
       <c r="G10" t="n">
-        <v>5.978</v>
+        <v>-13.272</v>
       </c>
       <c r="H10" t="n">
-        <v>198.605</v>
+        <v>195.006</v>
       </c>
     </row>
     <row r="11">
@@ -738,25 +738,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>645.163</v>
+        <v>644.208</v>
       </c>
       <c r="C11" t="n">
-        <v>-4.481</v>
+        <v>-8.239000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1.713</v>
+        <v>-2.084</v>
       </c>
       <c r="E11" t="n">
-        <v>198.239</v>
+        <v>195.878</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.495</v>
+        <v>-4.5</v>
       </c>
       <c r="G11" t="n">
-        <v>9.114000000000001</v>
+        <v>-8.086</v>
       </c>
       <c r="H11" t="n">
-        <v>198.239</v>
+        <v>195.878</v>
       </c>
     </row>
     <row r="12">
@@ -764,25 +764,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>725.0359999999999</v>
+        <v>724.784</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.308</v>
+        <v>-7.433</v>
       </c>
       <c r="D12" t="n">
-        <v>1.803</v>
+        <v>-2.069</v>
       </c>
       <c r="E12" t="n">
-        <v>197.598</v>
+        <v>196.476</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.113</v>
+        <v>-3.942</v>
       </c>
       <c r="G12" t="n">
-        <v>9.114000000000001</v>
+        <v>-2.504</v>
       </c>
       <c r="H12" t="n">
-        <v>197.598</v>
+        <v>196.476</v>
       </c>
     </row>
     <row r="13">
@@ -790,25 +790,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>805.625</v>
+        <v>804.5410000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>-4.135</v>
+        <v>-6.636</v>
       </c>
       <c r="D13" t="n">
-        <v>1.894</v>
+        <v>-2.054</v>
       </c>
       <c r="E13" t="n">
-        <v>197.007</v>
+        <v>196.825</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.46</v>
+        <v>-3.427</v>
       </c>
       <c r="G13" t="n">
-        <v>9.098000000000001</v>
+        <v>-2.303</v>
       </c>
       <c r="H13" t="n">
-        <v>197.007</v>
+        <v>196.825</v>
       </c>
     </row>
     <row r="14">
@@ -816,25 +816,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>885.217</v>
+        <v>884.645</v>
       </c>
       <c r="C14" t="n">
-        <v>-3.963</v>
+        <v>-5.835</v>
       </c>
       <c r="D14" t="n">
-        <v>1.983</v>
+        <v>-2.04</v>
       </c>
       <c r="E14" t="n">
-        <v>196.342</v>
+        <v>197.114</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.557</v>
+        <v>-2.984</v>
       </c>
       <c r="G14" t="n">
-        <v>9.435</v>
+        <v>0.748</v>
       </c>
       <c r="H14" t="n">
-        <v>196.342</v>
+        <v>197.114</v>
       </c>
     </row>
     <row r="15">
@@ -842,25 +842,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>965.165</v>
+        <v>964.688</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.784</v>
+        <v>-5.034</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.164</v>
+        <v>-2.025</v>
       </c>
       <c r="E15" t="n">
-        <v>195.798</v>
+        <v>197.288</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.916</v>
+        <v>-2.958</v>
       </c>
       <c r="G15" t="n">
-        <v>6.947</v>
+        <v>0.852</v>
       </c>
       <c r="H15" t="n">
-        <v>195.798</v>
+        <v>197.288</v>
       </c>
     </row>
     <row r="16">
@@ -868,25 +868,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1000</v>
+        <v>1048.853</v>
       </c>
       <c r="C16" t="n">
-        <v>0.898</v>
+        <v>-4.192</v>
       </c>
       <c r="D16" t="n">
-        <v>-16.191</v>
+        <v>-2.009</v>
       </c>
       <c r="E16" t="n">
-        <v>194.855</v>
+        <v>197.373</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.523</v>
+        <v>-2.769</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.204</v>
+        <v>0.904</v>
       </c>
       <c r="H16" t="n">
-        <v>194.855</v>
+        <v>197.373</v>
       </c>
     </row>
     <row r="17">
@@ -894,25 +894,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1000</v>
+        <v>1127.041</v>
       </c>
       <c r="C17" t="n">
-        <v>3.569</v>
+        <v>-4.167</v>
       </c>
       <c r="D17" t="n">
-        <v>-26.178</v>
+        <v>-1.91</v>
       </c>
       <c r="E17" t="n">
-        <v>190.406</v>
+        <v>197.165</v>
       </c>
       <c r="F17" t="n">
-        <v>-21.688</v>
+        <v>-5.187</v>
       </c>
       <c r="G17" t="n">
-        <v>49.624</v>
+        <v>1.171</v>
       </c>
       <c r="H17" t="n">
-        <v>190.406</v>
+        <v>197.165</v>
       </c>
     </row>
     <row r="18">
@@ -920,25 +920,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1000.064</v>
+        <v>1204.46</v>
       </c>
       <c r="C18" t="n">
-        <v>-18.861</v>
+        <v>-4.095</v>
       </c>
       <c r="D18" t="n">
-        <v>49.615</v>
+        <v>-1.627</v>
       </c>
       <c r="E18" t="n">
-        <v>190.491</v>
+        <v>196.737</v>
       </c>
       <c r="F18" t="n">
-        <v>-22.256</v>
+        <v>-7.095</v>
       </c>
       <c r="G18" t="n">
-        <v>47.821</v>
+        <v>0.502</v>
       </c>
       <c r="H18" t="n">
-        <v>190.491</v>
+        <v>196.737</v>
       </c>
     </row>
     <row r="19">
@@ -946,25 +946,25 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1074.814</v>
+        <v>1284.574</v>
       </c>
       <c r="C19" t="n">
-        <v>-16.74</v>
+        <v>-4.021</v>
       </c>
       <c r="D19" t="n">
-        <v>37.599</v>
+        <v>-1.335</v>
       </c>
       <c r="E19" t="n">
-        <v>190.479</v>
+        <v>197.302</v>
       </c>
       <c r="F19" t="n">
-        <v>-22.609</v>
+        <v>-6.968</v>
       </c>
       <c r="G19" t="n">
-        <v>48.528</v>
+        <v>1.213</v>
       </c>
       <c r="H19" t="n">
-        <v>190.479</v>
+        <v>197.302</v>
       </c>
     </row>
     <row r="20">
@@ -972,25 +972,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1154.719</v>
+        <v>1364.89</v>
       </c>
       <c r="C20" t="n">
-        <v>-14.473</v>
+        <v>-3.946</v>
       </c>
       <c r="D20" t="n">
-        <v>27.076</v>
+        <v>-1.041</v>
       </c>
       <c r="E20" t="n">
-        <v>190.944</v>
+        <v>196.957</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.368</v>
+        <v>-9.961</v>
       </c>
       <c r="G20" t="n">
-        <v>46.786</v>
+        <v>1.05</v>
       </c>
       <c r="H20" t="n">
-        <v>190.944</v>
+        <v>196.957</v>
       </c>
     </row>
     <row r="21">
@@ -998,25 +998,25 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1241.102</v>
+        <v>1444.841</v>
       </c>
       <c r="C21" t="n">
-        <v>-12.021</v>
+        <v>-3.872</v>
       </c>
       <c r="D21" t="n">
-        <v>14.557</v>
+        <v>-0.749</v>
       </c>
       <c r="E21" t="n">
-        <v>194.106</v>
+        <v>196.595</v>
       </c>
       <c r="F21" t="n">
-        <v>-23.795</v>
+        <v>-10.073</v>
       </c>
       <c r="G21" t="n">
-        <v>37.651</v>
+        <v>1.227</v>
       </c>
       <c r="H21" t="n">
-        <v>194.106</v>
+        <v>196.595</v>
       </c>
     </row>
     <row r="22">
@@ -1024,25 +1024,25 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1331.053</v>
+        <v>1524.689</v>
       </c>
       <c r="C22" t="n">
-        <v>-9.468999999999999</v>
+        <v>-3.797</v>
       </c>
       <c r="D22" t="n">
-        <v>2.038</v>
+        <v>-0.458</v>
       </c>
       <c r="E22" t="n">
-        <v>196.842</v>
+        <v>196.28</v>
       </c>
       <c r="F22" t="n">
-        <v>-19.135</v>
+        <v>-10.356</v>
       </c>
       <c r="G22" t="n">
-        <v>29.094</v>
+        <v>-1.818</v>
       </c>
       <c r="H22" t="n">
-        <v>196.842</v>
+        <v>196.28</v>
       </c>
     </row>
     <row r="23">
@@ -1050,25 +1050,25 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1413.598</v>
+        <v>1604.384</v>
       </c>
       <c r="C23" t="n">
-        <v>-9.332000000000001</v>
+        <v>-3.723</v>
       </c>
       <c r="D23" t="n">
-        <v>1.52</v>
+        <v>-0.167</v>
       </c>
       <c r="E23" t="n">
-        <v>199.568</v>
+        <v>195.93</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.716</v>
+        <v>-8.034000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>11.306</v>
+        <v>-1.983</v>
       </c>
       <c r="H23" t="n">
-        <v>199.568</v>
+        <v>195.93</v>
       </c>
     </row>
     <row r="24">
@@ -1076,25 +1076,25 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1490.89</v>
+        <v>1684.438</v>
       </c>
       <c r="C24" t="n">
-        <v>-9.166</v>
+        <v>-3.094</v>
       </c>
       <c r="D24" t="n">
-        <v>0.889</v>
+        <v>-2.385</v>
       </c>
       <c r="E24" t="n">
-        <v>200.429</v>
+        <v>195.798</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.098000000000001</v>
+        <v>-5.739</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.158</v>
+        <v>-2.075</v>
       </c>
       <c r="H24" t="n">
-        <v>200.429</v>
+        <v>195.798</v>
       </c>
     </row>
     <row r="25">
@@ -1102,25 +1102,25 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1570.997</v>
+        <v>1764.223</v>
       </c>
       <c r="C25" t="n">
-        <v>-8.993</v>
+        <v>-1.637</v>
       </c>
       <c r="D25" t="n">
-        <v>0.236</v>
+        <v>-7.525</v>
       </c>
       <c r="E25" t="n">
-        <v>200.248</v>
+        <v>195.366</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.762</v>
+        <v>-1.017</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.224</v>
+        <v>0.988</v>
       </c>
       <c r="H25" t="n">
-        <v>200.248</v>
+        <v>195.366</v>
       </c>
     </row>
     <row r="26">
@@ -1128,25 +1128,25 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>1651.321</v>
+        <v>1844.296</v>
       </c>
       <c r="C26" t="n">
-        <v>-8.127000000000001</v>
+        <v>-0.176</v>
       </c>
       <c r="D26" t="n">
-        <v>0.196</v>
+        <v>-12.683</v>
       </c>
       <c r="E26" t="n">
-        <v>199.43</v>
+        <v>195.176</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.407</v>
+        <v>1.487</v>
       </c>
       <c r="G26" t="n">
-        <v>-11.189</v>
+        <v>1.291</v>
       </c>
       <c r="H26" t="n">
-        <v>199.43</v>
+        <v>195.176</v>
       </c>
     </row>
     <row r="27">
@@ -1154,25 +1154,25 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>1733.303</v>
+        <v>1925.091</v>
       </c>
       <c r="C27" t="n">
-        <v>-6.744</v>
+        <v>1.3</v>
       </c>
       <c r="D27" t="n">
-        <v>0.131</v>
+        <v>-17.888</v>
       </c>
       <c r="E27" t="n">
-        <v>198.569</v>
+        <v>194.644</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.571</v>
+        <v>4.361</v>
       </c>
       <c r="G27" t="n">
-        <v>-14.441</v>
+        <v>-0.635</v>
       </c>
       <c r="H27" t="n">
-        <v>198.569</v>
+        <v>194.644</v>
       </c>
     </row>
     <row r="28">
@@ -1180,25 +1180,25 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>1811.024</v>
+        <v>2000</v>
       </c>
       <c r="C28" t="n">
-        <v>-5.432</v>
+        <v>2.763</v>
       </c>
       <c r="D28" t="n">
-        <v>0.07000000000000001</v>
+        <v>-23.051</v>
       </c>
       <c r="E28" t="n">
-        <v>197.347</v>
+        <v>194.05</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.549</v>
+        <v>7.085</v>
       </c>
       <c r="G28" t="n">
-        <v>-10.968</v>
+        <v>-5.362</v>
       </c>
       <c r="H28" t="n">
-        <v>197.347</v>
+        <v>194.05</v>
       </c>
     </row>
     <row r="29">
@@ -1206,25 +1206,25 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>1890.668</v>
+        <v>2000</v>
       </c>
       <c r="C29" t="n">
-        <v>-4.088</v>
+        <v>4.243</v>
       </c>
       <c r="D29" t="n">
-        <v>0.007</v>
+        <v>-28.272</v>
       </c>
       <c r="E29" t="n">
-        <v>195.679</v>
+        <v>190.854</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.101</v>
+        <v>-20.264</v>
       </c>
       <c r="G29" t="n">
-        <v>-6.918</v>
+        <v>47.389</v>
       </c>
       <c r="H29" t="n">
-        <v>195.679</v>
+        <v>190.854</v>
       </c>
     </row>
     <row r="30">
@@ -1232,25 +1232,25 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1971.108</v>
+        <v>2000.058</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.681</v>
+        <v>-22.514</v>
       </c>
       <c r="D30" t="n">
-        <v>7.24</v>
+        <v>47.384</v>
       </c>
       <c r="E30" t="n">
-        <v>195.075</v>
+        <v>190.381</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.261</v>
+        <v>-22.614</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.968</v>
+        <v>45.91</v>
       </c>
       <c r="H30" t="n">
-        <v>195.075</v>
+        <v>190.381</v>
       </c>
     </row>
     <row r="31">
@@ -1258,25 +1258,25 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>2000</v>
+        <v>2087.407</v>
       </c>
       <c r="C31" t="n">
-        <v>1.023</v>
+        <v>-20.354</v>
       </c>
       <c r="D31" t="n">
-        <v>15.363</v>
+        <v>39.222</v>
       </c>
       <c r="E31" t="n">
-        <v>194.533</v>
+        <v>190.36</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.049</v>
+        <v>-22.614</v>
       </c>
       <c r="G31" t="n">
-        <v>5.638</v>
+        <v>46.263</v>
       </c>
       <c r="H31" t="n">
-        <v>194.533</v>
+        <v>190.36</v>
       </c>
     </row>
     <row r="32">
@@ -1284,25 +1284,25 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>2000</v>
+        <v>2167.362</v>
       </c>
       <c r="C32" t="n">
-        <v>3.723</v>
+        <v>-18.377</v>
       </c>
       <c r="D32" t="n">
-        <v>23.476</v>
+        <v>33.359</v>
       </c>
       <c r="E32" t="n">
-        <v>190.451</v>
+        <v>190.239</v>
       </c>
       <c r="F32" t="n">
-        <v>-29.579</v>
+        <v>-22.446</v>
       </c>
       <c r="G32" t="n">
-        <v>-47.329</v>
+        <v>46.967</v>
       </c>
       <c r="H32" t="n">
-        <v>190.451</v>
+        <v>190.239</v>
       </c>
     </row>
     <row r="33">
@@ -1310,25 +1310,25 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>2000.056</v>
+        <v>2247.254</v>
       </c>
       <c r="C33" t="n">
-        <v>-23.944</v>
+        <v>-16.402</v>
       </c>
       <c r="D33" t="n">
-        <v>-47.322</v>
+        <v>27.612</v>
       </c>
       <c r="E33" t="n">
-        <v>188.642</v>
+        <v>191.885</v>
       </c>
       <c r="F33" t="n">
-        <v>-34.103</v>
+        <v>-22.827</v>
       </c>
       <c r="G33" t="n">
-        <v>-45.746</v>
+        <v>42.102</v>
       </c>
       <c r="H33" t="n">
-        <v>188.642</v>
+        <v>191.885</v>
       </c>
     </row>
     <row r="34">
@@ -1336,25 +1336,25 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>2075.993</v>
+        <v>2327.434</v>
       </c>
       <c r="C34" t="n">
-        <v>-20.686</v>
+        <v>-14.42</v>
       </c>
       <c r="D34" t="n">
-        <v>-36.031</v>
+        <v>19.126</v>
       </c>
       <c r="E34" t="n">
-        <v>188.85</v>
+        <v>192.649</v>
       </c>
       <c r="F34" t="n">
-        <v>-34.118</v>
+        <v>-23.014</v>
       </c>
       <c r="G34" t="n">
-        <v>-46.115</v>
+        <v>38.113</v>
       </c>
       <c r="H34" t="n">
-        <v>188.85</v>
+        <v>192.649</v>
       </c>
     </row>
     <row r="35">
@@ -1362,25 +1362,25 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>2156.224</v>
+        <v>2407.259</v>
       </c>
       <c r="C35" t="n">
-        <v>-17.244</v>
+        <v>-12.446</v>
       </c>
       <c r="D35" t="n">
-        <v>-25.978</v>
+        <v>12.243</v>
       </c>
       <c r="E35" t="n">
-        <v>188.827</v>
+        <v>194.679</v>
       </c>
       <c r="F35" t="n">
-        <v>-35.279</v>
+        <v>-21.334</v>
       </c>
       <c r="G35" t="n">
-        <v>-47.172</v>
+        <v>28.757</v>
       </c>
       <c r="H35" t="n">
-        <v>188.827</v>
+        <v>194.679</v>
       </c>
     </row>
     <row r="36">
@@ -1388,25 +1388,25 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>2236.065</v>
+        <v>2492.531</v>
       </c>
       <c r="C36" t="n">
-        <v>-13.819</v>
+        <v>-10.338</v>
       </c>
       <c r="D36" t="n">
-        <v>-16.03</v>
+        <v>5.151</v>
       </c>
       <c r="E36" t="n">
-        <v>192.779</v>
+        <v>196.253</v>
       </c>
       <c r="F36" t="n">
-        <v>-31.255</v>
+        <v>-19.679</v>
       </c>
       <c r="G36" t="n">
-        <v>-38.177</v>
+        <v>19.245</v>
       </c>
       <c r="H36" t="n">
-        <v>192.779</v>
+        <v>196.253</v>
       </c>
     </row>
     <row r="37">
@@ -1414,25 +1414,25 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>2315.769</v>
+        <v>2567.389</v>
       </c>
       <c r="C37" t="n">
-        <v>-10.4</v>
+        <v>-8.487</v>
       </c>
       <c r="D37" t="n">
-        <v>-4.636</v>
+        <v>1.046</v>
       </c>
       <c r="E37" t="n">
-        <v>197.155</v>
+        <v>197.94</v>
       </c>
       <c r="F37" t="n">
-        <v>-24.434</v>
+        <v>-14.673</v>
       </c>
       <c r="G37" t="n">
-        <v>-25.819</v>
+        <v>11.791</v>
       </c>
       <c r="H37" t="n">
-        <v>197.155</v>
+        <v>197.94</v>
       </c>
     </row>
     <row r="38">
@@ -1440,25 +1440,25 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>2396.08</v>
+        <v>2649.487</v>
       </c>
       <c r="C38" t="n">
-        <v>-10.129</v>
+        <v>-8.407</v>
       </c>
       <c r="D38" t="n">
-        <v>-3.966</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>199.064</v>
+        <v>197.068</v>
       </c>
       <c r="F38" t="n">
-        <v>-16.967</v>
+        <v>-12.6</v>
       </c>
       <c r="G38" t="n">
-        <v>-13.595</v>
+        <v>2.789</v>
       </c>
       <c r="H38" t="n">
-        <v>199.064</v>
+        <v>197.068</v>
       </c>
     </row>
     <row r="39">
@@ -1466,25 +1466,25 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>2475.782</v>
+        <v>2727.323</v>
       </c>
       <c r="C39" t="n">
-        <v>-9.661</v>
+        <v>-8.282</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.807</v>
+        <v>0.78</v>
       </c>
       <c r="E39" t="n">
-        <v>200.06</v>
+        <v>197.371</v>
       </c>
       <c r="F39" t="n">
-        <v>-9.205</v>
+        <v>-9.891999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>-3.144</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>200.06</v>
+        <v>197.371</v>
       </c>
     </row>
     <row r="40">
@@ -1492,25 +1492,25 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>2556.283</v>
+        <v>2809.969</v>
       </c>
       <c r="C40" t="n">
-        <v>-9.188000000000001</v>
+        <v>-8.148999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.636</v>
+        <v>0.607</v>
       </c>
       <c r="E40" t="n">
-        <v>199.844</v>
+        <v>197.364</v>
       </c>
       <c r="F40" t="n">
-        <v>-7.516</v>
+        <v>-7.394</v>
       </c>
       <c r="G40" t="n">
-        <v>2.499</v>
+        <v>-5.83</v>
       </c>
       <c r="H40" t="n">
-        <v>199.844</v>
+        <v>197.364</v>
       </c>
     </row>
     <row r="41">
@@ -1518,25 +1518,25 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>2635.668</v>
+        <v>2887.434</v>
       </c>
       <c r="C41" t="n">
-        <v>-8.563000000000001</v>
+        <v>-8.023999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.56</v>
+        <v>0.445</v>
       </c>
       <c r="E41" t="n">
-        <v>198.716</v>
+        <v>197.013</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.281</v>
+        <v>-7.388</v>
       </c>
       <c r="G41" t="n">
-        <v>4.77</v>
+        <v>-6.097</v>
       </c>
       <c r="H41" t="n">
-        <v>198.716</v>
+        <v>197.013</v>
       </c>
     </row>
     <row r="42">
@@ -1544,25 +1544,25 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>2715.664</v>
+        <v>2967.514</v>
       </c>
       <c r="C42" t="n">
-        <v>-7.161</v>
+        <v>-7.895</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.391</v>
+        <v>0.277</v>
       </c>
       <c r="E42" t="n">
-        <v>198.328</v>
+        <v>196.438</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.463</v>
+        <v>-7.123</v>
       </c>
       <c r="G42" t="n">
-        <v>4.89</v>
+        <v>-5.749</v>
       </c>
       <c r="H42" t="n">
-        <v>198.328</v>
+        <v>196.438</v>
       </c>
     </row>
     <row r="43">
@@ -1570,25 +1570,25 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>2795.745</v>
+        <v>3047.412</v>
       </c>
       <c r="C43" t="n">
-        <v>-5.758</v>
+        <v>-7.766</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.221</v>
+        <v>0.11</v>
       </c>
       <c r="E43" t="n">
-        <v>197.841</v>
+        <v>196.741</v>
       </c>
       <c r="F43" t="n">
-        <v>0.291</v>
+        <v>-7.082</v>
       </c>
       <c r="G43" t="n">
-        <v>4.963</v>
+        <v>-6.405</v>
       </c>
       <c r="H43" t="n">
-        <v>197.841</v>
+        <v>196.741</v>
       </c>
     </row>
     <row r="44">
@@ -1596,25 +1596,25 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>2875.928</v>
+        <v>3127.552</v>
       </c>
       <c r="C44" t="n">
-        <v>-4.353</v>
+        <v>-7.511</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.051</v>
+        <v>0.104</v>
       </c>
       <c r="E44" t="n">
-        <v>195.851</v>
+        <v>196.441</v>
       </c>
       <c r="F44" t="n">
-        <v>3.252</v>
+        <v>-7.064</v>
       </c>
       <c r="G44" t="n">
-        <v>3.43</v>
+        <v>-3.748</v>
       </c>
       <c r="H44" t="n">
-        <v>195.851</v>
+        <v>196.441</v>
       </c>
     </row>
     <row r="45">
@@ -1622,25 +1622,25 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>2956.021</v>
+        <v>3207.819</v>
       </c>
       <c r="C45" t="n">
-        <v>-2.407</v>
+        <v>-6.769</v>
       </c>
       <c r="D45" t="n">
-        <v>-7.488</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>194.585</v>
+        <v>196.324</v>
       </c>
       <c r="F45" t="n">
-        <v>4.057</v>
+        <v>-6.732</v>
       </c>
       <c r="G45" t="n">
-        <v>3.124</v>
+        <v>-1.155</v>
       </c>
       <c r="H45" t="n">
-        <v>194.585</v>
+        <v>196.324</v>
       </c>
     </row>
     <row r="46">
@@ -1648,25 +1648,25 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>3000</v>
+        <v>3287.926</v>
       </c>
       <c r="C46" t="n">
-        <v>0.366</v>
+        <v>-6.029</v>
       </c>
       <c r="D46" t="n">
-        <v>-16.661</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>194.139</v>
+        <v>196.331</v>
       </c>
       <c r="F46" t="n">
-        <v>2.04</v>
+        <v>-6.403</v>
       </c>
       <c r="G46" t="n">
-        <v>-4.458</v>
+        <v>1.719</v>
       </c>
       <c r="H46" t="n">
-        <v>194.139</v>
+        <v>196.331</v>
       </c>
     </row>
     <row r="47">
@@ -1674,25 +1674,25 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>3000</v>
+        <v>3367.693</v>
       </c>
       <c r="C47" t="n">
-        <v>3.135</v>
+        <v>-5.291</v>
       </c>
       <c r="D47" t="n">
-        <v>-25.819</v>
+        <v>0.056</v>
       </c>
       <c r="E47" t="n">
-        <v>189.423</v>
+        <v>196.193</v>
       </c>
       <c r="F47" t="n">
-        <v>-28.986</v>
+        <v>-6.364</v>
       </c>
       <c r="G47" t="n">
-        <v>54.061</v>
+        <v>1.793</v>
       </c>
       <c r="H47" t="n">
-        <v>189.423</v>
+        <v>196.193</v>
       </c>
     </row>
     <row r="48">
@@ -1700,25 +1700,25 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>3000.073</v>
+        <v>3447.572</v>
       </c>
       <c r="C48" t="n">
-        <v>-25.562</v>
+        <v>-4.553</v>
       </c>
       <c r="D48" t="n">
-        <v>54.05</v>
+        <v>0.04</v>
       </c>
       <c r="E48" t="n">
-        <v>188.387</v>
+        <v>195.97</v>
       </c>
       <c r="F48" t="n">
-        <v>-31.609</v>
+        <v>-3.41</v>
       </c>
       <c r="G48" t="n">
-        <v>51.387</v>
+        <v>4.769</v>
       </c>
       <c r="H48" t="n">
-        <v>188.387</v>
+        <v>195.97</v>
       </c>
     </row>
     <row r="49">
@@ -1726,25 +1726,25 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>3075.103</v>
+        <v>3529.481</v>
       </c>
       <c r="C49" t="n">
-        <v>-21.996</v>
+        <v>-3.795</v>
       </c>
       <c r="D49" t="n">
-        <v>40.36</v>
+        <v>0.024</v>
       </c>
       <c r="E49" t="n">
-        <v>188.581</v>
+        <v>195.672</v>
       </c>
       <c r="F49" t="n">
-        <v>-31.622</v>
+        <v>-3.034</v>
       </c>
       <c r="G49" t="n">
-        <v>52.122</v>
+        <v>4.923</v>
       </c>
       <c r="H49" t="n">
-        <v>188.581</v>
+        <v>195.672</v>
       </c>
     </row>
     <row r="50">
@@ -1752,25 +1752,25 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>3154.731</v>
+        <v>3607.887</v>
       </c>
       <c r="C50" t="n">
-        <v>-18.211</v>
+        <v>-3.07</v>
       </c>
       <c r="D50" t="n">
-        <v>29.079</v>
+        <v>0.008</v>
       </c>
       <c r="E50" t="n">
-        <v>190.067</v>
+        <v>195.648</v>
       </c>
       <c r="F50" t="n">
-        <v>-28.611</v>
+        <v>-3.049</v>
       </c>
       <c r="G50" t="n">
-        <v>50.861</v>
+        <v>5.324</v>
       </c>
       <c r="H50" t="n">
-        <v>190.067</v>
+        <v>195.648</v>
       </c>
     </row>
     <row r="51">
@@ -1778,25 +1778,25 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>3234.624</v>
+        <v>3687.604</v>
       </c>
       <c r="C51" t="n">
-        <v>-14.414</v>
+        <v>-2.36</v>
       </c>
       <c r="D51" t="n">
-        <v>16.766</v>
+        <v>2.099</v>
       </c>
       <c r="E51" t="n">
-        <v>193.777</v>
+        <v>195.57</v>
       </c>
       <c r="F51" t="n">
-        <v>-27.671</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>41.773</v>
+        <v>2.54</v>
       </c>
       <c r="H51" t="n">
-        <v>193.777</v>
+        <v>195.57</v>
       </c>
     </row>
     <row r="52">
@@ -1804,25 +1804,25 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>3314.909</v>
+        <v>3767.237</v>
       </c>
       <c r="C52" t="n">
-        <v>-10.599</v>
+        <v>-0.855</v>
       </c>
       <c r="D52" t="n">
-        <v>4.188</v>
+        <v>6.528</v>
       </c>
       <c r="E52" t="n">
-        <v>197.311</v>
+        <v>195.429</v>
       </c>
       <c r="F52" t="n">
-        <v>-25.556</v>
+        <v>0.37</v>
       </c>
       <c r="G52" t="n">
-        <v>30.37</v>
+        <v>-3.112</v>
       </c>
       <c r="H52" t="n">
-        <v>197.311</v>
+        <v>195.429</v>
       </c>
     </row>
     <row r="53">
@@ -1830,25 +1830,25 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>3394.568</v>
+        <v>3847.552</v>
       </c>
       <c r="C53" t="n">
-        <v>-10.302</v>
+        <v>0.662</v>
       </c>
       <c r="D53" t="n">
-        <v>3.441</v>
+        <v>10.995</v>
       </c>
       <c r="E53" t="n">
-        <v>200.766</v>
+        <v>194.943</v>
       </c>
       <c r="F53" t="n">
-        <v>-17.946</v>
+        <v>0.661</v>
       </c>
       <c r="G53" t="n">
-        <v>14.764</v>
+        <v>-6.55</v>
       </c>
       <c r="H53" t="n">
-        <v>200.766</v>
+        <v>194.943</v>
       </c>
     </row>
     <row r="54">
@@ -1856,25 +1856,25 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>3475.168</v>
+        <v>3927.594</v>
       </c>
       <c r="C54" t="n">
-        <v>-9.763999999999999</v>
+        <v>2.173</v>
       </c>
       <c r="D54" t="n">
-        <v>2.091</v>
+        <v>15.447</v>
       </c>
       <c r="E54" t="n">
-        <v>201.273</v>
+        <v>194.622</v>
       </c>
       <c r="F54" t="n">
-        <v>-13.027</v>
+        <v>3.535</v>
       </c>
       <c r="G54" t="n">
-        <v>1.999</v>
+        <v>-4.291</v>
       </c>
       <c r="H54" t="n">
-        <v>201.273</v>
+        <v>194.622</v>
       </c>
     </row>
     <row r="55">
@@ -1882,25 +1882,25 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>3554.469</v>
+        <v>4000</v>
       </c>
       <c r="C55" t="n">
-        <v>-9.234999999999999</v>
+        <v>3.674</v>
       </c>
       <c r="D55" t="n">
-        <v>0.763</v>
+        <v>19.866</v>
       </c>
       <c r="E55" t="n">
-        <v>201.721</v>
+        <v>193.912</v>
       </c>
       <c r="F55" t="n">
-        <v>-10.224</v>
+        <v>3.391</v>
       </c>
       <c r="G55" t="n">
-        <v>-3.954</v>
+        <v>2.985</v>
       </c>
       <c r="H55" t="n">
-        <v>201.721</v>
+        <v>193.912</v>
       </c>
     </row>
     <row r="56">
@@ -1908,25 +1908,25 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>3637.033</v>
+        <v>4000</v>
       </c>
       <c r="C56" t="n">
-        <v>-8.58</v>
+        <v>5.2</v>
       </c>
       <c r="D56" t="n">
-        <v>0.669</v>
+        <v>24.358</v>
       </c>
       <c r="E56" t="n">
-        <v>201.2</v>
+        <v>191.297</v>
       </c>
       <c r="F56" t="n">
-        <v>-4.482</v>
+        <v>-17.166</v>
       </c>
       <c r="G56" t="n">
-        <v>-10.106</v>
+        <v>-46.817</v>
       </c>
       <c r="H56" t="n">
-        <v>201.2</v>
+        <v>191.297</v>
       </c>
     </row>
     <row r="57">
@@ -1934,25 +1934,25 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>3714.693</v>
+        <v>4000.055</v>
       </c>
       <c r="C57" t="n">
-        <v>-7.207</v>
+        <v>-11.545</v>
       </c>
       <c r="D57" t="n">
-        <v>0.471</v>
+        <v>-46.813</v>
       </c>
       <c r="E57" t="n">
-        <v>200.277</v>
+        <v>191.377</v>
       </c>
       <c r="F57" t="n">
-        <v>-4.241</v>
+        <v>-16.839</v>
       </c>
       <c r="G57" t="n">
-        <v>-12.995</v>
+        <v>-45.001</v>
       </c>
       <c r="H57" t="n">
-        <v>200.277</v>
+        <v>191.377</v>
       </c>
     </row>
     <row r="58">
@@ -1960,25 +1960,25 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>3794.743</v>
+        <v>4087.159</v>
       </c>
       <c r="C58" t="n">
-        <v>-5.792</v>
+        <v>-11.129</v>
       </c>
       <c r="D58" t="n">
-        <v>0.268</v>
+        <v>-38.609</v>
       </c>
       <c r="E58" t="n">
-        <v>199.388</v>
+        <v>191.278</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.57</v>
+        <v>-17.025</v>
       </c>
       <c r="G58" t="n">
-        <v>-13.212</v>
+        <v>-45.35</v>
       </c>
       <c r="H58" t="n">
-        <v>199.388</v>
+        <v>191.278</v>
       </c>
     </row>
     <row r="59">
@@ -1986,25 +1986,25 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>3875.021</v>
+        <v>4167.457</v>
       </c>
       <c r="C59" t="n">
-        <v>-4.373</v>
+        <v>-10.746</v>
       </c>
       <c r="D59" t="n">
-        <v>0.064</v>
+        <v>-32.972</v>
       </c>
       <c r="E59" t="n">
-        <v>198.233</v>
+        <v>190.68</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.797</v>
+        <v>-17.416</v>
       </c>
       <c r="G59" t="n">
-        <v>-7.117</v>
+        <v>-46.598</v>
       </c>
       <c r="H59" t="n">
-        <v>198.233</v>
+        <v>190.68</v>
       </c>
     </row>
     <row r="60">
@@ -2012,25 +2012,25 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>3954.932</v>
+        <v>4246.496</v>
       </c>
       <c r="C60" t="n">
-        <v>-2.461</v>
+        <v>-10.368</v>
       </c>
       <c r="D60" t="n">
-        <v>5.641</v>
+        <v>-27.865</v>
       </c>
       <c r="E60" t="n">
-        <v>197.73</v>
+        <v>190.899</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.347</v>
+        <v>-21.136</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.717</v>
+        <v>-44.488</v>
       </c>
       <c r="H60" t="n">
-        <v>197.73</v>
+        <v>190.899</v>
       </c>
     </row>
     <row r="61">
@@ -2038,25 +2038,25 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>4000</v>
+        <v>4328.986</v>
       </c>
       <c r="C61" t="n">
-        <v>0.313</v>
+        <v>-9.975</v>
       </c>
       <c r="D61" t="n">
-        <v>13.732</v>
+        <v>-20.643</v>
       </c>
       <c r="E61" t="n">
-        <v>196.581</v>
+        <v>193.416</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.011</v>
+        <v>-18.544</v>
       </c>
       <c r="G61" t="n">
-        <v>3.887</v>
+        <v>-37.14</v>
       </c>
       <c r="H61" t="n">
-        <v>196.581</v>
+        <v>193.416</v>
       </c>
     </row>
     <row r="62">
@@ -2064,25 +2064,25 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>4000</v>
+        <v>4406.544</v>
       </c>
       <c r="C62" t="n">
-        <v>3.103</v>
+        <v>-9.603999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>21.872</v>
+        <v>-12.652</v>
       </c>
       <c r="E62" t="n">
-        <v>189.754</v>
+        <v>194.713</v>
       </c>
       <c r="F62" t="n">
-        <v>-28.14</v>
+        <v>-16.481</v>
       </c>
       <c r="G62" t="n">
-        <v>-49.535</v>
+        <v>-30.622</v>
       </c>
       <c r="H62" t="n">
-        <v>189.754</v>
+        <v>194.713</v>
       </c>
     </row>
     <row r="63">
@@ -2090,25 +2090,25 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>4000.06</v>
+        <v>4486.618</v>
       </c>
       <c r="C63" t="n">
-        <v>-28.137</v>
+        <v>-9.222</v>
       </c>
       <c r="D63" t="n">
-        <v>-49.527</v>
+        <v>-6.598</v>
       </c>
       <c r="E63" t="n">
-        <v>189.235</v>
+        <v>196.264</v>
       </c>
       <c r="F63" t="n">
-        <v>-29.908</v>
+        <v>-14.587</v>
       </c>
       <c r="G63" t="n">
-        <v>-47.669</v>
+        <v>-21.145</v>
       </c>
       <c r="H63" t="n">
-        <v>189.235</v>
+        <v>196.264</v>
       </c>
     </row>
     <row r="64">
@@ -2116,25 +2116,25 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>4090.662</v>
+        <v>4566.354</v>
       </c>
       <c r="C64" t="n">
-        <v>-23.164</v>
+        <v>-8.842000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-35.58</v>
+        <v>-2.13</v>
       </c>
       <c r="E64" t="n">
-        <v>190.125</v>
+        <v>197.521</v>
       </c>
       <c r="F64" t="n">
-        <v>-29.71</v>
+        <v>-11.89</v>
       </c>
       <c r="G64" t="n">
-        <v>-47.86</v>
+        <v>-11.138</v>
       </c>
       <c r="H64" t="n">
-        <v>190.125</v>
+        <v>197.521</v>
       </c>
     </row>
     <row r="65">
@@ -2142,25 +2142,25 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>4169.612</v>
+        <v>4646.718</v>
       </c>
       <c r="C65" t="n">
-        <v>-18.831</v>
+        <v>-8.827</v>
       </c>
       <c r="D65" t="n">
-        <v>-25.151</v>
+        <v>-2.024</v>
       </c>
       <c r="E65" t="n">
-        <v>190.843</v>
+        <v>198.201</v>
       </c>
       <c r="F65" t="n">
-        <v>-30.109</v>
+        <v>-9.41</v>
       </c>
       <c r="G65" t="n">
-        <v>-46.145</v>
+        <v>-5.877</v>
       </c>
       <c r="H65" t="n">
-        <v>190.843</v>
+        <v>198.201</v>
       </c>
     </row>
     <row r="66">
@@ -2168,25 +2168,25 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>4249.617</v>
+        <v>4726.875</v>
       </c>
       <c r="C66" t="n">
-        <v>-14.44</v>
+        <v>-8.801</v>
       </c>
       <c r="D66" t="n">
-        <v>-13.948</v>
+        <v>-1.843</v>
       </c>
       <c r="E66" t="n">
-        <v>193.54</v>
+        <v>197.934</v>
       </c>
       <c r="F66" t="n">
-        <v>-28.643</v>
+        <v>-6.703</v>
       </c>
       <c r="G66" t="n">
-        <v>-37.608</v>
+        <v>-1.003</v>
       </c>
       <c r="H66" t="n">
-        <v>193.54</v>
+        <v>197.934</v>
       </c>
     </row>
     <row r="67">
@@ -2194,25 +2194,25 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>4330.255</v>
+        <v>4807.39</v>
       </c>
       <c r="C67" t="n">
-        <v>-10.015</v>
+        <v>-8.775</v>
       </c>
       <c r="D67" t="n">
-        <v>-3.065</v>
+        <v>-1.661</v>
       </c>
       <c r="E67" t="n">
-        <v>197.079</v>
+        <v>197.984</v>
       </c>
       <c r="F67" t="n">
-        <v>-23.632</v>
+        <v>-7.033</v>
       </c>
       <c r="G67" t="n">
-        <v>-25.848</v>
+        <v>-0.874</v>
       </c>
       <c r="H67" t="n">
-        <v>197.079</v>
+        <v>197.984</v>
       </c>
     </row>
     <row r="68">
@@ -2220,25 +2220,25 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>4409.593</v>
+        <v>4886.393</v>
       </c>
       <c r="C68" t="n">
-        <v>-9.757</v>
+        <v>-8.75</v>
       </c>
       <c r="D68" t="n">
-        <v>-2.573</v>
+        <v>-1.483</v>
       </c>
       <c r="E68" t="n">
-        <v>199.525</v>
+        <v>197.209</v>
       </c>
       <c r="F68" t="n">
-        <v>-18.998</v>
+        <v>-6.71</v>
       </c>
       <c r="G68" t="n">
-        <v>-13.251</v>
+        <v>4.188</v>
       </c>
       <c r="H68" t="n">
-        <v>199.525</v>
+        <v>197.209</v>
       </c>
     </row>
     <row r="69">
@@ -2246,25 +2246,25 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>4489.569</v>
+        <v>4966.626</v>
       </c>
       <c r="C69" t="n">
-        <v>-9.41</v>
+        <v>-8.724</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.912</v>
+        <v>-1.301</v>
       </c>
       <c r="E69" t="n">
-        <v>200.411</v>
+        <v>196.734</v>
       </c>
       <c r="F69" t="n">
-        <v>-14.077</v>
+        <v>-9.208</v>
       </c>
       <c r="G69" t="n">
-        <v>-5.688</v>
+        <v>3.542</v>
       </c>
       <c r="H69" t="n">
-        <v>200.411</v>
+        <v>196.734</v>
       </c>
     </row>
     <row r="70">
@@ -2272,25 +2272,25 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>4569.959</v>
+        <v>5048.919</v>
       </c>
       <c r="C70" t="n">
-        <v>-9.061</v>
+        <v>-8.696999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.248</v>
+        <v>-1.115</v>
       </c>
       <c r="E70" t="n">
-        <v>200.199</v>
+        <v>196.593</v>
       </c>
       <c r="F70" t="n">
-        <v>-9.231999999999999</v>
+        <v>-8.648</v>
       </c>
       <c r="G70" t="n">
-        <v>-3.584</v>
+        <v>3.837</v>
       </c>
       <c r="H70" t="n">
-        <v>200.199</v>
+        <v>196.593</v>
       </c>
     </row>
     <row r="71">
@@ -2298,25 +2298,25 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>4649.975</v>
+        <v>5126.786</v>
       </c>
       <c r="C71" t="n">
-        <v>-8.206</v>
+        <v>-8.452999999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.207</v>
+        <v>-1.109</v>
       </c>
       <c r="E71" t="n">
-        <v>199.673</v>
+        <v>196.442</v>
       </c>
       <c r="F71" t="n">
-        <v>-6.773</v>
+        <v>-8.317</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.857</v>
+        <v>4.127</v>
       </c>
       <c r="H71" t="n">
-        <v>199.673</v>
+        <v>196.442</v>
       </c>
     </row>
     <row r="72">
@@ -2324,25 +2324,25 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>4730.025</v>
+        <v>5206.657</v>
       </c>
       <c r="C72" t="n">
-        <v>-6.838</v>
+        <v>-7.724</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.141</v>
+        <v>-1.093</v>
       </c>
       <c r="E72" t="n">
-        <v>199.429</v>
+        <v>196.612</v>
       </c>
       <c r="F72" t="n">
-        <v>-5.938</v>
+        <v>-8.148999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>1.89</v>
+        <v>1.314</v>
       </c>
       <c r="H72" t="n">
-        <v>199.429</v>
+        <v>196.612</v>
       </c>
     </row>
     <row r="73">
@@ -2350,25 +2350,25 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>4809.884</v>
+        <v>5287.07</v>
       </c>
       <c r="C73" t="n">
-        <v>-5.472</v>
+        <v>-6.991</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.074</v>
+        <v>-1.076</v>
       </c>
       <c r="E73" t="n">
-        <v>199.154</v>
+        <v>196.38</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.695</v>
+        <v>-7.657</v>
       </c>
       <c r="G73" t="n">
-        <v>4.619</v>
+        <v>1.557</v>
       </c>
       <c r="H73" t="n">
-        <v>199.154</v>
+        <v>196.38</v>
       </c>
     </row>
     <row r="74">
@@ -2376,25 +2376,25 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>4889.91</v>
+        <v>5368.964</v>
       </c>
       <c r="C74" t="n">
-        <v>-4.104</v>
+        <v>-6.244</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.008</v>
+        <v>-1.059</v>
       </c>
       <c r="E74" t="n">
-        <v>197.915</v>
+        <v>196.199</v>
       </c>
       <c r="F74" t="n">
-        <v>-2.275</v>
+        <v>-7.58</v>
       </c>
       <c r="G74" t="n">
-        <v>6.737</v>
+        <v>-1.416</v>
       </c>
       <c r="H74" t="n">
-        <v>197.915</v>
+        <v>196.199</v>
       </c>
     </row>
     <row r="75">
@@ -2402,25 +2402,25 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>4970.172</v>
+        <v>5449.131</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.724</v>
+        <v>-5.513</v>
       </c>
       <c r="D75" t="n">
-        <v>-9.082000000000001</v>
+        <v>-1.042</v>
       </c>
       <c r="E75" t="n">
-        <v>197.001</v>
+        <v>195.984</v>
       </c>
       <c r="F75" t="n">
-        <v>1.172</v>
+        <v>-7.361</v>
       </c>
       <c r="G75" t="n">
-        <v>7.362</v>
+        <v>-1.527</v>
       </c>
       <c r="H75" t="n">
-        <v>197.001</v>
+        <v>195.984</v>
       </c>
     </row>
     <row r="76">
@@ -2428,25 +2428,25 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>5000</v>
+        <v>5527.03</v>
       </c>
       <c r="C76" t="n">
-        <v>0.969</v>
+        <v>-4.802</v>
       </c>
       <c r="D76" t="n">
-        <v>-18.219</v>
+        <v>-1.026</v>
       </c>
       <c r="E76" t="n">
-        <v>194.253</v>
+        <v>195.793</v>
       </c>
       <c r="F76" t="n">
-        <v>1.219</v>
+        <v>-4.616</v>
       </c>
       <c r="G76" t="n">
-        <v>6.217</v>
+        <v>-4.485</v>
       </c>
       <c r="H76" t="n">
-        <v>194.253</v>
+        <v>195.793</v>
       </c>
     </row>
     <row r="77">
@@ -2454,25 +2454,25 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>5000</v>
+        <v>5606.726000000001</v>
       </c>
       <c r="C77" t="n">
-        <v>3.681</v>
+        <v>-4.076</v>
       </c>
       <c r="D77" t="n">
-        <v>-27.42</v>
+        <v>-1.009</v>
       </c>
       <c r="E77" t="n">
-        <v>190.662</v>
+        <v>195.559</v>
       </c>
       <c r="F77" t="n">
-        <v>-22.363</v>
+        <v>-4.593</v>
       </c>
       <c r="G77" t="n">
-        <v>53.594</v>
+        <v>-4.599</v>
       </c>
       <c r="H77" t="n">
-        <v>190.662</v>
+        <v>195.559</v>
       </c>
     </row>
     <row r="78">
@@ -2480,25 +2480,25 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>5000.094</v>
+        <v>5686.603</v>
       </c>
       <c r="C78" t="n">
-        <v>-19.523</v>
+        <v>-3.384</v>
       </c>
       <c r="D78" t="n">
-        <v>53.58</v>
+        <v>-3.311</v>
       </c>
       <c r="E78" t="n">
-        <v>190.068</v>
+        <v>195.366</v>
       </c>
       <c r="F78" t="n">
-        <v>-22.778</v>
+        <v>-4.337</v>
       </c>
       <c r="G78" t="n">
-        <v>51.594</v>
+        <v>-4.695</v>
       </c>
       <c r="H78" t="n">
-        <v>190.068</v>
+        <v>195.366</v>
       </c>
     </row>
     <row r="79">
@@ -2506,25 +2506,25 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>5088.239</v>
+        <v>5767.15</v>
       </c>
       <c r="C79" t="n">
-        <v>-16.855</v>
+        <v>-1.862</v>
       </c>
       <c r="D79" t="n">
-        <v>38.587</v>
+        <v>-8.375999999999999</v>
       </c>
       <c r="E79" t="n">
-        <v>189.125</v>
+        <v>195.319</v>
       </c>
       <c r="F79" t="n">
-        <v>-23.155</v>
+        <v>1.197</v>
       </c>
       <c r="G79" t="n">
-        <v>55.419</v>
+        <v>-4.719</v>
       </c>
       <c r="H79" t="n">
-        <v>189.125</v>
+        <v>195.319</v>
       </c>
     </row>
     <row r="80">
@@ -2532,25 +2532,25 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>5168.591</v>
+        <v>5846.507</v>
       </c>
       <c r="C80" t="n">
-        <v>-14.423</v>
+        <v>-0.362</v>
       </c>
       <c r="D80" t="n">
-        <v>28.724</v>
+        <v>-13.367</v>
       </c>
       <c r="E80" t="n">
-        <v>191.244</v>
+        <v>194.951</v>
       </c>
       <c r="F80" t="n">
-        <v>-24.149</v>
+        <v>1.133</v>
       </c>
       <c r="G80" t="n">
-        <v>50.713</v>
+        <v>-4.116</v>
       </c>
       <c r="H80" t="n">
-        <v>191.244</v>
+        <v>194.951</v>
       </c>
     </row>
     <row r="81">
@@ -2558,25 +2558,25 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>5248.218</v>
+        <v>5926.635</v>
       </c>
       <c r="C81" t="n">
-        <v>-12.012</v>
+        <v>1.152</v>
       </c>
       <c r="D81" t="n">
-        <v>14.748</v>
+        <v>-18.406</v>
       </c>
       <c r="E81" t="n">
-        <v>193.865</v>
+        <v>194.436</v>
       </c>
       <c r="F81" t="n">
-        <v>-25.338</v>
+        <v>7.115</v>
       </c>
       <c r="G81" t="n">
-        <v>42.102</v>
+        <v>-3.533</v>
       </c>
       <c r="H81" t="n">
-        <v>193.865</v>
+        <v>194.436</v>
       </c>
     </row>
     <row r="82">
@@ -2584,25 +2584,25 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>5328.399</v>
+        <v>6000</v>
       </c>
       <c r="C82" t="n">
-        <v>-9.585000000000001</v>
+        <v>2.672</v>
       </c>
       <c r="D82" t="n">
-        <v>2.598</v>
+        <v>-23.462</v>
       </c>
       <c r="E82" t="n">
-        <v>198.28</v>
+        <v>193.97</v>
       </c>
       <c r="F82" t="n">
-        <v>-20.071</v>
+        <v>6.584</v>
       </c>
       <c r="G82" t="n">
-        <v>27.729</v>
+        <v>-5.74</v>
       </c>
       <c r="H82" t="n">
-        <v>198.28</v>
+        <v>193.97</v>
       </c>
     </row>
     <row r="83">
@@ -2610,25 +2610,25 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>5408.492</v>
+        <v>6000</v>
       </c>
       <c r="C83" t="n">
-        <v>-9.432</v>
+        <v>4.181</v>
       </c>
       <c r="D83" t="n">
-        <v>1.99</v>
+        <v>-28.484</v>
       </c>
       <c r="E83" t="n">
-        <v>200.904</v>
+        <v>189.922</v>
       </c>
       <c r="F83" t="n">
-        <v>-15.051</v>
+        <v>-25.893</v>
       </c>
       <c r="G83" t="n">
-        <v>12.117</v>
+        <v>49.582</v>
       </c>
       <c r="H83" t="n">
-        <v>200.904</v>
+        <v>189.922</v>
       </c>
     </row>
     <row r="84">
@@ -2636,25 +2636,25 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>5488.663</v>
+        <v>6000.056</v>
       </c>
       <c r="C84" t="n">
-        <v>-9.222</v>
+        <v>-20.252</v>
       </c>
       <c r="D84" t="n">
-        <v>1.157</v>
+        <v>49.577</v>
       </c>
       <c r="E84" t="n">
-        <v>201.406</v>
+        <v>189.358</v>
       </c>
       <c r="F84" t="n">
-        <v>-9.542</v>
+        <v>-27.523</v>
       </c>
       <c r="G84" t="n">
-        <v>2.214</v>
+        <v>48.077</v>
       </c>
       <c r="H84" t="n">
-        <v>201.406</v>
+        <v>189.358</v>
       </c>
     </row>
     <row r="85">
@@ -2662,25 +2662,25 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>5568.163</v>
+        <v>6083.122</v>
       </c>
       <c r="C85" t="n">
-        <v>-9.013999999999999</v>
+        <v>-18.511</v>
       </c>
       <c r="D85" t="n">
-        <v>0.331</v>
+        <v>41.417</v>
       </c>
       <c r="E85" t="n">
-        <v>201.388</v>
+        <v>189.338</v>
       </c>
       <c r="F85" t="n">
-        <v>-3.995</v>
+        <v>-27.878</v>
       </c>
       <c r="G85" t="n">
-        <v>-3.508</v>
+        <v>48.43</v>
       </c>
       <c r="H85" t="n">
-        <v>201.388</v>
+        <v>189.338</v>
       </c>
     </row>
     <row r="86">
@@ -2688,25 +2688,25 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>5648.517</v>
+        <v>6163.108</v>
       </c>
       <c r="C86" t="n">
-        <v>-8.192</v>
+        <v>-16.835</v>
       </c>
       <c r="D86" t="n">
-        <v>0.277</v>
+        <v>35.264</v>
       </c>
       <c r="E86" t="n">
-        <v>200.651</v>
+        <v>189.681</v>
       </c>
       <c r="F86" t="n">
-        <v>-3.634</v>
+        <v>-25.258</v>
       </c>
       <c r="G86" t="n">
-        <v>-9.561</v>
+        <v>48.818</v>
       </c>
       <c r="H86" t="n">
-        <v>200.651</v>
+        <v>189.681</v>
       </c>
     </row>
     <row r="87">
@@ -2714,25 +2714,25 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>5728.804</v>
+        <v>6242.974</v>
       </c>
       <c r="C87" t="n">
-        <v>-6.832</v>
+        <v>-15.162</v>
       </c>
       <c r="D87" t="n">
-        <v>0.189</v>
+        <v>29.049</v>
       </c>
       <c r="E87" t="n">
-        <v>200.017</v>
+        <v>191.702</v>
       </c>
       <c r="F87" t="n">
-        <v>0.037</v>
+        <v>-23.014</v>
       </c>
       <c r="G87" t="n">
-        <v>-12.552</v>
+        <v>43.996</v>
       </c>
       <c r="H87" t="n">
-        <v>200.017</v>
+        <v>191.702</v>
       </c>
     </row>
     <row r="88">
@@ -2740,25 +2740,25 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>5808.586</v>
+        <v>6324.323</v>
       </c>
       <c r="C88" t="n">
-        <v>-5.48</v>
+        <v>-13.457</v>
       </c>
       <c r="D88" t="n">
-        <v>0.101</v>
+        <v>20.214</v>
       </c>
       <c r="E88" t="n">
-        <v>199.241</v>
+        <v>192.781</v>
       </c>
       <c r="F88" t="n">
-        <v>0.965</v>
+        <v>-21.36</v>
       </c>
       <c r="G88" t="n">
-        <v>-12.768</v>
+        <v>40.351</v>
       </c>
       <c r="H88" t="n">
-        <v>199.241</v>
+        <v>192.781</v>
       </c>
     </row>
     <row r="89">
@@ -2766,25 +2766,25 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>5888.638</v>
+        <v>6403.074</v>
       </c>
       <c r="C89" t="n">
-        <v>-4.124</v>
+        <v>-11.807</v>
       </c>
       <c r="D89" t="n">
-        <v>0.013</v>
+        <v>13.244</v>
       </c>
       <c r="E89" t="n">
-        <v>197.977</v>
+        <v>194.845</v>
       </c>
       <c r="F89" t="n">
-        <v>1.161</v>
+        <v>-19.298</v>
       </c>
       <c r="G89" t="n">
-        <v>-9.279</v>
+        <v>31</v>
       </c>
       <c r="H89" t="n">
-        <v>197.977</v>
+        <v>194.845</v>
       </c>
     </row>
     <row r="90">
@@ -2792,25 +2792,25 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>5968.467</v>
+        <v>6482.916</v>
       </c>
       <c r="C90" t="n">
-        <v>-1.798</v>
+        <v>-10.134</v>
       </c>
       <c r="D90" t="n">
-        <v>6.976</v>
+        <v>6.049</v>
       </c>
       <c r="E90" t="n">
-        <v>197.484</v>
+        <v>197.602</v>
       </c>
       <c r="F90" t="n">
-        <v>1.803</v>
+        <v>-11.991</v>
       </c>
       <c r="G90" t="n">
-        <v>-4.234</v>
+        <v>20.782</v>
       </c>
       <c r="H90" t="n">
-        <v>197.484</v>
+        <v>197.602</v>
       </c>
     </row>
     <row r="91">
@@ -2818,25 +2818,25 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>6000</v>
+        <v>6562.919</v>
       </c>
       <c r="C91" t="n">
-        <v>0.925</v>
+        <v>-8.458</v>
       </c>
       <c r="D91" t="n">
-        <v>15.126</v>
+        <v>1.284</v>
       </c>
       <c r="E91" t="n">
-        <v>196.415</v>
+        <v>197.641</v>
       </c>
       <c r="F91" t="n">
-        <v>3.099</v>
+        <v>-9.847</v>
       </c>
       <c r="G91" t="n">
-        <v>1.048</v>
+        <v>14.364</v>
       </c>
       <c r="H91" t="n">
-        <v>196.415</v>
+        <v>197.641</v>
       </c>
     </row>
     <row r="92">
@@ -2844,25 +2844,4731 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>6000</v>
+        <v>6642.993</v>
       </c>
       <c r="C92" t="n">
-        <v>3.645</v>
+        <v>-8.391</v>
       </c>
       <c r="D92" t="n">
-        <v>23.269</v>
+        <v>1.174</v>
       </c>
       <c r="E92" t="n">
-        <v>193.734</v>
+        <v>198.661</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.497</v>
+        <v>-10.313</v>
       </c>
       <c r="G92" t="n">
-        <v>28.286</v>
+        <v>6.466</v>
       </c>
       <c r="H92" t="n">
-        <v>193.734</v>
+        <v>198.661</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>6724.769</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-8.263999999999999</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="E93" t="n">
+        <v>199.031</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-7.608</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="H93" t="n">
+        <v>199.031</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>6803.087</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-8.141999999999999</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="E94" t="n">
+        <v>197.264</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-9.797000000000001</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H94" t="n">
+        <v>197.264</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>6883.106</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-8.018000000000001</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="E95" t="n">
+        <v>196.814</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-9.297000000000001</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="H95" t="n">
+        <v>196.814</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>6963.119</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-7.894</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="E96" t="n">
+        <v>196.888</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-9.009</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-5.203</v>
+      </c>
+      <c r="H96" t="n">
+        <v>196.888</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>7047.326</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-7.763</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="E97" t="n">
+        <v>196.665</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-8.984</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-5.143</v>
+      </c>
+      <c r="H97" t="n">
+        <v>196.665</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>7123.267</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-7.548</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="E98" t="n">
+        <v>196.42</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-8.335000000000001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>196.42</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>7203.135</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E99" t="n">
+        <v>195.715</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-9.452</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-8.428000000000001</v>
+      </c>
+      <c r="H99" t="n">
+        <v>195.715</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>7283.008</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-6.072</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E100" t="n">
+        <v>196.289</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-9.518000000000001</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-6.619</v>
+      </c>
+      <c r="H100" t="n">
+        <v>196.289</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>7363.178</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-5.331</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E101" t="n">
+        <v>195.438</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-6.309</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-6.06</v>
+      </c>
+      <c r="H101" t="n">
+        <v>195.438</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>7443.300999999999</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-4.591</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="E102" t="n">
+        <v>195.171</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-6.101</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-0.513</v>
+      </c>
+      <c r="H102" t="n">
+        <v>195.171</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>7523.226000000001</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-3.852</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="E103" t="n">
+        <v>194.716</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-4.017</v>
+      </c>
+      <c r="G103" t="n">
+        <v>5.332</v>
+      </c>
+      <c r="H103" t="n">
+        <v>194.716</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>7607.442</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-3.074</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E104" t="n">
+        <v>194.375</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-1.284</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.284000000000001</v>
+      </c>
+      <c r="H104" t="n">
+        <v>194.375</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>7684.6</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1.934</v>
+      </c>
+      <c r="E105" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-1.551</v>
+      </c>
+      <c r="G105" t="n">
+        <v>8.734999999999999</v>
+      </c>
+      <c r="H105" t="n">
+        <v>194.1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>7763.172</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.9350000000000001</v>
+      </c>
+      <c r="D106" t="n">
+        <v>6.304</v>
+      </c>
+      <c r="E106" t="n">
+        <v>193.955</v>
+      </c>
+      <c r="F106" t="n">
+        <v>7.041</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3.183</v>
+      </c>
+      <c r="H106" t="n">
+        <v>193.955</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>7843.123</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="D107" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="E107" t="n">
+        <v>193.978</v>
+      </c>
+      <c r="F107" t="n">
+        <v>7.817</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H107" t="n">
+        <v>193.978</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>7923.195</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2.088</v>
+      </c>
+      <c r="D108" t="n">
+        <v>15.203</v>
+      </c>
+      <c r="E108" t="n">
+        <v>193.598</v>
+      </c>
+      <c r="F108" t="n">
+        <v>7.824</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H108" t="n">
+        <v>193.598</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3.604</v>
+      </c>
+      <c r="D109" t="n">
+        <v>19.663</v>
+      </c>
+      <c r="E109" t="n">
+        <v>193.162</v>
+      </c>
+      <c r="F109" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-1.216</v>
+      </c>
+      <c r="H109" t="n">
+        <v>193.162</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C110" t="n">
+        <v>5.108</v>
+      </c>
+      <c r="D110" t="n">
+        <v>24.089</v>
+      </c>
+      <c r="E110" t="n">
+        <v>189.647</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-22.838</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-51.784</v>
+      </c>
+      <c r="H110" t="n">
+        <v>189.647</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>8000.056</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-20.011</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-51.779</v>
+      </c>
+      <c r="E111" t="n">
+        <v>189.757</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-22.836</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-49.61</v>
+      </c>
+      <c r="H111" t="n">
+        <v>189.757</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>8089.264</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-18.326</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-42.378</v>
+      </c>
+      <c r="E112" t="n">
+        <v>189.644</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-23.021</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-49.955</v>
+      </c>
+      <c r="H112" t="n">
+        <v>189.644</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>8168.916</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-16.822</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-36.173</v>
+      </c>
+      <c r="E113" t="n">
+        <v>189.665</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-23.404</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-50.666</v>
+      </c>
+      <c r="H113" t="n">
+        <v>189.665</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>8248.841</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-15.313</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-30.068</v>
+      </c>
+      <c r="E114" t="n">
+        <v>191.318</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-23.617</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-45.821</v>
+      </c>
+      <c r="H114" t="n">
+        <v>191.318</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>8329.098</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-13.797</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-21.237</v>
+      </c>
+      <c r="E115" t="n">
+        <v>193.331</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-18.898</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-41.282</v>
+      </c>
+      <c r="H115" t="n">
+        <v>193.331</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>8408.639999999999</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-12.295</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-13.847</v>
+      </c>
+      <c r="E116" t="n">
+        <v>195.507</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-17.216</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-31.884</v>
+      </c>
+      <c r="H116" t="n">
+        <v>195.507</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>8489.584999999999</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-10.766</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-6.683</v>
+      </c>
+      <c r="E117" t="n">
+        <v>197.425</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-14.609</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-22.33</v>
+      </c>
+      <c r="H117" t="n">
+        <v>197.425</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>8569.263999999999</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-9.260999999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-2.093</v>
+      </c>
+      <c r="E118" t="n">
+        <v>198.497</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-12.053</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-12.686</v>
+      </c>
+      <c r="H118" t="n">
+        <v>198.497</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>8648.761</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-9.204000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-1.986</v>
+      </c>
+      <c r="E119" t="n">
+        <v>199.267</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-12.552</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-4.434</v>
+      </c>
+      <c r="H119" t="n">
+        <v>199.267</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>8728.889999999999</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-9.111000000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-1.811</v>
+      </c>
+      <c r="E120" t="n">
+        <v>198.88</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-12.665</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-2.459</v>
+      </c>
+      <c r="H120" t="n">
+        <v>198.88</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>8808.859</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-9.019</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-1.636</v>
+      </c>
+      <c r="E121" t="n">
+        <v>198.472</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-10.169</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-0.146</v>
+      </c>
+      <c r="H121" t="n">
+        <v>198.472</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>8888.982</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-8.926</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-1.461</v>
+      </c>
+      <c r="E122" t="n">
+        <v>198.182</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-13.024</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="H122" t="n">
+        <v>198.182</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>8968.985000000001</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-8.833</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-1.286</v>
+      </c>
+      <c r="E123" t="n">
+        <v>198.179</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-12.59</v>
+      </c>
+      <c r="G123" t="n">
+        <v>5.713</v>
+      </c>
+      <c r="H123" t="n">
+        <v>198.179</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>9048.599</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-8.741</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-1.112</v>
+      </c>
+      <c r="E124" t="n">
+        <v>198.154</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-12.542</v>
+      </c>
+      <c r="G124" t="n">
+        <v>6.096</v>
+      </c>
+      <c r="H124" t="n">
+        <v>198.154</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>9128.739</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-8.477</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-1.106</v>
+      </c>
+      <c r="E125" t="n">
+        <v>197.266</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-12.139</v>
+      </c>
+      <c r="G125" t="n">
+        <v>8.468</v>
+      </c>
+      <c r="H125" t="n">
+        <v>197.266</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>9209.130000000001</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-7.737</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="E126" t="n">
+        <v>197.38</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-9.025</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5.902</v>
+      </c>
+      <c r="H126" t="n">
+        <v>197.38</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>9288.627</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-7.006</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-1.074</v>
+      </c>
+      <c r="E127" t="n">
+        <v>196.62</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-6.782</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="H127" t="n">
+        <v>196.62</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>9369.194</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-6.264</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-1.057</v>
+      </c>
+      <c r="E128" t="n">
+        <v>195.682</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-6.329</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-0.885</v>
+      </c>
+      <c r="H128" t="n">
+        <v>195.682</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>9448.893</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-5.531</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-1.041</v>
+      </c>
+      <c r="E129" t="n">
+        <v>195.214</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-3.883</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-3.904</v>
+      </c>
+      <c r="H129" t="n">
+        <v>195.214</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>9531.205</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-4.774</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-1.024</v>
+      </c>
+      <c r="E130" t="n">
+        <v>194.867</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-1.137</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-6.873</v>
+      </c>
+      <c r="H130" t="n">
+        <v>194.867</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>9608.949000000001</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-4.059</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-1.008</v>
+      </c>
+      <c r="E131" t="n">
+        <v>194.378</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-1.277</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-10.191</v>
+      </c>
+      <c r="H131" t="n">
+        <v>194.378</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>9688.654</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-3.439</v>
+      </c>
+      <c r="E132" t="n">
+        <v>194.197</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.673</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-10.263</v>
+      </c>
+      <c r="H132" t="n">
+        <v>194.197</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>9769.241</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.809</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-8.507</v>
+      </c>
+      <c r="E133" t="n">
+        <v>194.335</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4.828</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-7.798</v>
+      </c>
+      <c r="H133" t="n">
+        <v>194.335</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>9848.602999999999</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.312</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-13.498</v>
+      </c>
+      <c r="E134" t="n">
+        <v>194.323</v>
+      </c>
+      <c r="F134" t="n">
+        <v>8.339</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="H134" t="n">
+        <v>194.323</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>9929.103999999999</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-18.561</v>
+      </c>
+      <c r="E135" t="n">
+        <v>193.903</v>
+      </c>
+      <c r="F135" t="n">
+        <v>7.955</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-1.199</v>
+      </c>
+      <c r="H135" t="n">
+        <v>193.903</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C136" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-23.57</v>
+      </c>
+      <c r="E136" t="n">
+        <v>193.493</v>
+      </c>
+      <c r="F136" t="n">
+        <v>8.831</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-0.223</v>
+      </c>
+      <c r="H136" t="n">
+        <v>193.493</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C137" t="n">
+        <v>4.228</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-28.629</v>
+      </c>
+      <c r="E137" t="n">
+        <v>189.753</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-28.14</v>
+      </c>
+      <c r="G137" t="n">
+        <v>49.577</v>
+      </c>
+      <c r="H137" t="n">
+        <v>189.753</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>10000.119</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-22.512</v>
+      </c>
+      <c r="D138" t="n">
+        <v>49.567</v>
+      </c>
+      <c r="E138" t="n">
+        <v>188.589</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-29.887</v>
+      </c>
+      <c r="G138" t="n">
+        <v>48.238</v>
+      </c>
+      <c r="H138" t="n">
+        <v>188.589</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>10089.002</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-20.315</v>
+      </c>
+      <c r="D139" t="n">
+        <v>41.083</v>
+      </c>
+      <c r="E139" t="n">
+        <v>189.593</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-27.289</v>
+      </c>
+      <c r="G139" t="n">
+        <v>48.098</v>
+      </c>
+      <c r="H139" t="n">
+        <v>189.593</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>10168.46</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-18.35</v>
+      </c>
+      <c r="D140" t="n">
+        <v>34.594</v>
+      </c>
+      <c r="E140" t="n">
+        <v>189.603</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-27.884</v>
+      </c>
+      <c r="G140" t="n">
+        <v>48.807</v>
+      </c>
+      <c r="H140" t="n">
+        <v>189.603</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" t="n">
+        <v>10247.941</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-16.385</v>
+      </c>
+      <c r="D141" t="n">
+        <v>28.638</v>
+      </c>
+      <c r="E141" t="n">
+        <v>190.359</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-28.07</v>
+      </c>
+      <c r="G141" t="n">
+        <v>46.748</v>
+      </c>
+      <c r="H141" t="n">
+        <v>190.359</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="n">
+        <v>10327.994</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-14.406</v>
+      </c>
+      <c r="D142" t="n">
+        <v>21.193</v>
+      </c>
+      <c r="E142" t="n">
+        <v>192.656</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-23.581</v>
+      </c>
+      <c r="G142" t="n">
+        <v>40.356</v>
+      </c>
+      <c r="H142" t="n">
+        <v>192.656</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="n">
+        <v>10407.946</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-12.429</v>
+      </c>
+      <c r="D143" t="n">
+        <v>12.918</v>
+      </c>
+      <c r="E143" t="n">
+        <v>194.863</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-22.115</v>
+      </c>
+      <c r="G143" t="n">
+        <v>30.989</v>
+      </c>
+      <c r="H143" t="n">
+        <v>194.863</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="n">
+        <v>10492.438</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-10.34</v>
+      </c>
+      <c r="D144" t="n">
+        <v>5.555</v>
+      </c>
+      <c r="E144" t="n">
+        <v>197.173</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-15.383</v>
+      </c>
+      <c r="G144" t="n">
+        <v>18.547</v>
+      </c>
+      <c r="H144" t="n">
+        <v>197.173</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="n">
+        <v>10567.959</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-8.473000000000001</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E145" t="n">
+        <v>197.928</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-13.203</v>
+      </c>
+      <c r="G145" t="n">
+        <v>11.773</v>
+      </c>
+      <c r="H145" t="n">
+        <v>197.928</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="n">
+        <v>10650.35</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-8.393000000000001</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E146" t="n">
+        <v>198.802</v>
+      </c>
+      <c r="F146" t="n">
+        <v>-10.873</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3.516</v>
+      </c>
+      <c r="H146" t="n">
+        <v>198.802</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="n">
+        <v>10728.438</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="E147" t="n">
+        <v>198.279</v>
+      </c>
+      <c r="F147" t="n">
+        <v>-10.94</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="H147" t="n">
+        <v>198.279</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="n">
+        <v>10808.557</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-8.143000000000001</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="E148" t="n">
+        <v>197.196</v>
+      </c>
+      <c r="F148" t="n">
+        <v>-8.465999999999999</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H148" t="n">
+        <v>197.196</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="n">
+        <v>10888.001</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-8.016999999999999</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E149" t="n">
+        <v>196.792</v>
+      </c>
+      <c r="F149" t="n">
+        <v>-8.08</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="H149" t="n">
+        <v>196.792</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="n">
+        <v>10967.851</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="E150" t="n">
+        <v>196.531</v>
+      </c>
+      <c r="F150" t="n">
+        <v>-8.145</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="H150" t="n">
+        <v>196.531</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="n">
+        <v>11048.247</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-7.763</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="E151" t="n">
+        <v>196.752</v>
+      </c>
+      <c r="F151" t="n">
+        <v>-5.006</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H151" t="n">
+        <v>196.752</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="n">
+        <v>11133.327</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-7.455</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="E152" t="n">
+        <v>196.509</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-4.984</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="H152" t="n">
+        <v>196.509</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" t="n">
+        <v>11225.287</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-6.605</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E153" t="n">
+        <v>196.45</v>
+      </c>
+      <c r="F153" t="n">
+        <v>-4.298</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="H153" t="n">
+        <v>196.45</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" t="n">
+        <v>11304.48</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-5.874</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="E154" t="n">
+        <v>196.434</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-4.197</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="H154" t="n">
+        <v>196.434</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="n">
+        <v>11383.588</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-5.143</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="E155" t="n">
+        <v>196.223</v>
+      </c>
+      <c r="F155" t="n">
+        <v>-1.035</v>
+      </c>
+      <c r="G155" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="H155" t="n">
+        <v>196.223</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="n">
+        <v>11463.579</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-4.404</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E156" t="n">
+        <v>195.955</v>
+      </c>
+      <c r="F156" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G156" t="n">
+        <v>-4.776</v>
+      </c>
+      <c r="H156" t="n">
+        <v>195.955</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="n">
+        <v>11543.843</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-3.662</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E157" t="n">
+        <v>195.725</v>
+      </c>
+      <c r="F157" t="n">
+        <v>-0.152</v>
+      </c>
+      <c r="G157" t="n">
+        <v>-4.621</v>
+      </c>
+      <c r="H157" t="n">
+        <v>195.725</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="n">
+        <v>11624.828</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-2.914</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E158" t="n">
+        <v>195.368</v>
+      </c>
+      <c r="F158" t="n">
+        <v>-0.167</v>
+      </c>
+      <c r="G158" t="n">
+        <v>-4.798</v>
+      </c>
+      <c r="H158" t="n">
+        <v>195.368</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="n">
+        <v>11706.752</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.858</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3.162</v>
+      </c>
+      <c r="E159" t="n">
+        <v>195.014</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="G159" t="n">
+        <v>-4.986</v>
+      </c>
+      <c r="H159" t="n">
+        <v>195.014</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="n">
+        <v>11783.597</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.428</v>
+      </c>
+      <c r="D160" t="n">
+        <v>7.436</v>
+      </c>
+      <c r="E160" t="n">
+        <v>194.603</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="G160" t="n">
+        <v>-5.559</v>
+      </c>
+      <c r="H160" t="n">
+        <v>194.603</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="n">
+        <v>11866.879</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="D161" t="n">
+        <v>12.068</v>
+      </c>
+      <c r="E161" t="n">
+        <v>194.322</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="G161" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="H161" t="n">
+        <v>194.322</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="n">
+        <v>11943.617</v>
+      </c>
+      <c r="C162" t="n">
+        <v>2.549</v>
+      </c>
+      <c r="D162" t="n">
+        <v>16.337</v>
+      </c>
+      <c r="E162" t="n">
+        <v>193.93</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1.393</v>
+      </c>
+      <c r="H162" t="n">
+        <v>193.93</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C163" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D163" t="n">
+        <v>20.875</v>
+      </c>
+      <c r="E163" t="n">
+        <v>193.248</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="G163" t="n">
+        <v>8.907999999999999</v>
+      </c>
+      <c r="H163" t="n">
+        <v>193.248</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C164" t="n">
+        <v>5.528</v>
+      </c>
+      <c r="D164" t="n">
+        <v>25.242</v>
+      </c>
+      <c r="E164" t="n">
+        <v>191.199</v>
+      </c>
+      <c r="F164" t="n">
+        <v>-15.545</v>
+      </c>
+      <c r="G164" t="n">
+        <v>-47.38</v>
+      </c>
+      <c r="H164" t="n">
+        <v>191.199</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="n">
+        <v>12000.057</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-9.895</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-47.376</v>
+      </c>
+      <c r="E165" t="n">
+        <v>190.731</v>
+      </c>
+      <c r="F165" t="n">
+        <v>-16.283</v>
+      </c>
+      <c r="G165" t="n">
+        <v>-45.892</v>
+      </c>
+      <c r="H165" t="n">
+        <v>190.731</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" t="n">
+        <v>12087.089</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-9.718999999999999</v>
+      </c>
+      <c r="D166" t="n">
+        <v>-39.376</v>
+      </c>
+      <c r="E166" t="n">
+        <v>190.392</v>
+      </c>
+      <c r="F166" t="n">
+        <v>-19.303</v>
+      </c>
+      <c r="G166" t="n">
+        <v>-46.223</v>
+      </c>
+      <c r="H166" t="n">
+        <v>190.392</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" t="n">
+        <v>12166.335</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-9.558</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-33.686</v>
+      </c>
+      <c r="E167" t="n">
+        <v>190.312</v>
+      </c>
+      <c r="F167" t="n">
+        <v>-19.277</v>
+      </c>
+      <c r="G167" t="n">
+        <v>-46.93</v>
+      </c>
+      <c r="H167" t="n">
+        <v>190.312</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="n">
+        <v>12246.189</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-9.397</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-28.084</v>
+      </c>
+      <c r="E168" t="n">
+        <v>192.547</v>
+      </c>
+      <c r="F168" t="n">
+        <v>-19.843</v>
+      </c>
+      <c r="G168" t="n">
+        <v>-38.907</v>
+      </c>
+      <c r="H168" t="n">
+        <v>192.547</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="n">
+        <v>12326.478</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-9.234</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-18.281</v>
+      </c>
+      <c r="E169" t="n">
+        <v>193.768</v>
+      </c>
+      <c r="F169" t="n">
+        <v>-20.783</v>
+      </c>
+      <c r="G169" t="n">
+        <v>-34.665</v>
+      </c>
+      <c r="H169" t="n">
+        <v>193.768</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="n">
+        <v>12406.506</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-9.073</v>
+      </c>
+      <c r="D170" t="n">
+        <v>-11.857</v>
+      </c>
+      <c r="E170" t="n">
+        <v>195.214</v>
+      </c>
+      <c r="F170" t="n">
+        <v>-18.162</v>
+      </c>
+      <c r="G170" t="n">
+        <v>-27.772</v>
+      </c>
+      <c r="H170" t="n">
+        <v>195.214</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="n">
+        <v>12486.177</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-8.911</v>
+      </c>
+      <c r="D171" t="n">
+        <v>-6.079</v>
+      </c>
+      <c r="E171" t="n">
+        <v>195.562</v>
+      </c>
+      <c r="F171" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="G171" t="n">
+        <v>-21.429</v>
+      </c>
+      <c r="H171" t="n">
+        <v>195.562</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="n">
+        <v>12566.206</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-8.749000000000001</v>
+      </c>
+      <c r="D172" t="n">
+        <v>-2.151</v>
+      </c>
+      <c r="E172" t="n">
+        <v>197.527</v>
+      </c>
+      <c r="F172" t="n">
+        <v>-11.676</v>
+      </c>
+      <c r="G172" t="n">
+        <v>-11.134</v>
+      </c>
+      <c r="H172" t="n">
+        <v>197.527</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="n">
+        <v>12645.927</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-8.743</v>
+      </c>
+      <c r="D173" t="n">
+        <v>-2.045</v>
+      </c>
+      <c r="E173" t="n">
+        <v>197.593</v>
+      </c>
+      <c r="F173" t="n">
+        <v>-9.048999999999999</v>
+      </c>
+      <c r="G173" t="n">
+        <v>-3.736</v>
+      </c>
+      <c r="H173" t="n">
+        <v>197.593</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="n">
+        <v>12726.505</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-8.731999999999999</v>
+      </c>
+      <c r="D174" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="E174" t="n">
+        <v>197.125</v>
+      </c>
+      <c r="F174" t="n">
+        <v>-6.375</v>
+      </c>
+      <c r="G174" t="n">
+        <v>-1.452</v>
+      </c>
+      <c r="H174" t="n">
+        <v>197.125</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="n">
+        <v>12806.676</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-8.721</v>
+      </c>
+      <c r="D175" t="n">
+        <v>-1.675</v>
+      </c>
+      <c r="E175" t="n">
+        <v>195.92</v>
+      </c>
+      <c r="F175" t="n">
+        <v>-6.33</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="H175" t="n">
+        <v>195.92</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="n">
+        <v>12886.221</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-8.710000000000001</v>
+      </c>
+      <c r="D176" t="n">
+        <v>-1.492</v>
+      </c>
+      <c r="E176" t="n">
+        <v>196.603</v>
+      </c>
+      <c r="F176" t="n">
+        <v>-8.603999999999999</v>
+      </c>
+      <c r="G176" t="n">
+        <v>3.769</v>
+      </c>
+      <c r="H176" t="n">
+        <v>196.603</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="n">
+        <v>12966.387</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-8.699</v>
+      </c>
+      <c r="D177" t="n">
+        <v>-1.308</v>
+      </c>
+      <c r="E177" t="n">
+        <v>196.57</v>
+      </c>
+      <c r="F177" t="n">
+        <v>-8.875</v>
+      </c>
+      <c r="G177" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="H177" t="n">
+        <v>196.57</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="n">
+        <v>13046.911</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-8.688000000000001</v>
+      </c>
+      <c r="D178" t="n">
+        <v>-1.122</v>
+      </c>
+      <c r="E178" t="n">
+        <v>196.442</v>
+      </c>
+      <c r="F178" t="n">
+        <v>-8.317</v>
+      </c>
+      <c r="G178" t="n">
+        <v>4.127</v>
+      </c>
+      <c r="H178" t="n">
+        <v>196.442</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="n">
+        <v>13126.316</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-8.448</v>
+      </c>
+      <c r="D179" t="n">
+        <v>-1.116</v>
+      </c>
+      <c r="E179" t="n">
+        <v>196.812</v>
+      </c>
+      <c r="F179" t="n">
+        <v>-7.632</v>
+      </c>
+      <c r="G179" t="n">
+        <v>4.271</v>
+      </c>
+      <c r="H179" t="n">
+        <v>196.812</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="n">
+        <v>13206.193</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-7.721</v>
+      </c>
+      <c r="D180" t="n">
+        <v>-1.098</v>
+      </c>
+      <c r="E180" t="n">
+        <v>196.724</v>
+      </c>
+      <c r="F180" t="n">
+        <v>-7.303</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1.681</v>
+      </c>
+      <c r="H180" t="n">
+        <v>196.724</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="n">
+        <v>13286.478</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-6.99</v>
+      </c>
+      <c r="D181" t="n">
+        <v>-1.081</v>
+      </c>
+      <c r="E181" t="n">
+        <v>196.525</v>
+      </c>
+      <c r="F181" t="n">
+        <v>-7.169</v>
+      </c>
+      <c r="G181" t="n">
+        <v>-0.9389999999999999</v>
+      </c>
+      <c r="H181" t="n">
+        <v>196.525</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="n">
+        <v>13365.907</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-6.267</v>
+      </c>
+      <c r="D182" t="n">
+        <v>-1.063</v>
+      </c>
+      <c r="E182" t="n">
+        <v>196.084</v>
+      </c>
+      <c r="F182" t="n">
+        <v>-7.246</v>
+      </c>
+      <c r="G182" t="n">
+        <v>-1.104</v>
+      </c>
+      <c r="H182" t="n">
+        <v>196.084</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="n">
+        <v>13446.377</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-5.535</v>
+      </c>
+      <c r="D183" t="n">
+        <v>-1.045</v>
+      </c>
+      <c r="E183" t="n">
+        <v>195.825</v>
+      </c>
+      <c r="F183" t="n">
+        <v>-7.023</v>
+      </c>
+      <c r="G183" t="n">
+        <v>-4.079</v>
+      </c>
+      <c r="H183" t="n">
+        <v>195.825</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="n">
+        <v>13526.636</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-4.804</v>
+      </c>
+      <c r="D184" t="n">
+        <v>-1.027</v>
+      </c>
+      <c r="E184" t="n">
+        <v>195.557</v>
+      </c>
+      <c r="F184" t="n">
+        <v>-6.991</v>
+      </c>
+      <c r="G184" t="n">
+        <v>-4.204</v>
+      </c>
+      <c r="H184" t="n">
+        <v>195.557</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="n">
+        <v>13609.289</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-4.052</v>
+      </c>
+      <c r="D185" t="n">
+        <v>-1.009</v>
+      </c>
+      <c r="E185" t="n">
+        <v>195.365</v>
+      </c>
+      <c r="F185" t="n">
+        <v>-6.962</v>
+      </c>
+      <c r="G185" t="n">
+        <v>-7.489</v>
+      </c>
+      <c r="H185" t="n">
+        <v>195.365</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="n">
+        <v>13686.406</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-3.366</v>
+      </c>
+      <c r="D186" t="n">
+        <v>-3.298</v>
+      </c>
+      <c r="E186" t="n">
+        <v>195.233</v>
+      </c>
+      <c r="F186" t="n">
+        <v>-7.103</v>
+      </c>
+      <c r="G186" t="n">
+        <v>-7.549</v>
+      </c>
+      <c r="H186" t="n">
+        <v>195.233</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="n">
+        <v>13766.325</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.859</v>
+      </c>
+      <c r="D187" t="n">
+        <v>-8.324</v>
+      </c>
+      <c r="E187" t="n">
+        <v>195.339</v>
+      </c>
+      <c r="F187" t="n">
+        <v>-1.541</v>
+      </c>
+      <c r="G187" t="n">
+        <v>-4.714</v>
+      </c>
+      <c r="H187" t="n">
+        <v>195.339</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="n">
+        <v>13846.176</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.353</v>
+      </c>
+      <c r="D188" t="n">
+        <v>-13.346</v>
+      </c>
+      <c r="E188" t="n">
+        <v>195.15</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="G188" t="n">
+        <v>-1.579</v>
+      </c>
+      <c r="H188" t="n">
+        <v>195.15</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" t="n">
+        <v>13925.973</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="D189" t="n">
+        <v>-18.364</v>
+      </c>
+      <c r="E189" t="n">
+        <v>194.78</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="G189" t="n">
+        <v>-0.973</v>
+      </c>
+      <c r="H189" t="n">
+        <v>194.78</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2.661</v>
+      </c>
+      <c r="D190" t="n">
+        <v>-23.398</v>
+      </c>
+      <c r="E190" t="n">
+        <v>193.795</v>
+      </c>
+      <c r="F190" t="n">
+        <v>6.111</v>
+      </c>
+      <c r="G190" t="n">
+        <v>-2.971</v>
+      </c>
+      <c r="H190" t="n">
+        <v>193.795</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C191" t="n">
+        <v>4.177</v>
+      </c>
+      <c r="D191" t="n">
+        <v>-28.454</v>
+      </c>
+      <c r="E191" t="n">
+        <v>191.319</v>
+      </c>
+      <c r="F191" t="n">
+        <v>-19.44</v>
+      </c>
+      <c r="G191" t="n">
+        <v>46.847</v>
+      </c>
+      <c r="H191" t="n">
+        <v>191.319</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="n">
+        <v>14000.049</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-19.45</v>
+      </c>
+      <c r="D192" t="n">
+        <v>46.843</v>
+      </c>
+      <c r="E192" t="n">
+        <v>190.285</v>
+      </c>
+      <c r="F192" t="n">
+        <v>-22.446</v>
+      </c>
+      <c r="G192" t="n">
+        <v>45.904</v>
+      </c>
+      <c r="H192" t="n">
+        <v>190.285</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="n">
+        <v>14088.781</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-17.709</v>
+      </c>
+      <c r="D193" t="n">
+        <v>39.112</v>
+      </c>
+      <c r="E193" t="n">
+        <v>190.909</v>
+      </c>
+      <c r="F193" t="n">
+        <v>-22.446</v>
+      </c>
+      <c r="G193" t="n">
+        <v>45.722</v>
+      </c>
+      <c r="H193" t="n">
+        <v>190.909</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="n">
+        <v>14168.173</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-16.152</v>
+      </c>
+      <c r="D194" t="n">
+        <v>32.907</v>
+      </c>
+      <c r="E194" t="n">
+        <v>190.141</v>
+      </c>
+      <c r="F194" t="n">
+        <v>-22.827</v>
+      </c>
+      <c r="G194" t="n">
+        <v>49.209</v>
+      </c>
+      <c r="H194" t="n">
+        <v>190.141</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="n">
+        <v>14248.25</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-14.581</v>
+      </c>
+      <c r="D195" t="n">
+        <v>28.849</v>
+      </c>
+      <c r="E195" t="n">
+        <v>191.702</v>
+      </c>
+      <c r="F195" t="n">
+        <v>-23.014</v>
+      </c>
+      <c r="G195" t="n">
+        <v>43.996</v>
+      </c>
+      <c r="H195" t="n">
+        <v>191.702</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="n">
+        <v>14328.27</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-13.011</v>
+      </c>
+      <c r="D196" t="n">
+        <v>19.925</v>
+      </c>
+      <c r="E196" t="n">
+        <v>193.407</v>
+      </c>
+      <c r="F196" t="n">
+        <v>-21.334</v>
+      </c>
+      <c r="G196" t="n">
+        <v>37.537</v>
+      </c>
+      <c r="H196" t="n">
+        <v>193.407</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="n">
+        <v>14408.07</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-11.446</v>
+      </c>
+      <c r="D197" t="n">
+        <v>12.007</v>
+      </c>
+      <c r="E197" t="n">
+        <v>194.944</v>
+      </c>
+      <c r="F197" t="n">
+        <v>-19.679</v>
+      </c>
+      <c r="G197" t="n">
+        <v>30.975</v>
+      </c>
+      <c r="H197" t="n">
+        <v>194.944</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="n">
+        <v>14488.753</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-9.863</v>
+      </c>
+      <c r="D198" t="n">
+        <v>5.743</v>
+      </c>
+      <c r="E198" t="n">
+        <v>196.493</v>
+      </c>
+      <c r="F198" t="n">
+        <v>-17.617</v>
+      </c>
+      <c r="G198" t="n">
+        <v>21.494</v>
+      </c>
+      <c r="H198" t="n">
+        <v>196.493</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="n">
+        <v>14572.381</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-8.223000000000001</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="E199" t="n">
+        <v>197.576</v>
+      </c>
+      <c r="F199" t="n">
+        <v>-15.595</v>
+      </c>
+      <c r="G199" t="n">
+        <v>11.487</v>
+      </c>
+      <c r="H199" t="n">
+        <v>197.576</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="n">
+        <v>14648.614</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-8.17</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="E200" t="n">
+        <v>198.438</v>
+      </c>
+      <c r="F200" t="n">
+        <v>-13.086</v>
+      </c>
+      <c r="G200" t="n">
+        <v>6.536</v>
+      </c>
+      <c r="H200" t="n">
+        <v>198.438</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="n">
+        <v>14728.001</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-8.084</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="E201" t="n">
+        <v>197.441</v>
+      </c>
+      <c r="F201" t="n">
+        <v>-13.369</v>
+      </c>
+      <c r="G201" t="n">
+        <v>2.418</v>
+      </c>
+      <c r="H201" t="n">
+        <v>197.441</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="n">
+        <v>14807.932</v>
+      </c>
+      <c r="C202" t="n">
+        <v>-7.998</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="E202" t="n">
+        <v>196.457</v>
+      </c>
+      <c r="F202" t="n">
+        <v>-11.003</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="H202" t="n">
+        <v>196.457</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="n">
+        <v>14887.983</v>
+      </c>
+      <c r="C203" t="n">
+        <v>-7.911</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="E203" t="n">
+        <v>196.124</v>
+      </c>
+      <c r="F203" t="n">
+        <v>-9.093999999999999</v>
+      </c>
+      <c r="G203" t="n">
+        <v>-4.948</v>
+      </c>
+      <c r="H203" t="n">
+        <v>196.124</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="n">
+        <v>14967.849</v>
+      </c>
+      <c r="C204" t="n">
+        <v>-7.824</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E204" t="n">
+        <v>196.867</v>
+      </c>
+      <c r="F204" t="n">
+        <v>-8.83</v>
+      </c>
+      <c r="G204" t="n">
+        <v>-5.805</v>
+      </c>
+      <c r="H204" t="n">
+        <v>196.867</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" t="n">
+        <v>15048.852</v>
+      </c>
+      <c r="C205" t="n">
+        <v>-7.736</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="E205" t="n">
+        <v>196.759</v>
+      </c>
+      <c r="F205" t="n">
+        <v>-5.504</v>
+      </c>
+      <c r="G205" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="H205" t="n">
+        <v>196.759</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" t="n">
+        <v>15128.027</v>
+      </c>
+      <c r="C206" t="n">
+        <v>-7.478</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="E206" t="n">
+        <v>195.982</v>
+      </c>
+      <c r="F206" t="n">
+        <v>-5.818</v>
+      </c>
+      <c r="G206" t="n">
+        <v>-5.302</v>
+      </c>
+      <c r="H206" t="n">
+        <v>195.982</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" t="n">
+        <v>15208.287</v>
+      </c>
+      <c r="C207" t="n">
+        <v>-6.741</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="E207" t="n">
+        <v>195.797</v>
+      </c>
+      <c r="F207" t="n">
+        <v>-5.486</v>
+      </c>
+      <c r="G207" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="H207" t="n">
+        <v>195.797</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" t="n">
+        <v>15288.475</v>
+      </c>
+      <c r="C208" t="n">
+        <v>-6.004</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="E208" t="n">
+        <v>195.662</v>
+      </c>
+      <c r="F208" t="n">
+        <v>-2.415</v>
+      </c>
+      <c r="G208" t="n">
+        <v>-5.857</v>
+      </c>
+      <c r="H208" t="n">
+        <v>195.662</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" t="n">
+        <v>15367.971</v>
+      </c>
+      <c r="C209" t="n">
+        <v>-5.273</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="E209" t="n">
+        <v>195.383</v>
+      </c>
+      <c r="F209" t="n">
+        <v>-4.763</v>
+      </c>
+      <c r="G209" t="n">
+        <v>-0.298</v>
+      </c>
+      <c r="H209" t="n">
+        <v>195.383</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" t="n">
+        <v>15448.001</v>
+      </c>
+      <c r="C210" t="n">
+        <v>-4.538</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="E210" t="n">
+        <v>195.142</v>
+      </c>
+      <c r="F210" t="n">
+        <v>-1.471</v>
+      </c>
+      <c r="G210" t="n">
+        <v>-0.159</v>
+      </c>
+      <c r="H210" t="n">
+        <v>195.142</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" t="n">
+        <v>15529.645</v>
+      </c>
+      <c r="C211" t="n">
+        <v>-3.787</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="E211" t="n">
+        <v>194.864</v>
+      </c>
+      <c r="F211" t="n">
+        <v>-1.127</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2.829</v>
+      </c>
+      <c r="H211" t="n">
+        <v>194.864</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" t="n">
+        <v>15609.928</v>
+      </c>
+      <c r="C212" t="n">
+        <v>-3.049</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="E212" t="n">
+        <v>194.349</v>
+      </c>
+      <c r="F212" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="G212" t="n">
+        <v>5.835</v>
+      </c>
+      <c r="H212" t="n">
+        <v>194.349</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" t="n">
+        <v>15687.987</v>
+      </c>
+      <c r="C213" t="n">
+        <v>-2.333</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E213" t="n">
+        <v>194.809</v>
+      </c>
+      <c r="F213" t="n">
+        <v>-1.057</v>
+      </c>
+      <c r="G213" t="n">
+        <v>5.239</v>
+      </c>
+      <c r="H213" t="n">
+        <v>194.809</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" t="n">
+        <v>15768.375</v>
+      </c>
+      <c r="C214" t="n">
+        <v>-0.8179999999999999</v>
+      </c>
+      <c r="D214" t="n">
+        <v>6.591</v>
+      </c>
+      <c r="E214" t="n">
+        <v>194.913</v>
+      </c>
+      <c r="F214" t="n">
+        <v>4.978</v>
+      </c>
+      <c r="G214" t="n">
+        <v>-0.444</v>
+      </c>
+      <c r="H214" t="n">
+        <v>194.913</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" t="n">
+        <v>15847.625</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="D215" t="n">
+        <v>10.999</v>
+      </c>
+      <c r="E215" t="n">
+        <v>194.764</v>
+      </c>
+      <c r="F215" t="n">
+        <v>5.095</v>
+      </c>
+      <c r="G215" t="n">
+        <v>-0.764</v>
+      </c>
+      <c r="H215" t="n">
+        <v>194.764</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" t="n">
+        <v>15928.265</v>
+      </c>
+      <c r="C216" t="n">
+        <v>2.197</v>
+      </c>
+      <c r="D216" t="n">
+        <v>15.484</v>
+      </c>
+      <c r="E216" t="n">
+        <v>193.84</v>
+      </c>
+      <c r="F216" t="n">
+        <v>5.577</v>
+      </c>
+      <c r="G216" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="H216" t="n">
+        <v>193.84</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3.703</v>
+      </c>
+      <c r="D217" t="n">
+        <v>19.927</v>
+      </c>
+      <c r="E217" t="n">
+        <v>193.933</v>
+      </c>
+      <c r="F217" t="n">
+        <v>6.112</v>
+      </c>
+      <c r="G217" t="n">
+        <v>3.342</v>
+      </c>
+      <c r="H217" t="n">
+        <v>193.933</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" t="n">
+        <v>16000</v>
+      </c>
+      <c r="C218" t="n">
+        <v>5.216</v>
+      </c>
+      <c r="D218" t="n">
+        <v>24.392</v>
+      </c>
+      <c r="E218" t="n">
+        <v>190.243</v>
+      </c>
+      <c r="F218" t="n">
+        <v>-17.763</v>
+      </c>
+      <c r="G218" t="n">
+        <v>-49.586</v>
+      </c>
+      <c r="H218" t="n">
+        <v>190.243</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" t="n">
+        <v>16000.075</v>
+      </c>
+      <c r="C219" t="n">
+        <v>-12.117</v>
+      </c>
+      <c r="D219" t="n">
+        <v>-49.58</v>
+      </c>
+      <c r="E219" t="n">
+        <v>190.339</v>
+      </c>
+      <c r="F219" t="n">
+        <v>-17.409</v>
+      </c>
+      <c r="G219" t="n">
+        <v>-47.41</v>
+      </c>
+      <c r="H219" t="n">
+        <v>190.339</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" t="n">
+        <v>16088.665</v>
+      </c>
+      <c r="C220" t="n">
+        <v>-11.609</v>
+      </c>
+      <c r="D220" t="n">
+        <v>-40.552</v>
+      </c>
+      <c r="E220" t="n">
+        <v>190.197</v>
+      </c>
+      <c r="F220" t="n">
+        <v>-17.595</v>
+      </c>
+      <c r="G220" t="n">
+        <v>-48.109</v>
+      </c>
+      <c r="H220" t="n">
+        <v>190.197</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" t="n">
+        <v>16168.892</v>
+      </c>
+      <c r="C221" t="n">
+        <v>-11.15</v>
+      </c>
+      <c r="D221" t="n">
+        <v>-34.848</v>
+      </c>
+      <c r="E221" t="n">
+        <v>190.247</v>
+      </c>
+      <c r="F221" t="n">
+        <v>-17.976</v>
+      </c>
+      <c r="G221" t="n">
+        <v>-48.467</v>
+      </c>
+      <c r="H221" t="n">
+        <v>190.247</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" t="n">
+        <v>16248.942</v>
+      </c>
+      <c r="C222" t="n">
+        <v>-10.691</v>
+      </c>
+      <c r="D222" t="n">
+        <v>-28.773</v>
+      </c>
+      <c r="E222" t="n">
+        <v>191.874</v>
+      </c>
+      <c r="F222" t="n">
+        <v>-18.33</v>
+      </c>
+      <c r="G222" t="n">
+        <v>-43.957</v>
+      </c>
+      <c r="H222" t="n">
+        <v>191.874</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" t="n">
+        <v>16329.276</v>
+      </c>
+      <c r="C223" t="n">
+        <v>-10.231</v>
+      </c>
+      <c r="D223" t="n">
+        <v>-20.382</v>
+      </c>
+      <c r="E223" t="n">
+        <v>193.356</v>
+      </c>
+      <c r="F223" t="n">
+        <v>-18.544</v>
+      </c>
+      <c r="G223" t="n">
+        <v>-39.037</v>
+      </c>
+      <c r="H223" t="n">
+        <v>193.356</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" t="n">
+        <v>16408.706</v>
+      </c>
+      <c r="C224" t="n">
+        <v>-9.776</v>
+      </c>
+      <c r="D224" t="n">
+        <v>-13.127</v>
+      </c>
+      <c r="E224" t="n">
+        <v>194.831</v>
+      </c>
+      <c r="F224" t="n">
+        <v>-16.649</v>
+      </c>
+      <c r="G224" t="n">
+        <v>-32.502</v>
+      </c>
+      <c r="H224" t="n">
+        <v>194.831</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" t="n">
+        <v>16491.162</v>
+      </c>
+      <c r="C225" t="n">
+        <v>-9.304</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-6.714</v>
+      </c>
+      <c r="E225" t="n">
+        <v>197.032</v>
+      </c>
+      <c r="F225" t="n">
+        <v>-14.587</v>
+      </c>
+      <c r="G225" t="n">
+        <v>-22.395</v>
+      </c>
+      <c r="H225" t="n">
+        <v>197.032</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" t="n">
+        <v>16568.765</v>
+      </c>
+      <c r="C226" t="n">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-2.114</v>
+      </c>
+      <c r="E226" t="n">
+        <v>198.744</v>
+      </c>
+      <c r="F226" t="n">
+        <v>-11.864</v>
+      </c>
+      <c r="G226" t="n">
+        <v>-9.74</v>
+      </c>
+      <c r="H226" t="n">
+        <v>198.744</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" t="n">
+        <v>16649.051</v>
+      </c>
+      <c r="C227" t="n">
+        <v>-8.842000000000001</v>
+      </c>
+      <c r="D227" t="n">
+        <v>-2.005</v>
+      </c>
+      <c r="E227" t="n">
+        <v>197.963</v>
+      </c>
+      <c r="F227" t="n">
+        <v>-11.828</v>
+      </c>
+      <c r="G227" t="n">
+        <v>-5.959</v>
+      </c>
+      <c r="H227" t="n">
+        <v>197.963</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" t="n">
+        <v>16728.749</v>
+      </c>
+      <c r="C228" t="n">
+        <v>-8.814</v>
+      </c>
+      <c r="D228" t="n">
+        <v>-1.827</v>
+      </c>
+      <c r="E228" t="n">
+        <v>198.145</v>
+      </c>
+      <c r="F228" t="n">
+        <v>-10.063</v>
+      </c>
+      <c r="G228" t="n">
+        <v>-3.248</v>
+      </c>
+      <c r="H228" t="n">
+        <v>198.145</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" t="n">
+        <v>16808.503</v>
+      </c>
+      <c r="C229" t="n">
+        <v>-8.785</v>
+      </c>
+      <c r="D229" t="n">
+        <v>-1.649</v>
+      </c>
+      <c r="E229" t="n">
+        <v>198.395</v>
+      </c>
+      <c r="F229" t="n">
+        <v>-9.465999999999999</v>
+      </c>
+      <c r="G229" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H229" t="n">
+        <v>198.395</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" t="n">
+        <v>16889.35</v>
+      </c>
+      <c r="C230" t="n">
+        <v>-8.756</v>
+      </c>
+      <c r="D230" t="n">
+        <v>-1.469</v>
+      </c>
+      <c r="E230" t="n">
+        <v>198.373</v>
+      </c>
+      <c r="F230" t="n">
+        <v>-9.895</v>
+      </c>
+      <c r="G230" t="n">
+        <v>-0.109</v>
+      </c>
+      <c r="H230" t="n">
+        <v>198.373</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" t="n">
+        <v>16968.397</v>
+      </c>
+      <c r="C231" t="n">
+        <v>-8.728</v>
+      </c>
+      <c r="D231" t="n">
+        <v>-1.293</v>
+      </c>
+      <c r="E231" t="n">
+        <v>198.48</v>
+      </c>
+      <c r="F231" t="n">
+        <v>-9.260999999999999</v>
+      </c>
+      <c r="G231" t="n">
+        <v>2.884</v>
+      </c>
+      <c r="H231" t="n">
+        <v>198.48</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" t="n">
+        <v>17053.949</v>
+      </c>
+      <c r="C232" t="n">
+        <v>-8.696999999999999</v>
+      </c>
+      <c r="D232" t="n">
+        <v>-1.103</v>
+      </c>
+      <c r="E232" t="n">
+        <v>198.018</v>
+      </c>
+      <c r="F232" t="n">
+        <v>-9.061999999999999</v>
+      </c>
+      <c r="G232" t="n">
+        <v>2.191</v>
+      </c>
+      <c r="H232" t="n">
+        <v>198.018</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" t="n">
+        <v>17146.767</v>
+      </c>
+      <c r="C233" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="D233" t="n">
+        <v>-1.094</v>
+      </c>
+      <c r="E233" t="n">
+        <v>196.001</v>
+      </c>
+      <c r="F233" t="n">
+        <v>-8.621</v>
+      </c>
+      <c r="G233" t="n">
+        <v>3.097</v>
+      </c>
+      <c r="H233" t="n">
+        <v>196.001</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" t="n">
+        <v>17224.655</v>
+      </c>
+      <c r="C234" t="n">
+        <v>-7.56</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="E234" t="n">
+        <v>196.12</v>
+      </c>
+      <c r="F234" t="n">
+        <v>-8.452</v>
+      </c>
+      <c r="G234" t="n">
+        <v>3.164</v>
+      </c>
+      <c r="H234" t="n">
+        <v>196.12</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" t="n">
+        <v>17304.865</v>
+      </c>
+      <c r="C235" t="n">
+        <v>-6.829</v>
+      </c>
+      <c r="D235" t="n">
+        <v>-1.065</v>
+      </c>
+      <c r="E235" t="n">
+        <v>195.857</v>
+      </c>
+      <c r="F235" t="n">
+        <v>-7.827</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="H235" t="n">
+        <v>195.857</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" t="n">
+        <v>17385.175</v>
+      </c>
+      <c r="C236" t="n">
+        <v>-6.096</v>
+      </c>
+      <c r="D236" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="E236" t="n">
+        <v>195.678</v>
+      </c>
+      <c r="F236" t="n">
+        <v>-7.751</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="H236" t="n">
+        <v>195.678</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>235</v>
+      </c>
+      <c r="B237" t="n">
+        <v>17464.503</v>
+      </c>
+      <c r="C237" t="n">
+        <v>-5.373</v>
+      </c>
+      <c r="D237" t="n">
+        <v>-1.035</v>
+      </c>
+      <c r="E237" t="n">
+        <v>195.313</v>
+      </c>
+      <c r="F237" t="n">
+        <v>-7.531</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="H237" t="n">
+        <v>195.313</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B238" t="n">
+        <v>17544.635</v>
+      </c>
+      <c r="C238" t="n">
+        <v>-4.642</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="E238" t="n">
+        <v>195.055</v>
+      </c>
+      <c r="F238" t="n">
+        <v>-7.507</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H238" t="n">
+        <v>195.055</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>237</v>
+      </c>
+      <c r="B239" t="n">
+        <v>17624.781</v>
+      </c>
+      <c r="C239" t="n">
+        <v>-3.911</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-1.005</v>
+      </c>
+      <c r="E239" t="n">
+        <v>194.811</v>
+      </c>
+      <c r="F239" t="n">
+        <v>-7.482</v>
+      </c>
+      <c r="G239" t="n">
+        <v>-2.507</v>
+      </c>
+      <c r="H239" t="n">
+        <v>194.811</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>238</v>
+      </c>
+      <c r="B240" t="n">
+        <v>17704.554</v>
+      </c>
+      <c r="C240" t="n">
+        <v>-2.896</v>
+      </c>
+      <c r="D240" t="n">
+        <v>-4.436</v>
+      </c>
+      <c r="E240" t="n">
+        <v>195.147</v>
+      </c>
+      <c r="F240" t="n">
+        <v>-5.413</v>
+      </c>
+      <c r="G240" t="n">
+        <v>-1.913</v>
+      </c>
+      <c r="H240" t="n">
+        <v>195.147</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>239</v>
+      </c>
+      <c r="B241" t="n">
+        <v>17784.364</v>
+      </c>
+      <c r="C241" t="n">
+        <v>-1.412</v>
+      </c>
+      <c r="D241" t="n">
+        <v>-9.456</v>
+      </c>
+      <c r="E241" t="n">
+        <v>194.364</v>
+      </c>
+      <c r="F241" t="n">
+        <v>-2.727</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="H241" t="n">
+        <v>194.364</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B242" t="n">
+        <v>17867.699</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="D242" t="n">
+        <v>-14.697</v>
+      </c>
+      <c r="E242" t="n">
+        <v>194.036</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="G242" t="n">
+        <v>-1.684</v>
+      </c>
+      <c r="H242" t="n">
+        <v>194.036</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>241</v>
+      </c>
+      <c r="B243" t="n">
+        <v>17944.648</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1.569</v>
+      </c>
+      <c r="D243" t="n">
+        <v>-19.537</v>
+      </c>
+      <c r="E243" t="n">
+        <v>193.315</v>
+      </c>
+      <c r="F243" t="n">
+        <v>2.513</v>
+      </c>
+      <c r="G243" t="n">
+        <v>-3.609</v>
+      </c>
+      <c r="H243" t="n">
+        <v>193.315</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>242</v>
+      </c>
+      <c r="B244" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.056</v>
+      </c>
+      <c r="D244" t="n">
+        <v>-24.562</v>
+      </c>
+      <c r="E244" t="n">
+        <v>192.335</v>
+      </c>
+      <c r="F244" t="n">
+        <v>7.819</v>
+      </c>
+      <c r="G244" t="n">
+        <v>-8.337999999999999</v>
+      </c>
+      <c r="H244" t="n">
+        <v>192.335</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>243</v>
+      </c>
+      <c r="B245" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C245" t="n">
+        <v>4.547</v>
+      </c>
+      <c r="D245" t="n">
+        <v>-29.605</v>
+      </c>
+      <c r="E245" t="n">
+        <v>191.101</v>
+      </c>
+      <c r="F245" t="n">
+        <v>-17.313</v>
+      </c>
+      <c r="G245" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="H245" t="n">
+        <v>191.101</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B246" t="n">
+        <v>18000.106</v>
+      </c>
+      <c r="C246" t="n">
+        <v>-13.961</v>
+      </c>
+      <c r="D246" t="n">
+        <v>42.303</v>
+      </c>
+      <c r="E246" t="n">
+        <v>191.49</v>
+      </c>
+      <c r="F246" t="n">
+        <v>-15.365</v>
+      </c>
+      <c r="G246" t="n">
+        <v>41.602</v>
+      </c>
+      <c r="H246" t="n">
+        <v>191.49</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>245</v>
+      </c>
+      <c r="B247" t="n">
+        <v>18079.253</v>
+      </c>
+      <c r="C247" t="n">
+        <v>-13.132</v>
+      </c>
+      <c r="D247" t="n">
+        <v>36.107</v>
+      </c>
+      <c r="E247" t="n">
+        <v>191.575</v>
+      </c>
+      <c r="F247" t="n">
+        <v>-15.745</v>
+      </c>
+      <c r="G247" t="n">
+        <v>41.957</v>
+      </c>
+      <c r="H247" t="n">
+        <v>191.575</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>246</v>
+      </c>
+      <c r="B248" t="n">
+        <v>18159.031</v>
+      </c>
+      <c r="C248" t="n">
+        <v>-12.297</v>
+      </c>
+      <c r="D248" t="n">
+        <v>30.836</v>
+      </c>
+      <c r="E248" t="n">
+        <v>191.524</v>
+      </c>
+      <c r="F248" t="n">
+        <v>-15.719</v>
+      </c>
+      <c r="G248" t="n">
+        <v>42.312</v>
+      </c>
+      <c r="H248" t="n">
+        <v>191.524</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>247</v>
+      </c>
+      <c r="B249" t="n">
+        <v>18240.082</v>
+      </c>
+      <c r="C249" t="n">
+        <v>-11.449</v>
+      </c>
+      <c r="D249" t="n">
+        <v>25.381</v>
+      </c>
+      <c r="E249" t="n">
+        <v>191.703</v>
+      </c>
+      <c r="F249" t="n">
+        <v>-16.109</v>
+      </c>
+      <c r="G249" t="n">
+        <v>40.763</v>
+      </c>
+      <c r="H249" t="n">
+        <v>191.703</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B250" t="n">
+        <v>18319.016</v>
+      </c>
+      <c r="C250" t="n">
+        <v>-10.622</v>
+      </c>
+      <c r="D250" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="E250" t="n">
+        <v>192.794</v>
+      </c>
+      <c r="F250" t="n">
+        <v>-16.862</v>
+      </c>
+      <c r="G250" t="n">
+        <v>33.956</v>
+      </c>
+      <c r="H250" t="n">
+        <v>192.794</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>249</v>
+      </c>
+      <c r="B251" t="n">
+        <v>18399.3</v>
+      </c>
+      <c r="C251" t="n">
+        <v>-9.782</v>
+      </c>
+      <c r="D251" t="n">
+        <v>11.358</v>
+      </c>
+      <c r="E251" t="n">
+        <v>194.404</v>
+      </c>
+      <c r="F251" t="n">
+        <v>-17.745</v>
+      </c>
+      <c r="G251" t="n">
+        <v>26.858</v>
+      </c>
+      <c r="H251" t="n">
+        <v>194.404</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="B252" t="n">
+        <v>18478.89</v>
+      </c>
+      <c r="C252" t="n">
+        <v>-8.949</v>
+      </c>
+      <c r="D252" t="n">
+        <v>5.421</v>
+      </c>
+      <c r="E252" t="n">
+        <v>195.546</v>
+      </c>
+      <c r="F252" t="n">
+        <v>-15.181</v>
+      </c>
+      <c r="G252" t="n">
+        <v>19.896</v>
+      </c>
+      <c r="H252" t="n">
+        <v>195.546</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>251</v>
+      </c>
+      <c r="B253" t="n">
+        <v>18559.078</v>
+      </c>
+      <c r="C253" t="n">
+        <v>-8.109</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="E253" t="n">
+        <v>196.138</v>
+      </c>
+      <c r="F253" t="n">
+        <v>-15.757</v>
+      </c>
+      <c r="G253" t="n">
+        <v>10.061</v>
+      </c>
+      <c r="H253" t="n">
+        <v>196.138</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B254" t="n">
+        <v>18639.155</v>
+      </c>
+      <c r="C254" t="n">
+        <v>-8.074999999999999</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1.251</v>
+      </c>
+      <c r="E254" t="n">
+        <v>196.875</v>
+      </c>
+      <c r="F254" t="n">
+        <v>-13.284</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1.958</v>
+      </c>
+      <c r="H254" t="n">
+        <v>196.875</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>253</v>
+      </c>
+      <c r="B255" t="n">
+        <v>18719.223</v>
+      </c>
+      <c r="C255" t="n">
+        <v>-8.007</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="E255" t="n">
+        <v>196.797</v>
+      </c>
+      <c r="F255" t="n">
+        <v>-10.254</v>
+      </c>
+      <c r="G255" t="n">
+        <v>-0.057</v>
+      </c>
+      <c r="H255" t="n">
+        <v>196.797</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="B256" t="n">
+        <v>18799.253</v>
+      </c>
+      <c r="C256" t="n">
+        <v>-7.938</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="E256" t="n">
+        <v>196.841</v>
+      </c>
+      <c r="F256" t="n">
+        <v>-10.678</v>
+      </c>
+      <c r="G256" t="n">
+        <v>-3.088</v>
+      </c>
+      <c r="H256" t="n">
+        <v>196.841</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="n">
+        <v>18878.951</v>
+      </c>
+      <c r="C257" t="n">
+        <v>-7.87</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E257" t="n">
+        <v>196.813</v>
+      </c>
+      <c r="F257" t="n">
+        <v>-7.907</v>
+      </c>
+      <c r="G257" t="n">
+        <v>-3.121</v>
+      </c>
+      <c r="H257" t="n">
+        <v>196.813</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" t="n">
+        <v>18962.253</v>
+      </c>
+      <c r="C258" t="n">
+        <v>-7.799</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="E258" t="n">
+        <v>196.551</v>
+      </c>
+      <c r="F258" t="n">
+        <v>-8.161</v>
+      </c>
+      <c r="G258" t="n">
+        <v>-3.44</v>
+      </c>
+      <c r="H258" t="n">
+        <v>196.551</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B259" t="n">
+        <v>19041.041</v>
+      </c>
+      <c r="C259" t="n">
+        <v>-7.731</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E259" t="n">
+        <v>196.552</v>
+      </c>
+      <c r="F259" t="n">
+        <v>-7.598</v>
+      </c>
+      <c r="G259" t="n">
+        <v>-3.435</v>
+      </c>
+      <c r="H259" t="n">
+        <v>196.552</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="B260" t="n">
+        <v>19119.09</v>
+      </c>
+      <c r="C260" t="n">
+        <v>-7.556</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="E260" t="n">
+        <v>196.517</v>
+      </c>
+      <c r="F260" t="n">
+        <v>-4.637</v>
+      </c>
+      <c r="G260" t="n">
+        <v>-3.775</v>
+      </c>
+      <c r="H260" t="n">
+        <v>196.517</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="B261" t="n">
+        <v>19199.33</v>
+      </c>
+      <c r="C261" t="n">
+        <v>-6.819</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="E261" t="n">
+        <v>196.554</v>
+      </c>
+      <c r="F261" t="n">
+        <v>-4.308</v>
+      </c>
+      <c r="G261" t="n">
+        <v>-0.889</v>
+      </c>
+      <c r="H261" t="n">
+        <v>196.554</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B262" t="n">
+        <v>19278.776</v>
+      </c>
+      <c r="C262" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="E262" t="n">
+        <v>196.46</v>
+      </c>
+      <c r="F262" t="n">
+        <v>-1.248</v>
+      </c>
+      <c r="G262" t="n">
+        <v>-1.207</v>
+      </c>
+      <c r="H262" t="n">
+        <v>196.46</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="B263" t="n">
+        <v>19359.448</v>
+      </c>
+      <c r="C263" t="n">
+        <v>-5.349</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E263" t="n">
+        <v>195.733</v>
+      </c>
+      <c r="F263" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="G263" t="n">
+        <v>-0.412</v>
+      </c>
+      <c r="H263" t="n">
+        <v>195.733</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>262</v>
+      </c>
+      <c r="B264" t="n">
+        <v>19439.197</v>
+      </c>
+      <c r="C264" t="n">
+        <v>-4.617</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="E264" t="n">
+        <v>196.101</v>
+      </c>
+      <c r="F264" t="n">
+        <v>-0.459</v>
+      </c>
+      <c r="G264" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="H264" t="n">
+        <v>196.101</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>263</v>
+      </c>
+      <c r="B265" t="n">
+        <v>19519.505</v>
+      </c>
+      <c r="C265" t="n">
+        <v>-3.879</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="E265" t="n">
+        <v>195.844</v>
+      </c>
+      <c r="F265" t="n">
+        <v>-0.114</v>
+      </c>
+      <c r="G265" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="H265" t="n">
+        <v>195.844</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B266" t="n">
+        <v>19599.238</v>
+      </c>
+      <c r="C266" t="n">
+        <v>-3.147</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E266" t="n">
+        <v>195.581</v>
+      </c>
+      <c r="F266" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="G266" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="H266" t="n">
+        <v>195.581</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>265</v>
+      </c>
+      <c r="B267" t="n">
+        <v>19678.791</v>
+      </c>
+      <c r="C267" t="n">
+        <v>-2.599</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1.616</v>
+      </c>
+      <c r="E267" t="n">
+        <v>195.574</v>
+      </c>
+      <c r="F267" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G267" t="n">
+        <v>2.541</v>
+      </c>
+      <c r="H267" t="n">
+        <v>195.574</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>266</v>
+      </c>
+      <c r="B268" t="n">
+        <v>19758.784</v>
+      </c>
+      <c r="C268" t="n">
+        <v>-1.077</v>
+      </c>
+      <c r="D268" t="n">
+        <v>6.064</v>
+      </c>
+      <c r="E268" t="n">
+        <v>195.31</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="G268" t="n">
+        <v>-0.569</v>
+      </c>
+      <c r="H268" t="n">
+        <v>195.31</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>267</v>
+      </c>
+      <c r="B269" t="n">
+        <v>19839.263</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="D269" t="n">
+        <v>10.539</v>
+      </c>
+      <c r="E269" t="n">
+        <v>195.334</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="G269" t="n">
+        <v>-0.928</v>
+      </c>
+      <c r="H269" t="n">
+        <v>195.334</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B270" t="n">
+        <v>19919.026</v>
+      </c>
+      <c r="C270" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="D270" t="n">
+        <v>14.974</v>
+      </c>
+      <c r="E270" t="n">
+        <v>194.816</v>
+      </c>
+      <c r="F270" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="G270" t="n">
+        <v>-1.852</v>
+      </c>
+      <c r="H270" t="n">
+        <v>194.816</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>269</v>
+      </c>
+      <c r="B271" t="n">
+        <v>19999.075</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3.496</v>
+      </c>
+      <c r="D271" t="n">
+        <v>19.425</v>
+      </c>
+      <c r="E271" t="n">
+        <v>194.487</v>
+      </c>
+      <c r="F271" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="G271" t="n">
+        <v>6.023</v>
+      </c>
+      <c r="H271" t="n">
+        <v>194.487</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="B272" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C272" t="n">
+        <v>5.012</v>
+      </c>
+      <c r="D272" t="n">
+        <v>23.856</v>
+      </c>
+      <c r="E272" t="n">
+        <v>193.879</v>
+      </c>
+      <c r="F272" t="n">
+        <v>-0.577</v>
+      </c>
+      <c r="G272" t="n">
+        <v>10.699</v>
+      </c>
+      <c r="H272" t="n">
+        <v>193.879</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>271</v>
+      </c>
+      <c r="B273" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C273" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="D273" t="n">
+        <v>28.321</v>
+      </c>
+      <c r="E273" t="n">
+        <v>191.694</v>
+      </c>
+      <c r="F273" t="n">
+        <v>-1.079</v>
+      </c>
+      <c r="G273" t="n">
+        <v>28.817</v>
+      </c>
+      <c r="H273" t="n">
+        <v>191.694</v>
       </c>
     </row>
   </sheetData>

--- a/data/comRead_vs_refCOM-coba.xlsx
+++ b/data/comRead_vs_refCOM-coba.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
         <v>-11.005</v>
       </c>
       <c r="D2" t="n">
-        <v>-38.834</v>
+        <v>-38.844</v>
       </c>
       <c r="E2" t="n">
         <v>190.336</v>
@@ -512,13 +512,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
       <c r="C3" t="n">
         <v>-7.505000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>-38.832</v>
+        <v>-38.842</v>
       </c>
       <c r="E3" t="n">
         <v>190.336</v>
@@ -544,13 +544,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>112.795</v>
+        <v>92.367</v>
       </c>
       <c r="C4" t="n">
         <v>-7.505000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>-31.534</v>
+        <v>-32.864</v>
       </c>
       <c r="E4" t="n">
         <v>190.336</v>
@@ -576,25 +576,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>203.65</v>
+        <v>186.5</v>
       </c>
       <c r="C5" t="n">
         <v>-7.505000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>-25.653</v>
+        <v>-26.77</v>
       </c>
       <c r="E5" t="n">
-        <v>191.127</v>
+        <v>190.99</v>
       </c>
       <c r="F5" t="n">
-        <v>-7</v>
+        <v>-9.757</v>
       </c>
       <c r="G5" t="n">
-        <v>-36.225</v>
+        <v>-35.874</v>
       </c>
       <c r="H5" t="n">
-        <v>191.127</v>
+        <v>190.99</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -608,13 +608,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298.862</v>
+        <v>283.438</v>
       </c>
       <c r="C6" t="n">
         <v>-7.505000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>-19.491</v>
+        <v>-20.494</v>
       </c>
       <c r="E6" t="n">
         <v>191.674</v>
@@ -634,25 +634,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>393.421</v>
+        <v>378.84</v>
       </c>
       <c r="C7" t="n">
         <v>-7.505000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>-13.37</v>
+        <v>-14.318</v>
       </c>
       <c r="E7" t="n">
-        <v>193.064</v>
+        <v>192.275</v>
       </c>
       <c r="F7" t="n">
-        <v>-7</v>
+        <v>-6.974</v>
       </c>
       <c r="G7" t="n">
-        <v>-29.567</v>
+        <v>-29.802</v>
       </c>
       <c r="H7" t="n">
-        <v>193.064</v>
+        <v>192.275</v>
       </c>
     </row>
     <row r="8">
@@ -660,25 +660,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>490.763</v>
+        <v>480.685</v>
       </c>
       <c r="C8" t="n">
         <v>-7.505000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.07</v>
+        <v>-7.724</v>
       </c>
       <c r="E8" t="n">
-        <v>193.956</v>
+        <v>193.903</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.974</v>
+        <v>-7.355</v>
       </c>
       <c r="G8" t="n">
-        <v>-22.721</v>
+        <v>-22.368</v>
       </c>
       <c r="H8" t="n">
-        <v>193.956</v>
+        <v>193.903</v>
       </c>
     </row>
     <row r="9">
@@ -686,25 +686,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>585.492</v>
+        <v>570.408</v>
       </c>
       <c r="C9" t="n">
         <v>-7.505000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-1.916</v>
       </c>
       <c r="E9" t="n">
-        <v>195.406</v>
+        <v>195.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.701</v>
+        <v>-7.08</v>
       </c>
       <c r="G9" t="n">
-        <v>-15.136</v>
+        <v>-17.652</v>
       </c>
       <c r="H9" t="n">
-        <v>195.406</v>
+        <v>195.03</v>
       </c>
     </row>
     <row r="10">
@@ -712,25 +712,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>682.144</v>
+        <v>665.99</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.273</v>
+        <v>-6.515</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.62</v>
+        <v>-1.531</v>
       </c>
       <c r="E10" t="n">
-        <v>195.992</v>
+        <v>195.633</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.333</v>
+        <v>-6.538</v>
       </c>
       <c r="G10" t="n">
-        <v>-7.685</v>
+        <v>-10.266</v>
       </c>
       <c r="H10" t="n">
-        <v>195.992</v>
+        <v>195.633</v>
       </c>
     </row>
     <row r="11">
@@ -738,25 +738,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>776.984</v>
+        <v>763.0359999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>-4.85</v>
+        <v>-5.059</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.253</v>
+        <v>-0.965</v>
       </c>
       <c r="E11" t="n">
-        <v>196.783</v>
+        <v>196.613</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.951</v>
+        <v>-3.393</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.224</v>
+        <v>-4.948</v>
       </c>
       <c r="H11" t="n">
-        <v>196.783</v>
+        <v>196.613</v>
       </c>
     </row>
     <row r="12">
@@ -764,25 +764,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>880.388</v>
+        <v>858.807</v>
       </c>
       <c r="C12" t="n">
-        <v>-3.299</v>
+        <v>-3.623</v>
       </c>
       <c r="D12" t="n">
-        <v>0.148</v>
+        <v>-0.407</v>
       </c>
       <c r="E12" t="n">
-        <v>197.168</v>
+        <v>196.879</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.203</v>
+        <v>-3.371</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.341</v>
+        <v>-5.123</v>
       </c>
       <c r="H12" t="n">
-        <v>197.168</v>
+        <v>196.879</v>
       </c>
     </row>
     <row r="13">
@@ -790,25 +790,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>969.542</v>
+        <v>954.345</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.962</v>
+        <v>-2.19</v>
       </c>
       <c r="D13" t="n">
-        <v>0.494</v>
+        <v>0.151</v>
       </c>
       <c r="E13" t="n">
-        <v>197.412</v>
+        <v>197.32</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.932</v>
+        <v>-0.355</v>
       </c>
       <c r="G13" t="n">
-        <v>0.545</v>
+        <v>-2.4</v>
       </c>
       <c r="H13" t="n">
-        <v>197.412</v>
+        <v>197.32</v>
       </c>
     </row>
     <row r="14">
@@ -816,25 +816,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1065.021</v>
+        <v>1053.156</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.53</v>
+        <v>-0.708</v>
       </c>
       <c r="D14" t="n">
-        <v>0.864</v>
+        <v>0.727</v>
       </c>
       <c r="E14" t="n">
-        <v>197.672</v>
+        <v>197.497</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.743</v>
+        <v>0.028</v>
       </c>
       <c r="G14" t="n">
-        <v>0.323</v>
+        <v>0.598</v>
       </c>
       <c r="H14" t="n">
-        <v>197.672</v>
+        <v>197.497</v>
       </c>
     </row>
     <row r="15">
@@ -842,25 +842,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1161.237</v>
+        <v>1146.151</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.472</v>
+        <v>-0.649</v>
       </c>
       <c r="D15" t="n">
-        <v>0.768</v>
+        <v>0.666</v>
       </c>
       <c r="E15" t="n">
-        <v>197.769</v>
+        <v>197.71</v>
       </c>
       <c r="F15" t="n">
-        <v>0.193</v>
+        <v>0.356</v>
       </c>
       <c r="G15" t="n">
-        <v>3.311</v>
+        <v>0.349</v>
       </c>
       <c r="H15" t="n">
-        <v>197.769</v>
+        <v>197.71</v>
       </c>
     </row>
     <row r="16">
@@ -868,25 +868,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1257.607</v>
+        <v>1242.72</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.38</v>
+        <v>-0.526</v>
       </c>
       <c r="D16" t="n">
-        <v>0.616</v>
+        <v>0.538</v>
       </c>
       <c r="E16" t="n">
-        <v>197.489</v>
+        <v>197.695</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.178</v>
+        <v>3.455</v>
       </c>
       <c r="G16" t="n">
-        <v>3.193</v>
+        <v>0.362</v>
       </c>
       <c r="H16" t="n">
-        <v>197.489</v>
+        <v>197.695</v>
       </c>
     </row>
     <row r="17">
@@ -894,25 +894,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1354.94</v>
+        <v>1338.655</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.287</v>
+        <v>-0.403</v>
       </c>
       <c r="D17" t="n">
-        <v>0.464</v>
+        <v>0.412</v>
       </c>
       <c r="E17" t="n">
-        <v>197.19</v>
+        <v>197.614</v>
       </c>
       <c r="F17" t="n">
-        <v>0.075</v>
+        <v>3.38</v>
       </c>
       <c r="G17" t="n">
-        <v>6.335</v>
+        <v>0.309</v>
       </c>
       <c r="H17" t="n">
-        <v>197.19</v>
+        <v>197.614</v>
       </c>
     </row>
     <row r="18">
@@ -920,25 +920,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1449.91</v>
+        <v>1434.474</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.196</v>
+        <v>-0.28</v>
       </c>
       <c r="D18" t="n">
-        <v>0.314</v>
+        <v>0.285</v>
       </c>
       <c r="E18" t="n">
-        <v>196.917</v>
+        <v>197.332</v>
       </c>
       <c r="F18" t="n">
-        <v>0.123</v>
+        <v>3.776</v>
       </c>
       <c r="G18" t="n">
-        <v>6.151</v>
+        <v>0.131</v>
       </c>
       <c r="H18" t="n">
-        <v>196.917</v>
+        <v>197.332</v>
       </c>
     </row>
     <row r="19">
@@ -946,25 +946,25 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1545.981</v>
+        <v>1536.194</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.104</v>
+        <v>-0.15</v>
       </c>
       <c r="D19" t="n">
-        <v>0.163</v>
+        <v>0.15</v>
       </c>
       <c r="E19" t="n">
-        <v>196.367</v>
+        <v>197.057</v>
       </c>
       <c r="F19" t="n">
-        <v>3.096</v>
+        <v>3.963</v>
       </c>
       <c r="G19" t="n">
-        <v>6.205</v>
+        <v>-0.045</v>
       </c>
       <c r="H19" t="n">
-        <v>196.367</v>
+        <v>197.057</v>
       </c>
     </row>
     <row r="20">
@@ -972,25 +972,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1642.19</v>
+        <v>1626.874</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.012</v>
+        <v>-0.035</v>
       </c>
       <c r="D20" t="n">
-        <v>0.012</v>
+        <v>0.031</v>
       </c>
       <c r="E20" t="n">
-        <v>196.136</v>
+        <v>196.806</v>
       </c>
       <c r="F20" t="n">
-        <v>2.915</v>
+        <v>4.152</v>
       </c>
       <c r="G20" t="n">
-        <v>6.055</v>
+        <v>2.694</v>
       </c>
       <c r="H20" t="n">
-        <v>196.136</v>
+        <v>196.806</v>
       </c>
     </row>
     <row r="21">
@@ -998,25 +998,25 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1741.775</v>
+        <v>1722.653</v>
       </c>
       <c r="C21" t="n">
-        <v>2.075</v>
+        <v>1.62</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.47</v>
+        <v>-5.104</v>
       </c>
       <c r="E21" t="n">
-        <v>195.685</v>
+        <v>196.434</v>
       </c>
       <c r="F21" t="n">
-        <v>2.95</v>
+        <v>4.338</v>
       </c>
       <c r="G21" t="n">
-        <v>3.665</v>
+        <v>2.863</v>
       </c>
       <c r="H21" t="n">
-        <v>195.685</v>
+        <v>196.434</v>
       </c>
     </row>
     <row r="22">
@@ -1024,25 +1024,25 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1836.518</v>
+        <v>1819.029</v>
       </c>
       <c r="C22" t="n">
-        <v>4.229</v>
+        <v>3.816</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.162</v>
+        <v>-11.916</v>
       </c>
       <c r="E22" t="n">
-        <v>195.314</v>
+        <v>195.935</v>
       </c>
       <c r="F22" t="n">
-        <v>3.04</v>
+        <v>4.223</v>
       </c>
       <c r="G22" t="n">
-        <v>1.367</v>
+        <v>3.367</v>
       </c>
       <c r="H22" t="n">
-        <v>195.314</v>
+        <v>195.935</v>
       </c>
     </row>
     <row r="23">
@@ -1050,25 +1050,25 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1931.419</v>
+        <v>1914.58</v>
       </c>
       <c r="C23" t="n">
-        <v>6.387</v>
+        <v>5.993</v>
       </c>
       <c r="D23" t="n">
-        <v>-19.864</v>
+        <v>-18.67</v>
       </c>
       <c r="E23" t="n">
-        <v>194.696</v>
+        <v>195.097</v>
       </c>
       <c r="F23" t="n">
-        <v>3.357</v>
+        <v>1.756</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.269</v>
+        <v>0.419</v>
       </c>
       <c r="H23" t="n">
-        <v>194.696</v>
+        <v>195.097</v>
       </c>
     </row>
     <row r="24">
@@ -1079,22 +1079,22 @@
         <v>2000</v>
       </c>
       <c r="C24" t="n">
-        <v>8.56</v>
+        <v>8.193</v>
       </c>
       <c r="D24" t="n">
-        <v>-26.612</v>
+        <v>-25.496</v>
       </c>
       <c r="E24" t="n">
-        <v>194.06</v>
+        <v>195.001</v>
       </c>
       <c r="F24" t="n">
-        <v>3.502</v>
+        <v>4.652</v>
       </c>
       <c r="G24" t="n">
-        <v>-10.964</v>
+        <v>-3.353</v>
       </c>
       <c r="H24" t="n">
-        <v>194.06</v>
+        <v>195.001</v>
       </c>
     </row>
     <row r="25">
@@ -1105,22 +1105,22 @@
         <v>2000</v>
       </c>
       <c r="C25" t="n">
-        <v>10.763</v>
+        <v>10.353</v>
       </c>
       <c r="D25" t="n">
-        <v>-33.454</v>
+        <v>-32.198</v>
       </c>
       <c r="E25" t="n">
-        <v>190.564</v>
+        <v>189.946</v>
       </c>
       <c r="F25" t="n">
-        <v>-29.716</v>
+        <v>-33.605</v>
       </c>
       <c r="G25" t="n">
-        <v>49.637</v>
+        <v>54.134</v>
       </c>
       <c r="H25" t="n">
-        <v>190.564</v>
+        <v>189.946</v>
       </c>
     </row>
     <row r="26">
@@ -1131,22 +1131,22 @@
         <v>2000.047</v>
       </c>
       <c r="C26" t="n">
-        <v>-29.714</v>
+        <v>-33.603</v>
       </c>
       <c r="D26" t="n">
-        <v>49.633</v>
+        <v>54.13</v>
       </c>
       <c r="E26" t="n">
-        <v>188.785</v>
+        <v>186.868</v>
       </c>
       <c r="F26" t="n">
-        <v>-34.311</v>
+        <v>-41.371</v>
       </c>
       <c r="G26" t="n">
-        <v>48.025</v>
+        <v>51.201</v>
       </c>
       <c r="H26" t="n">
-        <v>188.785</v>
+        <v>186.868</v>
       </c>
     </row>
     <row r="27">
@@ -1154,25 +1154,25 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>2107.305</v>
+        <v>2087.784</v>
       </c>
       <c r="C27" t="n">
-        <v>-25.654</v>
+        <v>-29.713</v>
       </c>
       <c r="D27" t="n">
-        <v>39.436</v>
+        <v>43.71</v>
       </c>
       <c r="E27" t="n">
-        <v>188.727</v>
+        <v>187.438</v>
       </c>
       <c r="F27" t="n">
-        <v>-34.521</v>
+        <v>-40.598</v>
       </c>
       <c r="G27" t="n">
-        <v>48.374</v>
+        <v>51.624</v>
       </c>
       <c r="H27" t="n">
-        <v>188.727</v>
+        <v>187.438</v>
       </c>
     </row>
     <row r="28">
@@ -1180,25 +1180,25 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>2197.828</v>
+        <v>2183.651</v>
       </c>
       <c r="C28" t="n">
-        <v>-22.228</v>
+        <v>-25.463</v>
       </c>
       <c r="D28" t="n">
-        <v>32.424</v>
+        <v>35.823</v>
       </c>
       <c r="E28" t="n">
-        <v>189.739</v>
+        <v>187.521</v>
       </c>
       <c r="F28" t="n">
-        <v>-34.144</v>
+        <v>-40.407</v>
       </c>
       <c r="G28" t="n">
-        <v>46.346</v>
+        <v>52.347</v>
       </c>
       <c r="H28" t="n">
-        <v>189.739</v>
+        <v>187.521</v>
       </c>
     </row>
     <row r="29">
@@ -1206,25 +1206,25 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>2294.935</v>
+        <v>2279.895</v>
       </c>
       <c r="C29" t="n">
-        <v>-18.552</v>
+        <v>-21.196</v>
       </c>
       <c r="D29" t="n">
-        <v>23.564</v>
+        <v>27.928</v>
       </c>
       <c r="E29" t="n">
-        <v>190.319</v>
+        <v>189.877</v>
       </c>
       <c r="F29" t="n">
-        <v>-35.464</v>
+        <v>-38.381</v>
       </c>
       <c r="G29" t="n">
-        <v>42.05</v>
+        <v>48.337</v>
       </c>
       <c r="H29" t="n">
-        <v>190.319</v>
+        <v>189.877</v>
       </c>
     </row>
     <row r="30">
@@ -1232,25 +1232,25 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>2387.788</v>
+        <v>2376.09</v>
       </c>
       <c r="C30" t="n">
-        <v>-15.038</v>
+        <v>-16.932</v>
       </c>
       <c r="D30" t="n">
-        <v>14.873</v>
+        <v>18.039</v>
       </c>
       <c r="E30" t="n">
-        <v>192.963</v>
+        <v>193.016</v>
       </c>
       <c r="F30" t="n">
-        <v>-30.667</v>
+        <v>-34.924</v>
       </c>
       <c r="G30" t="n">
-        <v>35.641</v>
+        <v>38.826</v>
       </c>
       <c r="H30" t="n">
-        <v>192.963</v>
+        <v>193.016</v>
       </c>
     </row>
     <row r="31">
@@ -1258,25 +1258,25 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>2484.272</v>
+        <v>2472.89</v>
       </c>
       <c r="C31" t="n">
-        <v>-11.385</v>
+        <v>-12.64</v>
       </c>
       <c r="D31" t="n">
-        <v>6.874</v>
+        <v>8.225</v>
       </c>
       <c r="E31" t="n">
-        <v>195.171</v>
+        <v>195.693</v>
       </c>
       <c r="F31" t="n">
-        <v>-26.961</v>
+        <v>-31.447</v>
       </c>
       <c r="G31" t="n">
-        <v>26.232</v>
+        <v>29.764</v>
       </c>
       <c r="H31" t="n">
-        <v>195.171</v>
+        <v>195.693</v>
       </c>
     </row>
     <row r="32">
@@ -1284,25 +1284,25 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>2579.797</v>
+        <v>2567.576</v>
       </c>
       <c r="C32" t="n">
-        <v>-7.77</v>
+        <v>-8.442</v>
       </c>
       <c r="D32" t="n">
-        <v>0.883</v>
+        <v>1.608</v>
       </c>
       <c r="E32" t="n">
-        <v>196.905</v>
+        <v>198.256</v>
       </c>
       <c r="F32" t="n">
-        <v>-20.657</v>
+        <v>-24.787</v>
       </c>
       <c r="G32" t="n">
-        <v>16.604</v>
+        <v>20.035</v>
       </c>
       <c r="H32" t="n">
-        <v>196.905</v>
+        <v>198.256</v>
       </c>
     </row>
     <row r="33">
@@ -1310,25 +1310,25 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>2676.181</v>
+        <v>2664.075</v>
       </c>
       <c r="C33" t="n">
-        <v>-7.653</v>
+        <v>-8.257999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.748</v>
+        <v>1.402</v>
       </c>
       <c r="E33" t="n">
-        <v>198.081</v>
+        <v>199.135</v>
       </c>
       <c r="F33" t="n">
-        <v>-15.894</v>
+        <v>-20.978</v>
       </c>
       <c r="G33" t="n">
-        <v>8.804</v>
+        <v>9.92</v>
       </c>
       <c r="H33" t="n">
-        <v>198.081</v>
+        <v>199.135</v>
       </c>
     </row>
     <row r="34">
@@ -1336,25 +1336,25 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>2774.845</v>
+        <v>2759.358</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.502</v>
+        <v>-7.984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.574</v>
+        <v>1.096</v>
       </c>
       <c r="E34" t="n">
-        <v>197.354</v>
+        <v>199.937</v>
       </c>
       <c r="F34" t="n">
-        <v>-13.84</v>
+        <v>-16.141</v>
       </c>
       <c r="G34" t="n">
-        <v>2.065</v>
+        <v>4.498</v>
       </c>
       <c r="H34" t="n">
-        <v>197.354</v>
+        <v>199.937</v>
       </c>
     </row>
     <row r="35">
@@ -1362,25 +1362,25 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>2868.205</v>
+        <v>2855.938</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.36</v>
+        <v>-7.706</v>
       </c>
       <c r="D35" t="n">
-        <v>0.409</v>
+        <v>0.785</v>
       </c>
       <c r="E35" t="n">
-        <v>196.708</v>
+        <v>199.29</v>
       </c>
       <c r="F35" t="n">
-        <v>-8.714</v>
+        <v>-11.928</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6840000000000001</v>
+        <v>-0.332</v>
       </c>
       <c r="H35" t="n">
-        <v>196.708</v>
+        <v>199.29</v>
       </c>
     </row>
     <row r="36">
@@ -1388,25 +1388,25 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>2968.033</v>
+        <v>2951.658</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.207</v>
+        <v>-7.431</v>
       </c>
       <c r="D36" t="n">
-        <v>0.233</v>
+        <v>0.477</v>
       </c>
       <c r="E36" t="n">
-        <v>196.654</v>
+        <v>199.035</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.962</v>
+        <v>-9.891999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>-2.24</v>
+        <v>-3.304</v>
       </c>
       <c r="H36" t="n">
-        <v>196.654</v>
+        <v>199.035</v>
       </c>
     </row>
     <row r="37">
@@ -1414,25 +1414,25 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>3066.027</v>
+        <v>3047.344</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.057</v>
+        <v>-7.156</v>
       </c>
       <c r="D37" t="n">
-        <v>0.06</v>
+        <v>0.169</v>
       </c>
       <c r="E37" t="n">
-        <v>196.469</v>
+        <v>199.144</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.099</v>
+        <v>-6.303</v>
       </c>
       <c r="G37" t="n">
-        <v>-5.122</v>
+        <v>-3.324</v>
       </c>
       <c r="H37" t="n">
-        <v>196.469</v>
+        <v>199.144</v>
       </c>
     </row>
     <row r="38">
@@ -1440,25 +1440,25 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>3163.384</v>
+        <v>3144.129</v>
       </c>
       <c r="C38" t="n">
-        <v>-6.187</v>
+        <v>-6.542</v>
       </c>
       <c r="D38" t="n">
-        <v>0.053</v>
+        <v>0.155</v>
       </c>
       <c r="E38" t="n">
-        <v>196.019</v>
+        <v>198.282</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.746</v>
+        <v>-3.665</v>
       </c>
       <c r="G38" t="n">
-        <v>-5.308</v>
+        <v>-8.395</v>
       </c>
       <c r="H38" t="n">
-        <v>196.019</v>
+        <v>198.282</v>
       </c>
     </row>
     <row r="39">
@@ -1466,25 +1466,25 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>3251.846</v>
+        <v>3239.994</v>
       </c>
       <c r="C39" t="n">
-        <v>-4.972</v>
+        <v>-5.209</v>
       </c>
       <c r="D39" t="n">
-        <v>0.043</v>
+        <v>0.126</v>
       </c>
       <c r="E39" t="n">
-        <v>195.961</v>
+        <v>197.816</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.061</v>
+        <v>1.894</v>
       </c>
       <c r="G39" t="n">
-        <v>-5.267</v>
+        <v>-8.577999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>195.961</v>
+        <v>197.816</v>
       </c>
     </row>
     <row r="40">
@@ -1492,25 +1492,25 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>3348.652</v>
+        <v>3336.096</v>
       </c>
       <c r="C40" t="n">
-        <v>-3.643</v>
+        <v>-3.872</v>
       </c>
       <c r="D40" t="n">
-        <v>0.033</v>
+        <v>0.096</v>
       </c>
       <c r="E40" t="n">
-        <v>195.667</v>
+        <v>197.439</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.47</v>
+        <v>5.463</v>
       </c>
       <c r="G40" t="n">
-        <v>-5.469</v>
+        <v>-8.747999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>195.667</v>
+        <v>197.439</v>
       </c>
     </row>
     <row r="41">
@@ -1518,25 +1518,25 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>3445.94</v>
+        <v>3432.254</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.307</v>
+        <v>-2.534</v>
       </c>
       <c r="D41" t="n">
-        <v>0.022</v>
+        <v>0.067</v>
       </c>
       <c r="E41" t="n">
-        <v>195.326</v>
+        <v>197.084</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.961</v>
+        <v>6.334</v>
       </c>
       <c r="G41" t="n">
-        <v>-5.649</v>
+        <v>-5.934</v>
       </c>
       <c r="H41" t="n">
-        <v>195.326</v>
+        <v>197.084</v>
       </c>
     </row>
     <row r="42">
@@ -1544,25 +1544,25 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>3540.508</v>
+        <v>3527.215</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.008</v>
+        <v>-1.213</v>
       </c>
       <c r="D42" t="n">
-        <v>0.012</v>
+        <v>0.038</v>
       </c>
       <c r="E42" t="n">
-        <v>195.152</v>
+        <v>196.207</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.243</v>
+        <v>6.965</v>
       </c>
       <c r="G42" t="n">
-        <v>0.228</v>
+        <v>-2.456</v>
       </c>
       <c r="H42" t="n">
-        <v>195.152</v>
+        <v>196.207</v>
       </c>
     </row>
     <row r="43">
@@ -1570,25 +1570,25 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>3638.038</v>
+        <v>3624.083</v>
       </c>
       <c r="C43" t="n">
-        <v>0.331</v>
+        <v>0.134</v>
       </c>
       <c r="D43" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="E43" t="n">
-        <v>194.767</v>
+        <v>194.574</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.105</v>
+        <v>7.799</v>
       </c>
       <c r="G43" t="n">
-        <v>0.046</v>
+        <v>1.703</v>
       </c>
       <c r="H43" t="n">
-        <v>194.767</v>
+        <v>194.574</v>
       </c>
     </row>
     <row r="44">
@@ -1596,25 +1596,25 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>3738.008</v>
+        <v>3719.479</v>
       </c>
       <c r="C44" t="n">
-        <v>2.357</v>
+        <v>1.759</v>
       </c>
       <c r="D44" t="n">
-        <v>5.415</v>
+        <v>4.282</v>
       </c>
       <c r="E44" t="n">
-        <v>194.445</v>
+        <v>194.341</v>
       </c>
       <c r="F44" t="n">
-        <v>3.192</v>
+        <v>8.647</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.188</v>
+        <v>7.089</v>
       </c>
       <c r="H44" t="n">
-        <v>194.445</v>
+        <v>194.341</v>
       </c>
     </row>
     <row r="45">
@@ -1622,25 +1622,25 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>3829.798</v>
+        <v>3815.402</v>
       </c>
       <c r="C45" t="n">
-        <v>4.471</v>
+        <v>4.002</v>
       </c>
       <c r="D45" t="n">
-        <v>11.061</v>
+        <v>10.184</v>
       </c>
       <c r="E45" t="n">
-        <v>194.119</v>
+        <v>194.776</v>
       </c>
       <c r="F45" t="n">
-        <v>3.45</v>
+        <v>4.798</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.416</v>
+        <v>4.182</v>
       </c>
       <c r="H45" t="n">
-        <v>194.119</v>
+        <v>194.776</v>
       </c>
     </row>
     <row r="46">
@@ -1648,25 +1648,25 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>3927.847</v>
+        <v>3912.153</v>
       </c>
       <c r="C46" t="n">
-        <v>6.729</v>
+        <v>6.264</v>
       </c>
       <c r="D46" t="n">
-        <v>17.093</v>
+        <v>16.136</v>
       </c>
       <c r="E46" t="n">
-        <v>193.777</v>
+        <v>194.528</v>
       </c>
       <c r="F46" t="n">
-        <v>6.633</v>
+        <v>5.065</v>
       </c>
       <c r="G46" t="n">
-        <v>1.78</v>
+        <v>3.526</v>
       </c>
       <c r="H46" t="n">
-        <v>193.777</v>
+        <v>194.528</v>
       </c>
     </row>
     <row r="47">
@@ -1677,22 +1677,22 @@
         <v>4000</v>
       </c>
       <c r="C47" t="n">
-        <v>8.867000000000001</v>
+        <v>8.502000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>22.806</v>
+        <v>22.024</v>
       </c>
       <c r="E47" t="n">
-        <v>193.695</v>
+        <v>194.291</v>
       </c>
       <c r="F47" t="n">
-        <v>9.510999999999999</v>
+        <v>3.006</v>
       </c>
       <c r="G47" t="n">
-        <v>5.837</v>
+        <v>5.695</v>
       </c>
       <c r="H47" t="n">
-        <v>193.695</v>
+        <v>194.291</v>
       </c>
     </row>
     <row r="48">
@@ -1703,22 +1703,22 @@
         <v>4000</v>
       </c>
       <c r="C48" t="n">
-        <v>11.068</v>
+        <v>10.923</v>
       </c>
       <c r="D48" t="n">
-        <v>28.686</v>
+        <v>28.392</v>
       </c>
       <c r="E48" t="n">
-        <v>190.431</v>
+        <v>190.287</v>
       </c>
       <c r="F48" t="n">
-        <v>-26.388</v>
+        <v>-33.366</v>
       </c>
       <c r="G48" t="n">
-        <v>-47.332</v>
+        <v>-47.326</v>
       </c>
       <c r="H48" t="n">
-        <v>190.431</v>
+        <v>190.287</v>
       </c>
     </row>
     <row r="49">
@@ -1726,25 +1726,1325 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>4000.052</v>
+        <v>4000.053</v>
       </c>
       <c r="C49" t="n">
-        <v>-26.386</v>
+        <v>-33.364</v>
       </c>
       <c r="D49" t="n">
-        <v>-47.328</v>
+        <v>-47.322</v>
       </c>
       <c r="E49" t="n">
-        <v>192.492</v>
+        <v>187.742</v>
       </c>
       <c r="F49" t="n">
-        <v>2.623</v>
+        <v>-39.591</v>
       </c>
       <c r="G49" t="n">
-        <v>21.579</v>
+        <v>-45.33</v>
       </c>
       <c r="H49" t="n">
-        <v>192.492</v>
+        <v>187.742</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4086.711</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-29.629</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-38.779</v>
+      </c>
+      <c r="E50" t="n">
+        <v>188.352</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-38.882</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-45.726</v>
+      </c>
+      <c r="H50" t="n">
+        <v>188.352</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>4182.142</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-25.515</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-31.845</v>
+      </c>
+      <c r="E51" t="n">
+        <v>187.748</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-38.893</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-49.181</v>
+      </c>
+      <c r="H51" t="n">
+        <v>187.748</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4282.096</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-21.207</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-26.058</v>
+      </c>
+      <c r="E52" t="n">
+        <v>189.889</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-36.725</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-44.434</v>
+      </c>
+      <c r="H52" t="n">
+        <v>189.889</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4374.092</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-17.242</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-16.73</v>
+      </c>
+      <c r="E53" t="n">
+        <v>192.753</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-33.07</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-37.125</v>
+      </c>
+      <c r="H53" t="n">
+        <v>192.753</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>4470.101</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-13.104</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-8.038</v>
+      </c>
+      <c r="E54" t="n">
+        <v>195.119</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-29.584</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-27.73</v>
+      </c>
+      <c r="H54" t="n">
+        <v>195.119</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>4565.888</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-8.975</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-1.577</v>
+      </c>
+      <c r="E55" t="n">
+        <v>197.154</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-22.405</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-18.138</v>
+      </c>
+      <c r="H55" t="n">
+        <v>197.154</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>4662.748</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-8.791</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-1.254</v>
+      </c>
+      <c r="E56" t="n">
+        <v>197.727</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-18.729</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-10.991</v>
+      </c>
+      <c r="H56" t="n">
+        <v>197.727</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4758.809</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-8.507999999999999</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.758</v>
+      </c>
+      <c r="E57" t="n">
+        <v>198.006</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-13.352</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-6.019</v>
+      </c>
+      <c r="H57" t="n">
+        <v>198.006</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4853.613</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-8.228999999999999</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E58" t="n">
+        <v>198.047</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-11.02</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-6.628</v>
+      </c>
+      <c r="H58" t="n">
+        <v>198.047</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4951.187</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-7.943</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="E59" t="n">
+        <v>196.704</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-8.933</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-5.128</v>
+      </c>
+      <c r="H59" t="n">
+        <v>196.704</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5046.891</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-7.661</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="E60" t="n">
+        <v>196.422</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-8.294</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-3.188</v>
+      </c>
+      <c r="H60" t="n">
+        <v>196.422</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5144.891</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-7.036</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="E61" t="n">
+        <v>196.662</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.597</v>
+      </c>
+      <c r="H61" t="n">
+        <v>196.662</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5238.943</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-5.727</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E62" t="n">
+        <v>196.478</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-4.654</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-0.622</v>
+      </c>
+      <c r="H62" t="n">
+        <v>196.478</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5333.86</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-4.406</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="E63" t="n">
+        <v>196.375</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-1.093</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2.189</v>
+      </c>
+      <c r="H63" t="n">
+        <v>196.375</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5429.309999999999</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-3.077</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E64" t="n">
+        <v>195.849</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-1.073</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4.839</v>
+      </c>
+      <c r="H64" t="n">
+        <v>195.849</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>5525.474</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.738</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="E65" t="n">
+        <v>195.618</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.979</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4.693</v>
+      </c>
+      <c r="H65" t="n">
+        <v>195.618</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5622.442</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.389</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="E66" t="n">
+        <v>195.37</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4.525</v>
+      </c>
+      <c r="H66" t="n">
+        <v>195.37</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5717.386</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-4.139</v>
+      </c>
+      <c r="E67" t="n">
+        <v>194.989</v>
+      </c>
+      <c r="F67" t="n">
+        <v>3.218</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H67" t="n">
+        <v>194.989</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>5813.393</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3.439</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-11.441</v>
+      </c>
+      <c r="E68" t="n">
+        <v>194.541</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.801</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5.234</v>
+      </c>
+      <c r="H68" t="n">
+        <v>194.541</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5909.631</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5.693</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-18.76</v>
+      </c>
+      <c r="E69" t="n">
+        <v>194.16</v>
+      </c>
+      <c r="F69" t="n">
+        <v>4.068</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="H69" t="n">
+        <v>194.16</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7.946</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-26.076</v>
+      </c>
+      <c r="E70" t="n">
+        <v>193.54</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-3.902</v>
+      </c>
+      <c r="H70" t="n">
+        <v>193.54</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C71" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-33.361</v>
+      </c>
+      <c r="E71" t="n">
+        <v>190.256</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-28.877</v>
+      </c>
+      <c r="G71" t="n">
+        <v>51.879</v>
+      </c>
+      <c r="H71" t="n">
+        <v>190.256</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>6000.069</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-28.874</v>
+      </c>
+      <c r="D72" t="n">
+        <v>51.873</v>
+      </c>
+      <c r="E72" t="n">
+        <v>189.073</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-32.061</v>
+      </c>
+      <c r="G72" t="n">
+        <v>49.936</v>
+      </c>
+      <c r="H72" t="n">
+        <v>189.073</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>6087.934</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-25.672</v>
+      </c>
+      <c r="D73" t="n">
+        <v>42.618</v>
+      </c>
+      <c r="E73" t="n">
+        <v>189.406</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-31.864</v>
+      </c>
+      <c r="G73" t="n">
+        <v>50.323</v>
+      </c>
+      <c r="H73" t="n">
+        <v>189.406</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6187.979</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-22.025</v>
+      </c>
+      <c r="D74" t="n">
+        <v>34.557</v>
+      </c>
+      <c r="E74" t="n">
+        <v>189.251</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-31.91</v>
+      </c>
+      <c r="G74" t="n">
+        <v>51.021</v>
+      </c>
+      <c r="H74" t="n">
+        <v>189.251</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6280.591</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-18.649</v>
+      </c>
+      <c r="D75" t="n">
+        <v>27.161</v>
+      </c>
+      <c r="E75" t="n">
+        <v>190.97</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-32.477</v>
+      </c>
+      <c r="G75" t="n">
+        <v>46.189</v>
+      </c>
+      <c r="H75" t="n">
+        <v>190.97</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6374.907</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-15.21</v>
+      </c>
+      <c r="D76" t="n">
+        <v>17.328</v>
+      </c>
+      <c r="E76" t="n">
+        <v>193.033</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-31.046</v>
+      </c>
+      <c r="G76" t="n">
+        <v>37.516</v>
+      </c>
+      <c r="H76" t="n">
+        <v>193.033</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6471.025</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-11.707</v>
+      </c>
+      <c r="D77" t="n">
+        <v>8.064</v>
+      </c>
+      <c r="E77" t="n">
+        <v>196.221</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-26.605</v>
+      </c>
+      <c r="G77" t="n">
+        <v>27.481</v>
+      </c>
+      <c r="H77" t="n">
+        <v>196.221</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6567.58</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-8.186999999999999</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="E78" t="n">
+        <v>197.213</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-25.764</v>
+      </c>
+      <c r="G78" t="n">
+        <v>17.936</v>
+      </c>
+      <c r="H78" t="n">
+        <v>197.213</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>6668.146</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-8.026</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="E79" t="n">
+        <v>198.094</v>
+      </c>
+      <c r="F79" t="n">
+        <v>-21.161</v>
+      </c>
+      <c r="G79" t="n">
+        <v>10.754</v>
+      </c>
+      <c r="H79" t="n">
+        <v>198.094</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>6759.25</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-7.811</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.012</v>
+      </c>
+      <c r="E80" t="n">
+        <v>198.822</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-16.141</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3.058</v>
+      </c>
+      <c r="H80" t="n">
+        <v>198.822</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>6854.949</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-7.584</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="E81" t="n">
+        <v>198.491</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-14.713</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-2.431</v>
+      </c>
+      <c r="H81" t="n">
+        <v>198.491</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="n">
+        <v>6951.194</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-7.357</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="E82" t="n">
+        <v>198.117</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-12.661</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-8.302</v>
+      </c>
+      <c r="H82" t="n">
+        <v>198.117</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="n">
+        <v>7047.262</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="E83" t="n">
+        <v>197.8</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-9.965999999999999</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-8.532</v>
+      </c>
+      <c r="H83" t="n">
+        <v>197.8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="n">
+        <v>7143.907</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-6.521</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="E84" t="n">
+        <v>197.921</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-8.945</v>
+      </c>
+      <c r="H84" t="n">
+        <v>197.921</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="n">
+        <v>7238.975</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-5.203</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="E85" t="n">
+        <v>196.406</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-1.195</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-7.591</v>
+      </c>
+      <c r="H85" t="n">
+        <v>196.406</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="n">
+        <v>7335.602</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-3.864</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E86" t="n">
+        <v>195.553</v>
+      </c>
+      <c r="F86" t="n">
+        <v>5.091</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-4.149</v>
+      </c>
+      <c r="H86" t="n">
+        <v>195.553</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="n">
+        <v>7430.824000000001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-2.544</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="E87" t="n">
+        <v>195.116</v>
+      </c>
+      <c r="F87" t="n">
+        <v>5.956</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-1.411</v>
+      </c>
+      <c r="H87" t="n">
+        <v>195.116</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="n">
+        <v>7527.488</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.203</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="E88" t="n">
+        <v>194.777</v>
+      </c>
+      <c r="F88" t="n">
+        <v>6.622</v>
+      </c>
+      <c r="G88" t="n">
+        <v>4.434</v>
+      </c>
+      <c r="H88" t="n">
+        <v>194.777</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>7623.608</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="E89" t="n">
+        <v>194.243</v>
+      </c>
+      <c r="F89" t="n">
+        <v>7.453</v>
+      </c>
+      <c r="G89" t="n">
+        <v>10.247</v>
+      </c>
+      <c r="H89" t="n">
+        <v>194.243</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="n">
+        <v>7720.135</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="D90" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="E90" t="n">
+        <v>194.231</v>
+      </c>
+      <c r="F90" t="n">
+        <v>5.069</v>
+      </c>
+      <c r="G90" t="n">
+        <v>10.279</v>
+      </c>
+      <c r="H90" t="n">
+        <v>194.231</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="n">
+        <v>7815.494</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>10.189</v>
+      </c>
+      <c r="E91" t="n">
+        <v>194.588</v>
+      </c>
+      <c r="F91" t="n">
+        <v>6.528</v>
+      </c>
+      <c r="G91" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H91" t="n">
+        <v>194.588</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="n">
+        <v>7911.119</v>
+      </c>
+      <c r="C92" t="n">
+        <v>6.237</v>
+      </c>
+      <c r="D92" t="n">
+        <v>16.072</v>
+      </c>
+      <c r="E92" t="n">
+        <v>194.459</v>
+      </c>
+      <c r="F92" t="n">
+        <v>6.794</v>
+      </c>
+      <c r="G92" t="n">
+        <v>4.263</v>
+      </c>
+      <c r="H92" t="n">
+        <v>194.459</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C93" t="n">
+        <v>8.542</v>
+      </c>
+      <c r="D93" t="n">
+        <v>22.134</v>
+      </c>
+      <c r="E93" t="n">
+        <v>194.158</v>
+      </c>
+      <c r="F93" t="n">
+        <v>7.464</v>
+      </c>
+      <c r="G93" t="n">
+        <v>3.627</v>
+      </c>
+      <c r="H93" t="n">
+        <v>194.158</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C94" t="n">
+        <v>10.823</v>
+      </c>
+      <c r="D94" t="n">
+        <v>28.132</v>
+      </c>
+      <c r="E94" t="n">
+        <v>189.175</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-30.642</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-54.6</v>
+      </c>
+      <c r="H94" t="n">
+        <v>189.175</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="n">
+        <v>8000.047</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-30.64</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-54.596</v>
+      </c>
+      <c r="E95" t="n">
+        <v>187.503</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-34.899</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-51.843</v>
+      </c>
+      <c r="H95" t="n">
+        <v>187.503</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8087.161</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-27.281</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-44.312</v>
+      </c>
+      <c r="E96" t="n">
+        <v>187.749</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-34.331</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-52.228</v>
+      </c>
+      <c r="H96" t="n">
+        <v>187.749</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8183.743</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-23.557</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-36.234</v>
+      </c>
+      <c r="E97" t="n">
+        <v>187.841</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-34.153</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-52.952</v>
+      </c>
+      <c r="H97" t="n">
+        <v>187.841</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="n">
+        <v>8279.883</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-19.849</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-28.251</v>
+      </c>
+      <c r="E98" t="n">
+        <v>189.259</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-35.293</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-48.495</v>
+      </c>
+      <c r="H98" t="n">
+        <v>189.259</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8376.395</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-16.128</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-18.073</v>
+      </c>
+      <c r="E99" t="n">
+        <v>189.918</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G99" t="n">
+        <v>31.657</v>
+      </c>
+      <c r="H99" t="n">
+        <v>189.918</v>
       </c>
     </row>
   </sheetData>

--- a/data/comRead_vs_refCOM-coba.xlsx
+++ b/data/comRead_vs_refCOM-coba.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,28 +483,28 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-11.005</v>
+        <v>-8.074999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>-38.844</v>
+        <v>-38.91</v>
       </c>
       <c r="E2" t="n">
-        <v>190.336</v>
+        <v>190.459</v>
       </c>
       <c r="F2" t="n">
-        <v>-9.757</v>
+        <v>-7</v>
       </c>
       <c r="G2" t="n">
         <v>-38.299</v>
       </c>
       <c r="H2" t="n">
-        <v>190.336</v>
+        <v>190.459</v>
       </c>
       <c r="I2" t="n">
         <v>800</v>
       </c>
       <c r="J2" t="n">
-        <v>10.21025887870141</v>
+        <v>10.82810021104666</v>
       </c>
     </row>
     <row r="3">
@@ -512,31 +512,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="C3" t="n">
-        <v>-7.505000000000001</v>
+        <v>-4.574999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-38.842</v>
+        <v>-38.908</v>
       </c>
       <c r="E3" t="n">
-        <v>190.336</v>
+        <v>190.476</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.757</v>
+        <v>-6.646</v>
       </c>
       <c r="G3" t="n">
         <v>-38.299</v>
       </c>
       <c r="H3" t="n">
-        <v>190.336</v>
+        <v>190.476</v>
       </c>
       <c r="I3" t="n">
         <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.237640998469394</v>
+        <v>1.258701299698998</v>
       </c>
     </row>
     <row r="4">
@@ -544,31 +544,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>92.367</v>
+        <v>100.712</v>
       </c>
       <c r="C4" t="n">
-        <v>-7.505000000000001</v>
+        <v>-4.574999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>-32.864</v>
+        <v>-32.379</v>
       </c>
       <c r="E4" t="n">
-        <v>190.336</v>
+        <v>190.476</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.757</v>
+        <v>-6.646</v>
       </c>
       <c r="G4" t="n">
         <v>-38.299</v>
       </c>
       <c r="H4" t="n">
-        <v>190.336</v>
+        <v>190.476</v>
       </c>
       <c r="I4" t="n">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="J4" t="n">
-        <v>9.424216470663904</v>
+        <v>9.273414220300607</v>
       </c>
     </row>
     <row r="5">
@@ -576,31 +576,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>186.5</v>
+        <v>195.737</v>
       </c>
       <c r="C5" t="n">
-        <v>-7.505000000000001</v>
+        <v>-4.574999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>-26.77</v>
+        <v>-26.216</v>
       </c>
       <c r="E5" t="n">
-        <v>190.99</v>
+        <v>191.09</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.757</v>
+        <v>-6.619</v>
       </c>
       <c r="G5" t="n">
-        <v>-35.874</v>
+        <v>-36.227</v>
       </c>
       <c r="H5" t="n">
-        <v>190.99</v>
+        <v>191.09</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.152970454009237</v>
+        <v>1.143856262168107</v>
       </c>
     </row>
     <row r="6">
@@ -608,25 +608,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>283.438</v>
+        <v>294.662</v>
       </c>
       <c r="C6" t="n">
-        <v>-7.505000000000001</v>
+        <v>-4.574999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>-20.494</v>
+        <v>-19.801</v>
       </c>
       <c r="E6" t="n">
-        <v>191.674</v>
+        <v>191.796</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.757999999999999</v>
+        <v>-7</v>
       </c>
       <c r="G6" t="n">
-        <v>-34.141</v>
+        <v>-34.137</v>
       </c>
       <c r="H6" t="n">
-        <v>191.674</v>
+        <v>191.796</v>
       </c>
     </row>
     <row r="7">
@@ -634,25 +634,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>378.84</v>
+        <v>390.533</v>
       </c>
       <c r="C7" t="n">
-        <v>-7.505000000000001</v>
+        <v>-4.574999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-14.318</v>
+        <v>-13.584</v>
       </c>
       <c r="E7" t="n">
-        <v>192.275</v>
+        <v>193</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.974</v>
+        <v>-7</v>
       </c>
       <c r="G7" t="n">
-        <v>-29.802</v>
+        <v>-29.219</v>
       </c>
       <c r="H7" t="n">
-        <v>192.275</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8">
@@ -660,25 +660,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>480.685</v>
+        <v>484.614</v>
       </c>
       <c r="C8" t="n">
-        <v>-7.505000000000001</v>
+        <v>-4.574999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.724</v>
+        <v>-7.483</v>
       </c>
       <c r="E8" t="n">
-        <v>193.903</v>
+        <v>193.914</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.355</v>
+        <v>-7</v>
       </c>
       <c r="G8" t="n">
-        <v>-22.368</v>
+        <v>-22.365</v>
       </c>
       <c r="H8" t="n">
-        <v>193.903</v>
+        <v>193.914</v>
       </c>
     </row>
     <row r="9">
@@ -686,25 +686,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>570.408</v>
+        <v>579.6</v>
       </c>
       <c r="C9" t="n">
-        <v>-7.505000000000001</v>
+        <v>-4.574999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.916</v>
+        <v>-1.323</v>
       </c>
       <c r="E9" t="n">
-        <v>195.03</v>
+        <v>195.474</v>
       </c>
       <c r="F9" t="n">
-        <v>-7.08</v>
+        <v>-3.945</v>
       </c>
       <c r="G9" t="n">
-        <v>-17.652</v>
+        <v>-15.124</v>
       </c>
       <c r="H9" t="n">
-        <v>195.03</v>
+        <v>195.474</v>
       </c>
     </row>
     <row r="10">
@@ -712,25 +712,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>665.99</v>
+        <v>676.102</v>
       </c>
       <c r="C10" t="n">
-        <v>-6.515</v>
+        <v>-3.433</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.531</v>
+        <v>-0.893</v>
       </c>
       <c r="E10" t="n">
-        <v>195.633</v>
+        <v>196.004</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.538</v>
+        <v>-3.557</v>
       </c>
       <c r="G10" t="n">
-        <v>-10.266</v>
+        <v>-7.695</v>
       </c>
       <c r="H10" t="n">
-        <v>195.633</v>
+        <v>196.004</v>
       </c>
     </row>
     <row r="11">
@@ -738,25 +738,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>763.0359999999999</v>
+        <v>772.317</v>
       </c>
       <c r="C11" t="n">
-        <v>-5.059</v>
+        <v>-1.99</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.965</v>
+        <v>-0.35</v>
       </c>
       <c r="E11" t="n">
-        <v>196.613</v>
+        <v>196.541</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.393</v>
+        <v>-0.952</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.948</v>
+        <v>-2.081</v>
       </c>
       <c r="H11" t="n">
-        <v>196.613</v>
+        <v>196.541</v>
       </c>
     </row>
     <row r="12">
@@ -764,25 +764,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>858.807</v>
+        <v>876.177</v>
       </c>
       <c r="C12" t="n">
-        <v>-3.623</v>
+        <v>-0.432</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.407</v>
+        <v>0.236</v>
       </c>
       <c r="E12" t="n">
-        <v>196.879</v>
+        <v>197.028</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.371</v>
+        <v>1.994</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.123</v>
+        <v>0.703</v>
       </c>
       <c r="H12" t="n">
-        <v>196.879</v>
+        <v>197.028</v>
       </c>
     </row>
     <row r="13">
@@ -790,25 +790,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>954.345</v>
+        <v>965.3440000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.19</v>
+        <v>0.905</v>
       </c>
       <c r="D13" t="n">
-        <v>0.151</v>
+        <v>0.74</v>
       </c>
       <c r="E13" t="n">
-        <v>197.32</v>
+        <v>197.184</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.355</v>
+        <v>2.25</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4</v>
+        <v>3.715</v>
       </c>
       <c r="H13" t="n">
-        <v>197.32</v>
+        <v>197.184</v>
       </c>
     </row>
     <row r="14">
@@ -816,25 +816,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1053.156</v>
+        <v>1065.288</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.708</v>
+        <v>2.404</v>
       </c>
       <c r="D14" t="n">
-        <v>0.727</v>
+        <v>1.304</v>
       </c>
       <c r="E14" t="n">
-        <v>197.497</v>
+        <v>197.24</v>
       </c>
       <c r="F14" t="n">
-        <v>0.028</v>
+        <v>2.796</v>
       </c>
       <c r="G14" t="n">
-        <v>0.598</v>
+        <v>3.757</v>
       </c>
       <c r="H14" t="n">
-        <v>197.497</v>
+        <v>197.24</v>
       </c>
     </row>
     <row r="15">
@@ -842,25 +842,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1146.151</v>
+        <v>1156.079</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.649</v>
+        <v>2.457</v>
       </c>
       <c r="D15" t="n">
-        <v>0.666</v>
+        <v>1.069</v>
       </c>
       <c r="E15" t="n">
-        <v>197.71</v>
+        <v>197.095</v>
       </c>
       <c r="F15" t="n">
-        <v>0.356</v>
+        <v>2.426</v>
       </c>
       <c r="G15" t="n">
-        <v>0.349</v>
+        <v>6.675</v>
       </c>
       <c r="H15" t="n">
-        <v>197.71</v>
+        <v>197.095</v>
       </c>
     </row>
     <row r="16">
@@ -868,25 +868,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1242.72</v>
+        <v>1251.91</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.526</v>
+        <v>2.548</v>
       </c>
       <c r="D16" t="n">
-        <v>0.538</v>
+        <v>0.668</v>
       </c>
       <c r="E16" t="n">
-        <v>197.695</v>
+        <v>197.045</v>
       </c>
       <c r="F16" t="n">
-        <v>3.455</v>
+        <v>2.914</v>
       </c>
       <c r="G16" t="n">
-        <v>0.362</v>
+        <v>6.645</v>
       </c>
       <c r="H16" t="n">
-        <v>197.695</v>
+        <v>197.045</v>
       </c>
     </row>
     <row r="17">
@@ -894,25 +894,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1338.655</v>
+        <v>1348.307</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.403</v>
+        <v>2.639</v>
       </c>
       <c r="D17" t="n">
-        <v>0.412</v>
+        <v>0.264</v>
       </c>
       <c r="E17" t="n">
-        <v>197.614</v>
+        <v>196.818</v>
       </c>
       <c r="F17" t="n">
-        <v>3.38</v>
+        <v>3.371</v>
       </c>
       <c r="G17" t="n">
-        <v>0.309</v>
+        <v>9.811</v>
       </c>
       <c r="H17" t="n">
-        <v>197.614</v>
+        <v>196.818</v>
       </c>
     </row>
     <row r="18">
@@ -920,25 +920,25 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1434.474</v>
+        <v>1444.398</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.28</v>
+        <v>2.73</v>
       </c>
       <c r="D18" t="n">
-        <v>0.285</v>
+        <v>-0.139</v>
       </c>
       <c r="E18" t="n">
-        <v>197.332</v>
+        <v>196.362</v>
       </c>
       <c r="F18" t="n">
-        <v>3.776</v>
+        <v>3.406</v>
       </c>
       <c r="G18" t="n">
-        <v>0.131</v>
+        <v>9.911</v>
       </c>
       <c r="H18" t="n">
-        <v>197.332</v>
+        <v>196.362</v>
       </c>
     </row>
     <row r="19">
@@ -946,25 +946,25 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1536.194</v>
+        <v>1540.351</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.15</v>
+        <v>2.821</v>
       </c>
       <c r="D19" t="n">
-        <v>0.15</v>
+        <v>-0.541</v>
       </c>
       <c r="E19" t="n">
-        <v>197.057</v>
+        <v>196.008</v>
       </c>
       <c r="F19" t="n">
-        <v>3.963</v>
+        <v>3.609</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.045</v>
+        <v>7.126</v>
       </c>
       <c r="H19" t="n">
-        <v>197.057</v>
+        <v>196.008</v>
       </c>
     </row>
     <row r="20">
@@ -972,25 +972,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1626.874</v>
+        <v>1635.99</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.035</v>
+        <v>2.912</v>
       </c>
       <c r="D20" t="n">
-        <v>0.031</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>196.806</v>
+        <v>195.376</v>
       </c>
       <c r="F20" t="n">
-        <v>4.152</v>
+        <v>3.278</v>
       </c>
       <c r="G20" t="n">
-        <v>2.694</v>
+        <v>4.675</v>
       </c>
       <c r="H20" t="n">
-        <v>196.806</v>
+        <v>195.376</v>
       </c>
     </row>
     <row r="21">
@@ -998,25 +998,25 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1722.653</v>
+        <v>1732.408</v>
       </c>
       <c r="C21" t="n">
-        <v>1.62</v>
+        <v>4.787</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.104</v>
+        <v>-6.33</v>
       </c>
       <c r="E21" t="n">
-        <v>196.434</v>
+        <v>195.096</v>
       </c>
       <c r="F21" t="n">
-        <v>4.338</v>
+        <v>2.946</v>
       </c>
       <c r="G21" t="n">
-        <v>2.863</v>
+        <v>2.034</v>
       </c>
       <c r="H21" t="n">
-        <v>196.434</v>
+        <v>195.096</v>
       </c>
     </row>
     <row r="22">
@@ -1024,25 +1024,25 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1819.029</v>
+        <v>1828.708</v>
       </c>
       <c r="C22" t="n">
-        <v>3.816</v>
+        <v>6.978</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.916</v>
+        <v>-12.628</v>
       </c>
       <c r="E22" t="n">
-        <v>195.935</v>
+        <v>194.817</v>
       </c>
       <c r="F22" t="n">
-        <v>4.223</v>
+        <v>3.538</v>
       </c>
       <c r="G22" t="n">
-        <v>3.367</v>
+        <v>-5.878</v>
       </c>
       <c r="H22" t="n">
-        <v>195.935</v>
+        <v>194.817</v>
       </c>
     </row>
     <row r="23">
@@ -1050,25 +1050,25 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1914.58</v>
+        <v>1923.968</v>
       </c>
       <c r="C23" t="n">
-        <v>5.993</v>
+        <v>9.145</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.67</v>
+        <v>-18.858</v>
       </c>
       <c r="E23" t="n">
-        <v>195.097</v>
+        <v>193.525</v>
       </c>
       <c r="F23" t="n">
-        <v>1.756</v>
+        <v>3.004</v>
       </c>
       <c r="G23" t="n">
-        <v>0.419</v>
+        <v>-16.646</v>
       </c>
       <c r="H23" t="n">
-        <v>195.097</v>
+        <v>193.525</v>
       </c>
     </row>
     <row r="24">
@@ -1079,22 +1079,22 @@
         <v>2000</v>
       </c>
       <c r="C24" t="n">
-        <v>8.193</v>
+        <v>11.33</v>
       </c>
       <c r="D24" t="n">
-        <v>-25.496</v>
+        <v>-25.138</v>
       </c>
       <c r="E24" t="n">
-        <v>195.001</v>
+        <v>193.119</v>
       </c>
       <c r="F24" t="n">
-        <v>4.652</v>
+        <v>2.977</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.353</v>
+        <v>-18.776</v>
       </c>
       <c r="H24" t="n">
-        <v>195.001</v>
+        <v>193.119</v>
       </c>
     </row>
     <row r="25">
@@ -1105,22 +1105,22 @@
         <v>2000</v>
       </c>
       <c r="C25" t="n">
-        <v>10.353</v>
+        <v>13.537</v>
       </c>
       <c r="D25" t="n">
-        <v>-32.198</v>
+        <v>-31.483</v>
       </c>
       <c r="E25" t="n">
-        <v>189.946</v>
+        <v>190.838</v>
       </c>
       <c r="F25" t="n">
-        <v>-33.605</v>
+        <v>-26.649</v>
       </c>
       <c r="G25" t="n">
-        <v>54.134</v>
+        <v>47.386</v>
       </c>
       <c r="H25" t="n">
-        <v>189.946</v>
+        <v>190.838</v>
       </c>
     </row>
     <row r="26">
@@ -1128,25 +1128,25 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>2000.047</v>
+        <v>2000.044</v>
       </c>
       <c r="C26" t="n">
-        <v>-33.603</v>
+        <v>-26.647</v>
       </c>
       <c r="D26" t="n">
-        <v>54.13</v>
+        <v>47.383</v>
       </c>
       <c r="E26" t="n">
-        <v>186.868</v>
+        <v>189.669</v>
       </c>
       <c r="F26" t="n">
-        <v>-41.371</v>
+        <v>-30.043</v>
       </c>
       <c r="G26" t="n">
-        <v>51.201</v>
+        <v>46.214</v>
       </c>
       <c r="H26" t="n">
-        <v>186.868</v>
+        <v>189.669</v>
       </c>
     </row>
     <row r="27">
@@ -1154,25 +1154,25 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>2087.784</v>
+        <v>2088.693</v>
       </c>
       <c r="C27" t="n">
-        <v>-29.713</v>
+        <v>-23.312</v>
       </c>
       <c r="D27" t="n">
-        <v>43.71</v>
+        <v>39.383</v>
       </c>
       <c r="E27" t="n">
-        <v>187.438</v>
+        <v>189.941</v>
       </c>
       <c r="F27" t="n">
-        <v>-40.598</v>
+        <v>-29.486</v>
       </c>
       <c r="G27" t="n">
-        <v>51.624</v>
+        <v>46.586</v>
       </c>
       <c r="H27" t="n">
-        <v>187.438</v>
+        <v>189.941</v>
       </c>
     </row>
     <row r="28">
@@ -1180,25 +1180,25 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>2183.651</v>
+        <v>2184.819</v>
       </c>
       <c r="C28" t="n">
-        <v>-25.463</v>
+        <v>-19.695</v>
       </c>
       <c r="D28" t="n">
-        <v>35.823</v>
+        <v>32.236</v>
       </c>
       <c r="E28" t="n">
-        <v>187.521</v>
+        <v>189.856</v>
       </c>
       <c r="F28" t="n">
-        <v>-40.407</v>
+        <v>-29.673</v>
       </c>
       <c r="G28" t="n">
-        <v>52.347</v>
+        <v>47.291</v>
       </c>
       <c r="H28" t="n">
-        <v>187.521</v>
+        <v>189.856</v>
       </c>
     </row>
     <row r="29">
@@ -1206,25 +1206,25 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>2279.895</v>
+        <v>2279.554</v>
       </c>
       <c r="C29" t="n">
-        <v>-21.196</v>
+        <v>-16.131</v>
       </c>
       <c r="D29" t="n">
-        <v>27.928</v>
+        <v>25.257</v>
       </c>
       <c r="E29" t="n">
-        <v>189.877</v>
+        <v>191.459</v>
       </c>
       <c r="F29" t="n">
-        <v>-38.381</v>
+        <v>-30.099</v>
       </c>
       <c r="G29" t="n">
-        <v>48.337</v>
+        <v>39.85</v>
       </c>
       <c r="H29" t="n">
-        <v>189.877</v>
+        <v>191.459</v>
       </c>
     </row>
     <row r="30">
@@ -1232,25 +1232,25 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>2376.09</v>
+        <v>2376.242</v>
       </c>
       <c r="C30" t="n">
-        <v>-16.932</v>
+        <v>-12.494</v>
       </c>
       <c r="D30" t="n">
-        <v>18.039</v>
+        <v>14.861</v>
       </c>
       <c r="E30" t="n">
-        <v>193.016</v>
+        <v>193.604</v>
       </c>
       <c r="F30" t="n">
-        <v>-34.924</v>
+        <v>-25.842</v>
       </c>
       <c r="G30" t="n">
-        <v>38.826</v>
+        <v>35.63</v>
       </c>
       <c r="H30" t="n">
-        <v>193.016</v>
+        <v>193.604</v>
       </c>
     </row>
     <row r="31">
@@ -1258,25 +1258,25 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>2472.89</v>
+        <v>2471.782</v>
       </c>
       <c r="C31" t="n">
-        <v>-12.64</v>
+        <v>-8.898999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>8.225</v>
+        <v>7.614</v>
       </c>
       <c r="E31" t="n">
-        <v>195.693</v>
+        <v>195.077</v>
       </c>
       <c r="F31" t="n">
-        <v>-31.447</v>
+        <v>-24.929</v>
       </c>
       <c r="G31" t="n">
-        <v>29.764</v>
+        <v>23.982</v>
       </c>
       <c r="H31" t="n">
-        <v>195.693</v>
+        <v>195.077</v>
       </c>
     </row>
     <row r="32">
@@ -1284,25 +1284,25 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>2567.576</v>
+        <v>2567.643</v>
       </c>
       <c r="C32" t="n">
-        <v>-8.442</v>
+        <v>-5.292</v>
       </c>
       <c r="D32" t="n">
-        <v>1.608</v>
+        <v>1.293</v>
       </c>
       <c r="E32" t="n">
-        <v>198.256</v>
+        <v>197.228</v>
       </c>
       <c r="F32" t="n">
-        <v>-24.787</v>
+        <v>-18.078</v>
       </c>
       <c r="G32" t="n">
-        <v>20.035</v>
+        <v>16.55</v>
       </c>
       <c r="H32" t="n">
-        <v>198.256</v>
+        <v>197.228</v>
       </c>
     </row>
     <row r="33">
@@ -1310,25 +1310,25 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>2664.075</v>
+        <v>2663.828</v>
       </c>
       <c r="C33" t="n">
-        <v>-8.257999999999999</v>
+        <v>-5.137</v>
       </c>
       <c r="D33" t="n">
-        <v>1.402</v>
+        <v>1.319</v>
       </c>
       <c r="E33" t="n">
-        <v>199.135</v>
+        <v>197.682</v>
       </c>
       <c r="F33" t="n">
-        <v>-20.978</v>
+        <v>-13.324</v>
       </c>
       <c r="G33" t="n">
-        <v>9.92</v>
+        <v>9.459</v>
       </c>
       <c r="H33" t="n">
-        <v>199.135</v>
+        <v>197.682</v>
       </c>
     </row>
     <row r="34">
@@ -1336,25 +1336,25 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>2759.358</v>
+        <v>2760.136</v>
       </c>
       <c r="C34" t="n">
-        <v>-7.984</v>
+        <v>-4.902</v>
       </c>
       <c r="D34" t="n">
-        <v>1.096</v>
+        <v>1.359</v>
       </c>
       <c r="E34" t="n">
-        <v>199.937</v>
+        <v>196.877</v>
       </c>
       <c r="F34" t="n">
-        <v>-16.141</v>
+        <v>-8.522</v>
       </c>
       <c r="G34" t="n">
-        <v>4.498</v>
+        <v>2.415</v>
       </c>
       <c r="H34" t="n">
-        <v>199.937</v>
+        <v>196.877</v>
       </c>
     </row>
     <row r="35">
@@ -1362,25 +1362,25 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>2855.938</v>
+        <v>2861.728</v>
       </c>
       <c r="C35" t="n">
-        <v>-7.706</v>
+        <v>-4.655</v>
       </c>
       <c r="D35" t="n">
-        <v>0.785</v>
+        <v>1.401</v>
       </c>
       <c r="E35" t="n">
-        <v>199.29</v>
+        <v>196.615</v>
       </c>
       <c r="F35" t="n">
-        <v>-11.928</v>
+        <v>-6.175</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.332</v>
+        <v>0.383</v>
       </c>
       <c r="H35" t="n">
-        <v>199.29</v>
+        <v>196.615</v>
       </c>
     </row>
     <row r="36">
@@ -1388,25 +1388,25 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>2951.658</v>
+        <v>2953.979</v>
       </c>
       <c r="C36" t="n">
-        <v>-7.431</v>
+        <v>-4.43</v>
       </c>
       <c r="D36" t="n">
-        <v>0.477</v>
+        <v>1.44</v>
       </c>
       <c r="E36" t="n">
-        <v>199.035</v>
+        <v>196.199</v>
       </c>
       <c r="F36" t="n">
-        <v>-9.891999999999999</v>
+        <v>-6.471</v>
       </c>
       <c r="G36" t="n">
-        <v>-3.304</v>
+        <v>0.446</v>
       </c>
       <c r="H36" t="n">
-        <v>199.035</v>
+        <v>196.199</v>
       </c>
     </row>
     <row r="37">
@@ -1414,25 +1414,25 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>3047.344</v>
+        <v>3047.717</v>
       </c>
       <c r="C37" t="n">
-        <v>-7.156</v>
+        <v>-4.202</v>
       </c>
       <c r="D37" t="n">
-        <v>0.169</v>
+        <v>1.478</v>
       </c>
       <c r="E37" t="n">
-        <v>199.144</v>
+        <v>196.257</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.303</v>
+        <v>-2.951</v>
       </c>
       <c r="G37" t="n">
-        <v>-3.324</v>
+        <v>0.431</v>
       </c>
       <c r="H37" t="n">
-        <v>199.144</v>
+        <v>196.257</v>
       </c>
     </row>
     <row r="38">
@@ -1440,25 +1440,25 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>3144.129</v>
+        <v>3143.728</v>
       </c>
       <c r="C38" t="n">
-        <v>-6.542</v>
+        <v>-3.596</v>
       </c>
       <c r="D38" t="n">
-        <v>0.155</v>
+        <v>1.44</v>
       </c>
       <c r="E38" t="n">
-        <v>198.282</v>
+        <v>196.395</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.665</v>
+        <v>-2.563</v>
       </c>
       <c r="G38" t="n">
-        <v>-8.395</v>
+        <v>0.349</v>
       </c>
       <c r="H38" t="n">
-        <v>198.282</v>
+        <v>196.395</v>
       </c>
     </row>
     <row r="39">
@@ -1466,25 +1466,25 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>3239.994</v>
+        <v>3240.491</v>
       </c>
       <c r="C39" t="n">
-        <v>-5.209</v>
+        <v>-2.254</v>
       </c>
       <c r="D39" t="n">
-        <v>0.126</v>
+        <v>1.356</v>
       </c>
       <c r="E39" t="n">
-        <v>197.816</v>
+        <v>196.043</v>
       </c>
       <c r="F39" t="n">
-        <v>1.894</v>
+        <v>0.352</v>
       </c>
       <c r="G39" t="n">
-        <v>-8.577999999999999</v>
+        <v>0.475</v>
       </c>
       <c r="H39" t="n">
-        <v>197.816</v>
+        <v>196.043</v>
       </c>
     </row>
     <row r="40">
@@ -1492,25 +1492,25 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>3336.096</v>
+        <v>3336.273</v>
       </c>
       <c r="C40" t="n">
-        <v>-3.872</v>
+        <v>-0.926</v>
       </c>
       <c r="D40" t="n">
-        <v>0.096</v>
+        <v>1.273</v>
       </c>
       <c r="E40" t="n">
-        <v>197.439</v>
+        <v>195.789</v>
       </c>
       <c r="F40" t="n">
-        <v>5.463</v>
+        <v>3.521</v>
       </c>
       <c r="G40" t="n">
-        <v>-8.747999999999999</v>
+        <v>0.224</v>
       </c>
       <c r="H40" t="n">
-        <v>197.439</v>
+        <v>195.789</v>
       </c>
     </row>
     <row r="41">
@@ -1518,25 +1518,25 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>3432.254</v>
+        <v>3438.387</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.534</v>
+        <v>0.491</v>
       </c>
       <c r="D41" t="n">
-        <v>0.067</v>
+        <v>1.184</v>
       </c>
       <c r="E41" t="n">
-        <v>197.084</v>
+        <v>195.492</v>
       </c>
       <c r="F41" t="n">
-        <v>6.334</v>
+        <v>4.398</v>
       </c>
       <c r="G41" t="n">
-        <v>-5.934</v>
+        <v>0.391</v>
       </c>
       <c r="H41" t="n">
-        <v>197.084</v>
+        <v>195.492</v>
       </c>
     </row>
     <row r="42">
@@ -1544,25 +1544,25 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>3527.215</v>
+        <v>3531.835</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.213</v>
+        <v>1.786</v>
       </c>
       <c r="D42" t="n">
-        <v>0.038</v>
+        <v>1.103</v>
       </c>
       <c r="E42" t="n">
-        <v>196.207</v>
+        <v>195.15</v>
       </c>
       <c r="F42" t="n">
-        <v>6.965</v>
+        <v>7.436</v>
       </c>
       <c r="G42" t="n">
-        <v>-2.456</v>
+        <v>0.551</v>
       </c>
       <c r="H42" t="n">
-        <v>196.207</v>
+        <v>195.15</v>
       </c>
     </row>
     <row r="43">
@@ -1570,25 +1570,25 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>3624.083</v>
+        <v>3625.414</v>
       </c>
       <c r="C43" t="n">
-        <v>0.134</v>
+        <v>3.084</v>
       </c>
       <c r="D43" t="n">
-        <v>0.008</v>
+        <v>1.021</v>
       </c>
       <c r="E43" t="n">
-        <v>194.574</v>
+        <v>194.874</v>
       </c>
       <c r="F43" t="n">
-        <v>7.799</v>
+        <v>7.921</v>
       </c>
       <c r="G43" t="n">
-        <v>1.703</v>
+        <v>0.706</v>
       </c>
       <c r="H43" t="n">
-        <v>194.574</v>
+        <v>194.874</v>
       </c>
     </row>
     <row r="44">
@@ -1596,25 +1596,25 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>3719.479</v>
+        <v>3720.39</v>
       </c>
       <c r="C44" t="n">
-        <v>1.759</v>
+        <v>4.727</v>
       </c>
       <c r="D44" t="n">
-        <v>4.282</v>
+        <v>5.486</v>
       </c>
       <c r="E44" t="n">
-        <v>194.341</v>
+        <v>194.652</v>
       </c>
       <c r="F44" t="n">
-        <v>8.647</v>
+        <v>8.657</v>
       </c>
       <c r="G44" t="n">
-        <v>7.089</v>
+        <v>0.827</v>
       </c>
       <c r="H44" t="n">
-        <v>194.341</v>
+        <v>194.652</v>
       </c>
     </row>
     <row r="45">
@@ -1622,25 +1622,25 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>3815.402</v>
+        <v>3816.533</v>
       </c>
       <c r="C45" t="n">
-        <v>4.002</v>
+        <v>6.972</v>
       </c>
       <c r="D45" t="n">
-        <v>10.184</v>
+        <v>11.585</v>
       </c>
       <c r="E45" t="n">
-        <v>194.776</v>
+        <v>194.192</v>
       </c>
       <c r="F45" t="n">
-        <v>4.798</v>
+        <v>9.23</v>
       </c>
       <c r="G45" t="n">
-        <v>4.182</v>
+        <v>-2.575</v>
       </c>
       <c r="H45" t="n">
-        <v>194.776</v>
+        <v>194.192</v>
       </c>
     </row>
     <row r="46">
@@ -1648,25 +1648,25 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>3912.153</v>
+        <v>3912.41</v>
       </c>
       <c r="C46" t="n">
-        <v>6.264</v>
+        <v>9.211</v>
       </c>
       <c r="D46" t="n">
-        <v>16.136</v>
+        <v>17.667</v>
       </c>
       <c r="E46" t="n">
-        <v>194.528</v>
+        <v>193.905</v>
       </c>
       <c r="F46" t="n">
-        <v>5.065</v>
+        <v>9.493</v>
       </c>
       <c r="G46" t="n">
-        <v>3.526</v>
+        <v>-0.367</v>
       </c>
       <c r="H46" t="n">
-        <v>194.528</v>
+        <v>193.905</v>
       </c>
     </row>
     <row r="47">
@@ -1677,22 +1677,22 @@
         <v>4000</v>
       </c>
       <c r="C47" t="n">
-        <v>8.502000000000001</v>
+        <v>11.437</v>
       </c>
       <c r="D47" t="n">
-        <v>22.024</v>
+        <v>23.716</v>
       </c>
       <c r="E47" t="n">
-        <v>194.291</v>
+        <v>193.441</v>
       </c>
       <c r="F47" t="n">
-        <v>3.006</v>
+        <v>9.987</v>
       </c>
       <c r="G47" t="n">
-        <v>5.695</v>
+        <v>4.321</v>
       </c>
       <c r="H47" t="n">
-        <v>194.291</v>
+        <v>193.441</v>
       </c>
     </row>
     <row r="48">
@@ -1703,22 +1703,22 @@
         <v>4000</v>
       </c>
       <c r="C48" t="n">
-        <v>10.923</v>
+        <v>13.682</v>
       </c>
       <c r="D48" t="n">
-        <v>28.392</v>
+        <v>29.814</v>
       </c>
       <c r="E48" t="n">
-        <v>190.287</v>
+        <v>189.984</v>
       </c>
       <c r="F48" t="n">
-        <v>-33.366</v>
+        <v>-29.46</v>
       </c>
       <c r="G48" t="n">
-        <v>-47.326</v>
+        <v>-51.817</v>
       </c>
       <c r="H48" t="n">
-        <v>190.287</v>
+        <v>189.984</v>
       </c>
     </row>
     <row r="49">
@@ -1726,25 +1726,25 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>4000.053</v>
+        <v>4000.047</v>
       </c>
       <c r="C49" t="n">
-        <v>-33.364</v>
+        <v>-29.458</v>
       </c>
       <c r="D49" t="n">
-        <v>-47.322</v>
+        <v>-51.813</v>
       </c>
       <c r="E49" t="n">
-        <v>187.742</v>
+        <v>188.872</v>
       </c>
       <c r="F49" t="n">
-        <v>-39.591</v>
+        <v>-32.661</v>
       </c>
       <c r="G49" t="n">
-        <v>-45.33</v>
+        <v>-49.517</v>
       </c>
       <c r="H49" t="n">
-        <v>187.742</v>
+        <v>188.872</v>
       </c>
     </row>
     <row r="50">
@@ -1752,25 +1752,25 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>4086.711</v>
+        <v>4090.866</v>
       </c>
       <c r="C50" t="n">
-        <v>-29.629</v>
+        <v>-25.691</v>
       </c>
       <c r="D50" t="n">
-        <v>-38.779</v>
+        <v>-42.018</v>
       </c>
       <c r="E50" t="n">
-        <v>188.352</v>
+        <v>189.13</v>
       </c>
       <c r="F50" t="n">
-        <v>-38.882</v>
+        <v>-32.089</v>
       </c>
       <c r="G50" t="n">
-        <v>-45.726</v>
+        <v>-49.898</v>
       </c>
       <c r="H50" t="n">
-        <v>188.352</v>
+        <v>189.13</v>
       </c>
     </row>
     <row r="51">
@@ -1778,25 +1778,25 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>4182.142</v>
+        <v>4184.271</v>
       </c>
       <c r="C51" t="n">
-        <v>-25.515</v>
+        <v>-21.817</v>
       </c>
       <c r="D51" t="n">
-        <v>-31.845</v>
+        <v>-34.573</v>
       </c>
       <c r="E51" t="n">
-        <v>187.748</v>
+        <v>189.936</v>
       </c>
       <c r="F51" t="n">
-        <v>-38.893</v>
+        <v>-32.655</v>
       </c>
       <c r="G51" t="n">
-        <v>-49.181</v>
+        <v>-47.841</v>
       </c>
       <c r="H51" t="n">
-        <v>187.748</v>
+        <v>189.936</v>
       </c>
     </row>
     <row r="52">
@@ -1804,25 +1804,25 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>4282.096</v>
+        <v>4281.071</v>
       </c>
       <c r="C52" t="n">
-        <v>-21.207</v>
+        <v>-17.803</v>
       </c>
       <c r="D52" t="n">
-        <v>-26.058</v>
+        <v>-25.43</v>
       </c>
       <c r="E52" t="n">
-        <v>189.889</v>
+        <v>190.069</v>
       </c>
       <c r="F52" t="n">
-        <v>-36.725</v>
+        <v>-33.072</v>
       </c>
       <c r="G52" t="n">
-        <v>-44.434</v>
+        <v>-46.673</v>
       </c>
       <c r="H52" t="n">
-        <v>189.889</v>
+        <v>190.069</v>
       </c>
     </row>
     <row r="53">
@@ -1830,25 +1830,25 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>4374.092</v>
+        <v>4376.805</v>
       </c>
       <c r="C53" t="n">
-        <v>-17.242</v>
+        <v>-13.832</v>
       </c>
       <c r="D53" t="n">
-        <v>-16.73</v>
+        <v>-17.362</v>
       </c>
       <c r="E53" t="n">
-        <v>192.753</v>
+        <v>193.048</v>
       </c>
       <c r="F53" t="n">
-        <v>-33.07</v>
+        <v>-28.425</v>
       </c>
       <c r="G53" t="n">
-        <v>-37.125</v>
+        <v>-39.38</v>
       </c>
       <c r="H53" t="n">
-        <v>192.753</v>
+        <v>193.048</v>
       </c>
     </row>
     <row r="54">
@@ -1856,25 +1856,25 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>4470.101</v>
+        <v>4472.564</v>
       </c>
       <c r="C54" t="n">
-        <v>-13.104</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-8.038</v>
+        <v>-8.364000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>195.119</v>
+        <v>195.728</v>
       </c>
       <c r="F54" t="n">
-        <v>-29.584</v>
+        <v>-24.36</v>
       </c>
       <c r="G54" t="n">
-        <v>-27.73</v>
+        <v>-29.964</v>
       </c>
       <c r="H54" t="n">
-        <v>195.119</v>
+        <v>195.728</v>
       </c>
     </row>
     <row r="55">
@@ -1882,25 +1882,25 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>4565.888</v>
+        <v>4568.256</v>
       </c>
       <c r="C55" t="n">
-        <v>-8.975</v>
+        <v>-5.892</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.577</v>
+        <v>-1.585</v>
       </c>
       <c r="E55" t="n">
-        <v>197.154</v>
+        <v>197.579</v>
       </c>
       <c r="F55" t="n">
-        <v>-22.405</v>
+        <v>-18.055</v>
       </c>
       <c r="G55" t="n">
-        <v>-18.138</v>
+        <v>-20.329</v>
       </c>
       <c r="H55" t="n">
-        <v>197.154</v>
+        <v>197.579</v>
       </c>
     </row>
     <row r="56">
@@ -1908,25 +1908,25 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>4662.748</v>
+        <v>4665.644</v>
       </c>
       <c r="C56" t="n">
-        <v>-8.791</v>
+        <v>-5.719</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.254</v>
+        <v>-1.18</v>
       </c>
       <c r="E56" t="n">
-        <v>197.727</v>
+        <v>198.293</v>
       </c>
       <c r="F56" t="n">
-        <v>-18.729</v>
+        <v>-15.549</v>
       </c>
       <c r="G56" t="n">
-        <v>-10.991</v>
+        <v>-13.21</v>
       </c>
       <c r="H56" t="n">
-        <v>197.727</v>
+        <v>198.293</v>
       </c>
     </row>
     <row r="57">
@@ -1934,25 +1934,25 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>4758.809</v>
+        <v>4760.163</v>
       </c>
       <c r="C57" t="n">
-        <v>-8.507999999999999</v>
+        <v>-5.47</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.758</v>
+        <v>-0.597</v>
       </c>
       <c r="E57" t="n">
-        <v>198.006</v>
+        <v>198.263</v>
       </c>
       <c r="F57" t="n">
-        <v>-13.352</v>
+        <v>-8.484</v>
       </c>
       <c r="G57" t="n">
-        <v>-6.019</v>
+        <v>-8.634</v>
       </c>
       <c r="H57" t="n">
-        <v>198.006</v>
+        <v>198.263</v>
       </c>
     </row>
     <row r="58">
@@ -1960,25 +1960,25 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>4853.613</v>
+        <v>4857.755</v>
       </c>
       <c r="C58" t="n">
-        <v>-8.228999999999999</v>
+        <v>-5.213</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.27</v>
+        <v>0.005</v>
       </c>
       <c r="E58" t="n">
-        <v>198.047</v>
+        <v>198.88</v>
       </c>
       <c r="F58" t="n">
-        <v>-11.02</v>
+        <v>-5.761</v>
       </c>
       <c r="G58" t="n">
-        <v>-6.628</v>
+        <v>-3.268</v>
       </c>
       <c r="H58" t="n">
-        <v>198.047</v>
+        <v>198.88</v>
       </c>
     </row>
     <row r="59">
@@ -1986,25 +1986,25 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>4951.187</v>
+        <v>4951.609</v>
       </c>
       <c r="C59" t="n">
-        <v>-7.943</v>
+        <v>-4.966</v>
       </c>
       <c r="D59" t="n">
-        <v>0.233</v>
+        <v>0.584</v>
       </c>
       <c r="E59" t="n">
-        <v>196.704</v>
+        <v>199.122</v>
       </c>
       <c r="F59" t="n">
-        <v>-8.933</v>
+        <v>-3.156</v>
       </c>
       <c r="G59" t="n">
-        <v>-5.128</v>
+        <v>-0.504</v>
       </c>
       <c r="H59" t="n">
-        <v>196.704</v>
+        <v>199.122</v>
       </c>
     </row>
     <row r="60">
@@ -2012,25 +2012,25 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>5046.891</v>
+        <v>5049.992</v>
       </c>
       <c r="C60" t="n">
-        <v>-7.661</v>
+        <v>-4.707</v>
       </c>
       <c r="D60" t="n">
-        <v>0.726</v>
+        <v>1.191</v>
       </c>
       <c r="E60" t="n">
-        <v>196.422</v>
+        <v>198.814</v>
       </c>
       <c r="F60" t="n">
-        <v>-8.294</v>
+        <v>-2.951</v>
       </c>
       <c r="G60" t="n">
-        <v>-3.188</v>
+        <v>2.336</v>
       </c>
       <c r="H60" t="n">
-        <v>196.422</v>
+        <v>198.814</v>
       </c>
     </row>
     <row r="61">
@@ -2038,25 +2038,25 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>5144.891</v>
+        <v>5144.72</v>
       </c>
       <c r="C61" t="n">
-        <v>-7.036</v>
+        <v>-4.086</v>
       </c>
       <c r="D61" t="n">
-        <v>0.748</v>
+        <v>1.175</v>
       </c>
       <c r="E61" t="n">
-        <v>196.662</v>
+        <v>198.178</v>
       </c>
       <c r="F61" t="n">
-        <v>-4.65</v>
+        <v>0.556</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.597</v>
+        <v>7.467</v>
       </c>
       <c r="H61" t="n">
-        <v>196.662</v>
+        <v>198.178</v>
       </c>
     </row>
     <row r="62">
@@ -2064,25 +2064,25 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>5238.943</v>
+        <v>5240.028</v>
       </c>
       <c r="C62" t="n">
-        <v>-5.727</v>
+        <v>-2.764</v>
       </c>
       <c r="D62" t="n">
-        <v>0.795</v>
+        <v>1.142</v>
       </c>
       <c r="E62" t="n">
-        <v>196.478</v>
+        <v>197.945</v>
       </c>
       <c r="F62" t="n">
-        <v>-4.654</v>
+        <v>1.239</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.622</v>
+        <v>10.321</v>
       </c>
       <c r="H62" t="n">
-        <v>196.478</v>
+        <v>197.945</v>
       </c>
     </row>
     <row r="63">
@@ -2090,25 +2090,25 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>5333.86</v>
+        <v>5337.165</v>
       </c>
       <c r="C63" t="n">
-        <v>-4.406</v>
+        <v>-1.416</v>
       </c>
       <c r="D63" t="n">
-        <v>0.843</v>
+        <v>1.109</v>
       </c>
       <c r="E63" t="n">
-        <v>196.375</v>
+        <v>196.42</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.093</v>
+        <v>1.971</v>
       </c>
       <c r="G63" t="n">
-        <v>2.189</v>
+        <v>11.884</v>
       </c>
       <c r="H63" t="n">
-        <v>196.375</v>
+        <v>196.42</v>
       </c>
     </row>
     <row r="64">
@@ -2116,25 +2116,25 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>5429.309999999999</v>
+        <v>5433.477</v>
       </c>
       <c r="C64" t="n">
-        <v>-3.077</v>
+        <v>-0.08</v>
       </c>
       <c r="D64" t="n">
-        <v>0.89</v>
+        <v>1.075</v>
       </c>
       <c r="E64" t="n">
-        <v>195.849</v>
+        <v>195.226</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.073</v>
+        <v>2.482</v>
       </c>
       <c r="G64" t="n">
-        <v>4.839</v>
+        <v>14.093</v>
       </c>
       <c r="H64" t="n">
-        <v>195.849</v>
+        <v>195.226</v>
       </c>
     </row>
     <row r="65">
@@ -2142,25 +2142,25 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>5525.474</v>
+        <v>5527.694</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.738</v>
+        <v>1.228</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.042</v>
       </c>
       <c r="E65" t="n">
-        <v>195.618</v>
+        <v>194.785</v>
       </c>
       <c r="F65" t="n">
-        <v>1.979</v>
+        <v>2.958</v>
       </c>
       <c r="G65" t="n">
-        <v>4.693</v>
+        <v>11.609</v>
       </c>
       <c r="H65" t="n">
-        <v>195.618</v>
+        <v>194.785</v>
       </c>
     </row>
     <row r="66">
@@ -2168,25 +2168,25 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>5622.442</v>
+        <v>5623.644</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.389</v>
+        <v>2.559</v>
       </c>
       <c r="D66" t="n">
-        <v>0.986</v>
+        <v>1.009</v>
       </c>
       <c r="E66" t="n">
-        <v>195.37</v>
+        <v>194.705</v>
       </c>
       <c r="F66" t="n">
-        <v>2.475</v>
+        <v>3.315</v>
       </c>
       <c r="G66" t="n">
-        <v>4.525</v>
+        <v>6.079</v>
       </c>
       <c r="H66" t="n">
-        <v>195.37</v>
+        <v>194.705</v>
       </c>
     </row>
     <row r="67">
@@ -2194,25 +2194,25 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>5717.386</v>
+        <v>5719.852</v>
       </c>
       <c r="C67" t="n">
-        <v>1.19</v>
+        <v>4.193</v>
       </c>
       <c r="D67" t="n">
-        <v>-4.139</v>
+        <v>-4.315</v>
       </c>
       <c r="E67" t="n">
-        <v>194.989</v>
+        <v>194.31</v>
       </c>
       <c r="F67" t="n">
-        <v>3.218</v>
+        <v>4.055</v>
       </c>
       <c r="G67" t="n">
-        <v>4.69</v>
+        <v>0.903</v>
       </c>
       <c r="H67" t="n">
-        <v>194.989</v>
+        <v>194.31</v>
       </c>
     </row>
     <row r="68">
@@ -2220,25 +2220,25 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>5813.393</v>
+        <v>5815.17</v>
       </c>
       <c r="C68" t="n">
-        <v>3.439</v>
+        <v>6.423</v>
       </c>
       <c r="D68" t="n">
-        <v>-11.441</v>
+        <v>-11.58</v>
       </c>
       <c r="E68" t="n">
-        <v>194.541</v>
+        <v>193.691</v>
       </c>
       <c r="F68" t="n">
-        <v>3.801</v>
+        <v>6.975</v>
       </c>
       <c r="G68" t="n">
-        <v>5.234</v>
+        <v>-7.025</v>
       </c>
       <c r="H68" t="n">
-        <v>194.541</v>
+        <v>193.691</v>
       </c>
     </row>
     <row r="69">
@@ -2246,25 +2246,25 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>5909.631</v>
+        <v>5911.943</v>
       </c>
       <c r="C69" t="n">
-        <v>5.693</v>
+        <v>8.686999999999999</v>
       </c>
       <c r="D69" t="n">
-        <v>-18.76</v>
+        <v>-18.955</v>
       </c>
       <c r="E69" t="n">
-        <v>194.16</v>
+        <v>193.857</v>
       </c>
       <c r="F69" t="n">
-        <v>4.068</v>
+        <v>4.564</v>
       </c>
       <c r="G69" t="n">
-        <v>0.483</v>
+        <v>-11.363</v>
       </c>
       <c r="H69" t="n">
-        <v>194.16</v>
+        <v>193.857</v>
       </c>
     </row>
     <row r="70">
@@ -2275,22 +2275,22 @@
         <v>6000</v>
       </c>
       <c r="C70" t="n">
-        <v>7.946</v>
+        <v>10.932</v>
       </c>
       <c r="D70" t="n">
-        <v>-26.076</v>
+        <v>-26.27</v>
       </c>
       <c r="E70" t="n">
-        <v>193.54</v>
+        <v>193.638</v>
       </c>
       <c r="F70" t="n">
-        <v>4.74</v>
+        <v>5.235</v>
       </c>
       <c r="G70" t="n">
-        <v>-3.902</v>
+        <v>-10.695</v>
       </c>
       <c r="H70" t="n">
-        <v>193.54</v>
+        <v>193.638</v>
       </c>
     </row>
     <row r="71">
@@ -2301,22 +2301,22 @@
         <v>6000</v>
       </c>
       <c r="C71" t="n">
-        <v>10.19</v>
+        <v>13.188</v>
       </c>
       <c r="D71" t="n">
-        <v>-33.361</v>
+        <v>-33.621</v>
       </c>
       <c r="E71" t="n">
-        <v>190.256</v>
+        <v>190.648</v>
       </c>
       <c r="F71" t="n">
-        <v>-28.877</v>
+        <v>-28.899</v>
       </c>
       <c r="G71" t="n">
-        <v>51.879</v>
+        <v>47.373</v>
       </c>
       <c r="H71" t="n">
-        <v>190.256</v>
+        <v>190.648</v>
       </c>
     </row>
     <row r="72">
@@ -2324,25 +2324,25 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>6000.069</v>
+        <v>6000.05</v>
       </c>
       <c r="C72" t="n">
-        <v>-28.874</v>
+        <v>-28.897</v>
       </c>
       <c r="D72" t="n">
-        <v>51.873</v>
+        <v>47.369</v>
       </c>
       <c r="E72" t="n">
-        <v>189.073</v>
+        <v>189.486</v>
       </c>
       <c r="F72" t="n">
-        <v>-32.061</v>
+        <v>-32.421</v>
       </c>
       <c r="G72" t="n">
-        <v>49.936</v>
+        <v>46.2</v>
       </c>
       <c r="H72" t="n">
-        <v>189.073</v>
+        <v>189.486</v>
       </c>
     </row>
     <row r="73">
@@ -2350,25 +2350,25 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>6087.934</v>
+        <v>6088.906</v>
       </c>
       <c r="C73" t="n">
-        <v>-25.672</v>
+        <v>-25.221</v>
       </c>
       <c r="D73" t="n">
-        <v>42.618</v>
+        <v>39.354</v>
       </c>
       <c r="E73" t="n">
-        <v>189.406</v>
+        <v>189.373</v>
       </c>
       <c r="F73" t="n">
-        <v>-31.864</v>
+        <v>-32.253</v>
       </c>
       <c r="G73" t="n">
-        <v>50.323</v>
+        <v>46.548</v>
       </c>
       <c r="H73" t="n">
-        <v>189.406</v>
+        <v>189.373</v>
       </c>
     </row>
     <row r="74">
@@ -2376,25 +2376,25 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>6187.979</v>
+        <v>6183.284</v>
       </c>
       <c r="C74" t="n">
-        <v>-22.025</v>
+        <v>-21.316</v>
       </c>
       <c r="D74" t="n">
-        <v>34.557</v>
+        <v>32.329</v>
       </c>
       <c r="E74" t="n">
-        <v>189.251</v>
+        <v>189.718</v>
       </c>
       <c r="F74" t="n">
-        <v>-31.91</v>
+        <v>-32.29</v>
       </c>
       <c r="G74" t="n">
-        <v>51.021</v>
+        <v>46.923</v>
       </c>
       <c r="H74" t="n">
-        <v>189.251</v>
+        <v>189.718</v>
       </c>
     </row>
     <row r="75">
@@ -2402,25 +2402,25 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>6280.591</v>
+        <v>6280.966</v>
       </c>
       <c r="C75" t="n">
-        <v>-18.649</v>
+        <v>-17.275</v>
       </c>
       <c r="D75" t="n">
-        <v>27.161</v>
+        <v>24.95</v>
       </c>
       <c r="E75" t="n">
-        <v>190.97</v>
+        <v>190.779</v>
       </c>
       <c r="F75" t="n">
-        <v>-32.477</v>
+        <v>-30.453</v>
       </c>
       <c r="G75" t="n">
-        <v>46.189</v>
+        <v>42.635</v>
       </c>
       <c r="H75" t="n">
-        <v>190.97</v>
+        <v>190.779</v>
       </c>
     </row>
     <row r="76">
@@ -2428,25 +2428,25 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>6374.907</v>
+        <v>6375.854</v>
       </c>
       <c r="C76" t="n">
-        <v>-15.21</v>
+        <v>-13.349</v>
       </c>
       <c r="D76" t="n">
-        <v>17.328</v>
+        <v>15.927</v>
       </c>
       <c r="E76" t="n">
-        <v>193.033</v>
+        <v>193.513</v>
       </c>
       <c r="F76" t="n">
-        <v>-31.046</v>
+        <v>-28.438</v>
       </c>
       <c r="G76" t="n">
-        <v>37.516</v>
+        <v>35.624</v>
       </c>
       <c r="H76" t="n">
-        <v>193.033</v>
+        <v>193.513</v>
       </c>
     </row>
     <row r="77">
@@ -2454,25 +2454,25 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>6471.025</v>
+        <v>6471.095</v>
       </c>
       <c r="C77" t="n">
-        <v>-11.707</v>
+        <v>-9.407999999999999</v>
       </c>
       <c r="D77" t="n">
-        <v>8.064</v>
+        <v>7.654</v>
       </c>
       <c r="E77" t="n">
-        <v>196.221</v>
+        <v>195.094</v>
       </c>
       <c r="F77" t="n">
-        <v>-26.605</v>
+        <v>-24.982</v>
       </c>
       <c r="G77" t="n">
-        <v>27.481</v>
+        <v>26.77</v>
       </c>
       <c r="H77" t="n">
-        <v>196.221</v>
+        <v>195.094</v>
       </c>
     </row>
     <row r="78">
@@ -2480,25 +2480,25 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>6567.58</v>
+        <v>6568.388</v>
       </c>
       <c r="C78" t="n">
-        <v>-8.186999999999999</v>
+        <v>-5.383</v>
       </c>
       <c r="D78" t="n">
-        <v>1.485</v>
+        <v>1.41</v>
       </c>
       <c r="E78" t="n">
-        <v>197.213</v>
+        <v>197.487</v>
       </c>
       <c r="F78" t="n">
-        <v>-25.764</v>
+        <v>-20.726</v>
       </c>
       <c r="G78" t="n">
-        <v>17.936</v>
+        <v>13.66</v>
       </c>
       <c r="H78" t="n">
-        <v>197.213</v>
+        <v>197.487</v>
       </c>
     </row>
     <row r="79">
@@ -2506,25 +2506,25 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>6668.146</v>
+        <v>6663.269</v>
       </c>
       <c r="C79" t="n">
-        <v>-8.026</v>
+        <v>-5.217</v>
       </c>
       <c r="D79" t="n">
-        <v>1.283</v>
+        <v>1.421</v>
       </c>
       <c r="E79" t="n">
-        <v>198.094</v>
+        <v>197.405</v>
       </c>
       <c r="F79" t="n">
-        <v>-21.161</v>
+        <v>-16.168</v>
       </c>
       <c r="G79" t="n">
-        <v>10.754</v>
+        <v>7.177</v>
       </c>
       <c r="H79" t="n">
-        <v>198.094</v>
+        <v>197.405</v>
       </c>
     </row>
     <row r="80">
@@ -2532,25 +2532,25 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>6759.25</v>
+        <v>6759.319</v>
       </c>
       <c r="C80" t="n">
-        <v>-7.811</v>
+        <v>-4.966</v>
       </c>
       <c r="D80" t="n">
-        <v>1.012</v>
+        <v>1.439</v>
       </c>
       <c r="E80" t="n">
-        <v>198.822</v>
+        <v>196.836</v>
       </c>
       <c r="F80" t="n">
-        <v>-16.141</v>
+        <v>-14.081</v>
       </c>
       <c r="G80" t="n">
-        <v>3.058</v>
+        <v>5.28</v>
       </c>
       <c r="H80" t="n">
-        <v>198.822</v>
+        <v>196.836</v>
       </c>
     </row>
     <row r="81">
@@ -2558,25 +2558,25 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>6854.949</v>
+        <v>6854.836</v>
       </c>
       <c r="C81" t="n">
-        <v>-7.584</v>
+        <v>-4.716</v>
       </c>
       <c r="D81" t="n">
-        <v>0.728</v>
+        <v>1.456</v>
       </c>
       <c r="E81" t="n">
-        <v>198.491</v>
+        <v>197.261</v>
       </c>
       <c r="F81" t="n">
-        <v>-14.713</v>
+        <v>-6.708</v>
       </c>
       <c r="G81" t="n">
-        <v>-2.431</v>
+        <v>2.52</v>
       </c>
       <c r="H81" t="n">
-        <v>198.491</v>
+        <v>197.261</v>
       </c>
     </row>
     <row r="82">
@@ -2584,25 +2584,25 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>6951.194</v>
+        <v>6950.765</v>
       </c>
       <c r="C82" t="n">
-        <v>-7.357</v>
+        <v>-4.465</v>
       </c>
       <c r="D82" t="n">
-        <v>0.442</v>
+        <v>1.473</v>
       </c>
       <c r="E82" t="n">
-        <v>198.117</v>
+        <v>196.801</v>
       </c>
       <c r="F82" t="n">
-        <v>-12.661</v>
+        <v>-4.453</v>
       </c>
       <c r="G82" t="n">
-        <v>-8.302</v>
+        <v>2.616</v>
       </c>
       <c r="H82" t="n">
-        <v>198.117</v>
+        <v>196.801</v>
       </c>
     </row>
     <row r="83">
@@ -2610,25 +2610,25 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>7047.262</v>
+        <v>7047.264</v>
       </c>
       <c r="C83" t="n">
-        <v>-7.13</v>
+        <v>-4.213</v>
       </c>
       <c r="D83" t="n">
-        <v>0.157</v>
+        <v>1.491</v>
       </c>
       <c r="E83" t="n">
-        <v>197.8</v>
+        <v>196.886</v>
       </c>
       <c r="F83" t="n">
-        <v>-9.965999999999999</v>
+        <v>-3.82</v>
       </c>
       <c r="G83" t="n">
-        <v>-8.532</v>
+        <v>2.565</v>
       </c>
       <c r="H83" t="n">
-        <v>197.8</v>
+        <v>196.886</v>
       </c>
     </row>
     <row r="84">
@@ -2636,25 +2636,25 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>7143.907</v>
+        <v>7143.332</v>
       </c>
       <c r="C84" t="n">
-        <v>-6.521</v>
+        <v>-3.611</v>
       </c>
       <c r="D84" t="n">
-        <v>0.144</v>
+        <v>1.452</v>
       </c>
       <c r="E84" t="n">
-        <v>197.921</v>
+        <v>196.041</v>
       </c>
       <c r="F84" t="n">
-        <v>-3.99</v>
+        <v>1.875</v>
       </c>
       <c r="G84" t="n">
-        <v>-8.945</v>
+        <v>3.32</v>
       </c>
       <c r="H84" t="n">
-        <v>197.921</v>
+        <v>196.041</v>
       </c>
     </row>
     <row r="85">
@@ -2662,25 +2662,25 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>7238.975</v>
+        <v>7238.896</v>
       </c>
       <c r="C85" t="n">
-        <v>-5.203</v>
+        <v>-2.284</v>
       </c>
       <c r="D85" t="n">
-        <v>0.117</v>
+        <v>1.367</v>
       </c>
       <c r="E85" t="n">
-        <v>196.406</v>
+        <v>196.052</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.195</v>
+        <v>2.411</v>
       </c>
       <c r="G85" t="n">
-        <v>-7.591</v>
+        <v>3.311</v>
       </c>
       <c r="H85" t="n">
-        <v>196.406</v>
+        <v>196.052</v>
       </c>
     </row>
     <row r="86">
@@ -2688,25 +2688,25 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>7335.602</v>
+        <v>7336.735</v>
       </c>
       <c r="C86" t="n">
-        <v>-3.864</v>
+        <v>-0.925</v>
       </c>
       <c r="D86" t="n">
-        <v>0.09</v>
+        <v>1.28</v>
       </c>
       <c r="E86" t="n">
-        <v>195.553</v>
+        <v>196.005</v>
       </c>
       <c r="F86" t="n">
-        <v>5.091</v>
+        <v>5.935</v>
       </c>
       <c r="G86" t="n">
-        <v>-4.149</v>
+        <v>3.684</v>
       </c>
       <c r="H86" t="n">
-        <v>195.553</v>
+        <v>196.005</v>
       </c>
     </row>
     <row r="87">
@@ -2714,25 +2714,25 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>7430.824000000001</v>
+        <v>7431.293</v>
       </c>
       <c r="C87" t="n">
-        <v>-2.544</v>
+        <v>0.388</v>
       </c>
       <c r="D87" t="n">
-        <v>0.063</v>
+        <v>1.195</v>
       </c>
       <c r="E87" t="n">
-        <v>195.116</v>
+        <v>195.683</v>
       </c>
       <c r="F87" t="n">
-        <v>5.956</v>
+        <v>6.8</v>
       </c>
       <c r="G87" t="n">
-        <v>-1.411</v>
+        <v>3.867</v>
       </c>
       <c r="H87" t="n">
-        <v>195.116</v>
+        <v>195.683</v>
       </c>
     </row>
     <row r="88">
@@ -2740,25 +2740,25 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>7527.488</v>
+        <v>7527.440000000001</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.203</v>
+        <v>1.723</v>
       </c>
       <c r="D88" t="n">
-        <v>0.035</v>
+        <v>1.109</v>
       </c>
       <c r="E88" t="n">
-        <v>194.777</v>
+        <v>195.5</v>
       </c>
       <c r="F88" t="n">
-        <v>6.622</v>
+        <v>7.442</v>
       </c>
       <c r="G88" t="n">
-        <v>4.434</v>
+        <v>1.134</v>
       </c>
       <c r="H88" t="n">
-        <v>194.777</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="89">
@@ -2766,25 +2766,25 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>7623.608</v>
+        <v>7623.703</v>
       </c>
       <c r="C89" t="n">
-        <v>0.129</v>
+        <v>3.06</v>
       </c>
       <c r="D89" t="n">
-        <v>0.008</v>
+        <v>1.023</v>
       </c>
       <c r="E89" t="n">
-        <v>194.243</v>
+        <v>195.415</v>
       </c>
       <c r="F89" t="n">
-        <v>7.453</v>
+        <v>7.931</v>
       </c>
       <c r="G89" t="n">
-        <v>10.247</v>
+        <v>1.588</v>
       </c>
       <c r="H89" t="n">
-        <v>194.243</v>
+        <v>195.415</v>
       </c>
     </row>
     <row r="90">
@@ -2792,25 +2792,25 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>7720.135</v>
+        <v>7719.762</v>
       </c>
       <c r="C90" t="n">
-        <v>1.77</v>
+        <v>4.692</v>
       </c>
       <c r="D90" t="n">
-        <v>4.323</v>
+        <v>5.448</v>
       </c>
       <c r="E90" t="n">
-        <v>194.231</v>
+        <v>195.097</v>
       </c>
       <c r="F90" t="n">
-        <v>5.069</v>
+        <v>9.144</v>
       </c>
       <c r="G90" t="n">
-        <v>10.279</v>
+        <v>-7.234</v>
       </c>
       <c r="H90" t="n">
-        <v>194.231</v>
+        <v>195.097</v>
       </c>
     </row>
     <row r="91">
@@ -2818,25 +2818,25 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>7815.494</v>
+        <v>7815.735</v>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>6.937</v>
       </c>
       <c r="D91" t="n">
-        <v>10.189</v>
+        <v>11.536</v>
       </c>
       <c r="E91" t="n">
-        <v>194.588</v>
+        <v>194.394</v>
       </c>
       <c r="F91" t="n">
-        <v>6.528</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="G91" t="n">
-        <v>4.59</v>
+        <v>-10.565</v>
       </c>
       <c r="H91" t="n">
-        <v>194.588</v>
+        <v>194.394</v>
       </c>
     </row>
     <row r="92">
@@ -2844,25 +2844,25 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>7911.119</v>
+        <v>7911.575</v>
       </c>
       <c r="C92" t="n">
-        <v>6.237</v>
+        <v>9.178000000000001</v>
       </c>
       <c r="D92" t="n">
-        <v>16.072</v>
+        <v>17.615</v>
       </c>
       <c r="E92" t="n">
-        <v>194.459</v>
+        <v>193.835</v>
       </c>
       <c r="F92" t="n">
-        <v>6.794</v>
+        <v>9.991</v>
       </c>
       <c r="G92" t="n">
-        <v>4.263</v>
+        <v>-11.459</v>
       </c>
       <c r="H92" t="n">
-        <v>194.459</v>
+        <v>193.835</v>
       </c>
     </row>
     <row r="93">
@@ -2873,22 +2873,22 @@
         <v>8000</v>
       </c>
       <c r="C93" t="n">
-        <v>8.542</v>
+        <v>11.43</v>
       </c>
       <c r="D93" t="n">
-        <v>22.134</v>
+        <v>23.721</v>
       </c>
       <c r="E93" t="n">
-        <v>194.158</v>
+        <v>193.357</v>
       </c>
       <c r="F93" t="n">
-        <v>7.464</v>
+        <v>10.624</v>
       </c>
       <c r="G93" t="n">
-        <v>3.627</v>
+        <v>-7.356</v>
       </c>
       <c r="H93" t="n">
-        <v>194.158</v>
+        <v>193.357</v>
       </c>
     </row>
     <row r="94">
@@ -2899,22 +2899,22 @@
         <v>8000</v>
       </c>
       <c r="C94" t="n">
-        <v>10.823</v>
+        <v>13.671</v>
       </c>
       <c r="D94" t="n">
-        <v>28.132</v>
+        <v>29.797</v>
       </c>
       <c r="E94" t="n">
-        <v>189.175</v>
+        <v>190.223</v>
       </c>
       <c r="F94" t="n">
-        <v>-30.642</v>
+        <v>-32.536</v>
       </c>
       <c r="G94" t="n">
-        <v>-54.6</v>
+        <v>-47.311</v>
       </c>
       <c r="H94" t="n">
-        <v>189.175</v>
+        <v>190.223</v>
       </c>
     </row>
     <row r="95">
@@ -2922,25 +2922,25 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>8000.047</v>
+        <v>8000.046</v>
       </c>
       <c r="C95" t="n">
-        <v>-30.64</v>
+        <v>-32.534</v>
       </c>
       <c r="D95" t="n">
-        <v>-54.596</v>
+        <v>-47.307</v>
       </c>
       <c r="E95" t="n">
-        <v>187.503</v>
+        <v>188.361</v>
       </c>
       <c r="F95" t="n">
-        <v>-34.899</v>
+        <v>-37.418</v>
       </c>
       <c r="G95" t="n">
-        <v>-51.843</v>
+        <v>-45.727</v>
       </c>
       <c r="H95" t="n">
-        <v>187.503</v>
+        <v>188.361</v>
       </c>
     </row>
     <row r="96">
@@ -2948,25 +2948,25 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>8087.161</v>
+        <v>8087.15</v>
       </c>
       <c r="C96" t="n">
-        <v>-27.281</v>
+        <v>-28.475</v>
       </c>
       <c r="D96" t="n">
-        <v>-44.312</v>
+        <v>-39.085</v>
       </c>
       <c r="E96" t="n">
-        <v>187.749</v>
+        <v>188.927</v>
       </c>
       <c r="F96" t="n">
-        <v>-34.331</v>
+        <v>-36.318</v>
       </c>
       <c r="G96" t="n">
-        <v>-52.228</v>
+        <v>-46.119</v>
       </c>
       <c r="H96" t="n">
-        <v>187.749</v>
+        <v>188.927</v>
       </c>
     </row>
     <row r="97">
@@ -2974,25 +2974,25 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>8183.743</v>
+        <v>8183.501</v>
       </c>
       <c r="C97" t="n">
-        <v>-23.557</v>
+        <v>-23.985</v>
       </c>
       <c r="D97" t="n">
-        <v>-36.234</v>
+        <v>-32.014</v>
       </c>
       <c r="E97" t="n">
-        <v>187.841</v>
+        <v>188.802</v>
       </c>
       <c r="F97" t="n">
-        <v>-34.153</v>
+        <v>-36.714</v>
       </c>
       <c r="G97" t="n">
-        <v>-52.952</v>
+        <v>-46.466</v>
       </c>
       <c r="H97" t="n">
-        <v>187.841</v>
+        <v>188.802</v>
       </c>
     </row>
     <row r="98">
@@ -3000,25 +3000,25 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>8279.883</v>
+        <v>8279.832</v>
       </c>
       <c r="C98" t="n">
-        <v>-19.849</v>
+        <v>-19.495</v>
       </c>
       <c r="D98" t="n">
-        <v>-28.251</v>
+        <v>-24.795</v>
       </c>
       <c r="E98" t="n">
-        <v>189.259</v>
+        <v>190.288</v>
       </c>
       <c r="F98" t="n">
-        <v>-35.293</v>
+        <v>-34.876</v>
       </c>
       <c r="G98" t="n">
-        <v>-48.495</v>
+        <v>-44.448</v>
       </c>
       <c r="H98" t="n">
-        <v>189.259</v>
+        <v>190.288</v>
       </c>
     </row>
     <row r="99">
@@ -3026,25 +3026,1091 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>8376.395</v>
+        <v>8376.334999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>-16.128</v>
+        <v>-14.998</v>
       </c>
       <c r="D99" t="n">
-        <v>-18.073</v>
+        <v>-16.569</v>
       </c>
       <c r="E99" t="n">
-        <v>189.918</v>
+        <v>192.329</v>
       </c>
       <c r="F99" t="n">
-        <v>6.81</v>
+        <v>-31.046</v>
       </c>
       <c r="G99" t="n">
-        <v>31.657</v>
+        <v>-37.7</v>
       </c>
       <c r="H99" t="n">
-        <v>189.918</v>
+        <v>192.329</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="n">
+        <v>8478.962</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-10.216</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-7.605</v>
+      </c>
+      <c r="E100" t="n">
+        <v>194.638</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-27.553</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-28.33</v>
+      </c>
+      <c r="H100" t="n">
+        <v>194.638</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="n">
+        <v>8569.421</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-6</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-1.444</v>
+      </c>
+      <c r="E101" t="n">
+        <v>196.675</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-20.542</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-18.744</v>
+      </c>
+      <c r="H101" t="n">
+        <v>196.675</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="n">
+        <v>8664.174999999999</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-5.817</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-1.066</v>
+      </c>
+      <c r="E102" t="n">
+        <v>198.011</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-16.145</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-10.934</v>
+      </c>
+      <c r="H102" t="n">
+        <v>198.011</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="n">
+        <v>8760.638999999999</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-5.542</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-0.498</v>
+      </c>
+      <c r="E103" t="n">
+        <v>197.681</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-11.836</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-6.447</v>
+      </c>
+      <c r="H103" t="n">
+        <v>197.681</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="n">
+        <v>8856.246999999999</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E104" t="n">
+        <v>196.258</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-6.364</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-5.851</v>
+      </c>
+      <c r="H104" t="n">
+        <v>196.258</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="n">
+        <v>8951.618</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-4.998</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="E105" t="n">
+        <v>196.521</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-3.753</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="H105" t="n">
+        <v>196.521</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="n">
+        <v>9055.825000000001</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-4.701</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E106" t="n">
+        <v>196.505</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.862</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-0.611</v>
+      </c>
+      <c r="H106" t="n">
+        <v>196.505</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="n">
+        <v>9149.08</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="E107" t="n">
+        <v>196.393</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2.751</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2.217</v>
+      </c>
+      <c r="H107" t="n">
+        <v>196.393</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="n">
+        <v>9240.065000000001</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-2.759</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="E108" t="n">
+        <v>196.312</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3.096</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1.866</v>
+      </c>
+      <c r="H108" t="n">
+        <v>196.312</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="n">
+        <v>9336.73</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-1.419</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="E109" t="n">
+        <v>196.026</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="H109" t="n">
+        <v>196.026</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="n">
+        <v>9432.421</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.092</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="E110" t="n">
+        <v>195.753</v>
+      </c>
+      <c r="F110" t="n">
+        <v>4.736</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4.812</v>
+      </c>
+      <c r="H110" t="n">
+        <v>195.753</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="n">
+        <v>9528.442999999999</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="E111" t="n">
+        <v>195.355</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5.215</v>
+      </c>
+      <c r="G111" t="n">
+        <v>7.479</v>
+      </c>
+      <c r="H111" t="n">
+        <v>195.355</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="n">
+        <v>9624.414000000001</v>
+      </c>
+      <c r="C112" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="E112" t="n">
+        <v>195.059</v>
+      </c>
+      <c r="F112" t="n">
+        <v>6.396</v>
+      </c>
+      <c r="G112" t="n">
+        <v>10.594</v>
+      </c>
+      <c r="H112" t="n">
+        <v>195.059</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="n">
+        <v>9721.25</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4.235</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-4.42</v>
+      </c>
+      <c r="E113" t="n">
+        <v>194.464</v>
+      </c>
+      <c r="F113" t="n">
+        <v>9.651</v>
+      </c>
+      <c r="G113" t="n">
+        <v>10.662</v>
+      </c>
+      <c r="H113" t="n">
+        <v>194.464</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="n">
+        <v>9816.454</v>
+      </c>
+      <c r="C114" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-11.676</v>
+      </c>
+      <c r="E114" t="n">
+        <v>194.285</v>
+      </c>
+      <c r="F114" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="G114" t="n">
+        <v>5.879</v>
+      </c>
+      <c r="H114" t="n">
+        <v>194.285</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="n">
+        <v>9912.213</v>
+      </c>
+      <c r="C115" t="n">
+        <v>8.699</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-18.975</v>
+      </c>
+      <c r="E115" t="n">
+        <v>193.742</v>
+      </c>
+      <c r="F115" t="n">
+        <v>10.481</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3.935</v>
+      </c>
+      <c r="H115" t="n">
+        <v>193.742</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C116" t="n">
+        <v>10.957</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-26.339</v>
+      </c>
+      <c r="E116" t="n">
+        <v>193.325</v>
+      </c>
+      <c r="F116" t="n">
+        <v>8.433999999999999</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-6.037</v>
+      </c>
+      <c r="H116" t="n">
+        <v>193.325</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C117" t="n">
+        <v>13.212</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-33.695</v>
+      </c>
+      <c r="E117" t="n">
+        <v>189.976</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-35.611</v>
+      </c>
+      <c r="G117" t="n">
+        <v>47.328</v>
+      </c>
+      <c r="H117" t="n">
+        <v>189.976</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="n">
+        <v>10000.077</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-35.607</v>
+      </c>
+      <c r="D118" t="n">
+        <v>47.322</v>
+      </c>
+      <c r="E118" t="n">
+        <v>186.74</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-41.938</v>
+      </c>
+      <c r="G118" t="n">
+        <v>46.582</v>
+      </c>
+      <c r="H118" t="n">
+        <v>186.74</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="n">
+        <v>10088.096</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-30.981</v>
+      </c>
+      <c r="D119" t="n">
+        <v>39.743</v>
+      </c>
+      <c r="E119" t="n">
+        <v>187.877</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-41.07</v>
+      </c>
+      <c r="G119" t="n">
+        <v>46.441</v>
+      </c>
+      <c r="H119" t="n">
+        <v>187.877</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="n">
+        <v>10185.249</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-25.874</v>
+      </c>
+      <c r="D120" t="n">
+        <v>32.102</v>
+      </c>
+      <c r="E120" t="n">
+        <v>188.321</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-41.099</v>
+      </c>
+      <c r="G120" t="n">
+        <v>44.961</v>
+      </c>
+      <c r="H120" t="n">
+        <v>188.321</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="n">
+        <v>10280.491</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-20.868</v>
+      </c>
+      <c r="D121" t="n">
+        <v>23.942</v>
+      </c>
+      <c r="E121" t="n">
+        <v>190.096</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-39.494</v>
+      </c>
+      <c r="G121" t="n">
+        <v>40.174</v>
+      </c>
+      <c r="H121" t="n">
+        <v>190.096</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="n">
+        <v>10377.384</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-15.776</v>
+      </c>
+      <c r="D122" t="n">
+        <v>14.906</v>
+      </c>
+      <c r="E122" t="n">
+        <v>192.517</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-35.49</v>
+      </c>
+      <c r="G122" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="H122" t="n">
+        <v>192.517</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="n">
+        <v>10472.315</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-10.786</v>
+      </c>
+      <c r="D123" t="n">
+        <v>7.184</v>
+      </c>
+      <c r="E123" t="n">
+        <v>194.813</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-32.224</v>
+      </c>
+      <c r="G123" t="n">
+        <v>24.342</v>
+      </c>
+      <c r="H123" t="n">
+        <v>194.813</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="n">
+        <v>10568.469</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-5.732</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="E124" t="n">
+        <v>197.081</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-25.979</v>
+      </c>
+      <c r="G124" t="n">
+        <v>13.726</v>
+      </c>
+      <c r="H124" t="n">
+        <v>197.081</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="n">
+        <v>10663.981</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-5.52</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="E125" t="n">
+        <v>196.576</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="G125" t="n">
+        <v>7.892</v>
+      </c>
+      <c r="H125" t="n">
+        <v>196.576</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="n">
+        <v>10760.822</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-5.199</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E126" t="n">
+        <v>197.268</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-9.316000000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>5.152</v>
+      </c>
+      <c r="H126" t="n">
+        <v>197.268</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" t="n">
+        <v>10856.714</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-4.881</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1.392</v>
+      </c>
+      <c r="E127" t="n">
+        <v>197.039</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-5.206</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H127" t="n">
+        <v>197.039</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" t="n">
+        <v>10954.448</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-4.557</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1.436</v>
+      </c>
+      <c r="E128" t="n">
+        <v>196.244</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-2.251</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3.308</v>
+      </c>
+      <c r="H128" t="n">
+        <v>196.244</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="n">
+        <v>11048.05</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-4.247</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="E129" t="n">
+        <v>196.118</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3.283</v>
+      </c>
+      <c r="H129" t="n">
+        <v>196.118</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="n">
+        <v>11143.939</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-3.634</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="E130" t="n">
+        <v>195.818</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3.585</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3.724</v>
+      </c>
+      <c r="H130" t="n">
+        <v>195.818</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="n">
+        <v>11239.687</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-2.298</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="E131" t="n">
+        <v>195.902</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4.305</v>
+      </c>
+      <c r="G131" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H131" t="n">
+        <v>195.902</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="n">
+        <v>11336.302</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.951</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="E132" t="n">
+        <v>195.686</v>
+      </c>
+      <c r="F132" t="n">
+        <v>5.565</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="H132" t="n">
+        <v>195.686</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="n">
+        <v>11431.309</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E133" t="n">
+        <v>195.343</v>
+      </c>
+      <c r="F133" t="n">
+        <v>9.013999999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H133" t="n">
+        <v>195.343</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="n">
+        <v>11527.577</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.717</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="E134" t="n">
+        <v>195.071</v>
+      </c>
+      <c r="F134" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="H134" t="n">
+        <v>195.071</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="n">
+        <v>11624.91</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.075</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="E135" t="n">
+        <v>194.847</v>
+      </c>
+      <c r="F135" t="n">
+        <v>10.141</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-1.445</v>
+      </c>
+      <c r="H135" t="n">
+        <v>194.847</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="n">
+        <v>11719.769</v>
+      </c>
+      <c r="C136" t="n">
+        <v>4.705</v>
+      </c>
+      <c r="D136" t="n">
+        <v>5.448</v>
+      </c>
+      <c r="E136" t="n">
+        <v>195.001</v>
+      </c>
+      <c r="F136" t="n">
+        <v>11.867</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-4.313</v>
+      </c>
+      <c r="H136" t="n">
+        <v>195.001</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="n">
+        <v>11816.453</v>
+      </c>
+      <c r="C137" t="n">
+        <v>6.964</v>
+      </c>
+      <c r="D137" t="n">
+        <v>11.581</v>
+      </c>
+      <c r="E137" t="n">
+        <v>194.396</v>
+      </c>
+      <c r="F137" t="n">
+        <v>12.429</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="H137" t="n">
+        <v>194.396</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" t="n">
+        <v>11911.416</v>
+      </c>
+      <c r="C138" t="n">
+        <v>9.183</v>
+      </c>
+      <c r="D138" t="n">
+        <v>17.604</v>
+      </c>
+      <c r="E138" t="n">
+        <v>193.807</v>
+      </c>
+      <c r="F138" t="n">
+        <v>13.203</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-8.563000000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>193.807</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C139" t="n">
+        <v>11.683</v>
+      </c>
+      <c r="D139" t="n">
+        <v>24.394</v>
+      </c>
+      <c r="E139" t="n">
+        <v>193.306</v>
+      </c>
+      <c r="F139" t="n">
+        <v>13.835</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-6.983</v>
+      </c>
+      <c r="H139" t="n">
+        <v>193.306</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C140" t="n">
+        <v>14.047</v>
+      </c>
+      <c r="D140" t="n">
+        <v>30.812</v>
+      </c>
+      <c r="E140" t="n">
+        <v>192.605</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="G140" t="n">
+        <v>26.663</v>
+      </c>
+      <c r="H140" t="n">
+        <v>192.605</v>
       </c>
     </row>
   </sheetData>
